--- a/planning.xlsx
+++ b/planning.xlsx
@@ -12,10 +12,10 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7095"/>
   </bookViews>
   <sheets>
-    <sheet name="Total_ND" sheetId="1" r:id="rId1"/>
+    <sheet name="Fusion unique" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Total_ND!$A$1:$I$1063</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fusion unique'!$A$1:$I$1063</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -6931,18 +6931,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7277,10 +7266,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1081"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I1063"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7309,7 +7298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7338,7 +7327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7367,7 +7356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -7396,7 +7385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -7425,7 +7414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -7454,7 +7443,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -7483,7 +7472,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -7512,7 +7501,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -7541,7 +7530,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -7570,7 +7559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -7599,7 +7588,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -7628,7 +7617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -7657,7 +7646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -7686,7 +7675,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -7715,7 +7704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -7744,7 +7733,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>90</v>
       </c>
@@ -7773,7 +7762,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -7802,7 +7791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -7831,7 +7820,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -7860,7 +7849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -7889,7 +7878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -7918,7 +7907,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>115</v>
       </c>
@@ -7947,7 +7936,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -7976,7 +7965,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>127</v>
       </c>
@@ -8005,7 +7994,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -8034,7 +8023,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -8063,7 +8052,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>127</v>
       </c>
@@ -8092,7 +8081,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -8121,7 +8110,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>127</v>
       </c>
@@ -8150,7 +8139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>127</v>
       </c>
@@ -8179,7 +8168,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>127</v>
       </c>
@@ -8208,7 +8197,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>157</v>
       </c>
@@ -8237,7 +8226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -8266,7 +8255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>161</v>
       </c>
@@ -8295,7 +8284,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>161</v>
       </c>
@@ -8324,7 +8313,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>161</v>
       </c>
@@ -8353,7 +8342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -8382,7 +8371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -8411,7 +8400,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -8440,7 +8429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -8469,7 +8458,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -8498,7 +8487,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -8527,7 +8516,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -8556,7 +8545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>185</v>
       </c>
@@ -8585,7 +8574,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -8614,7 +8603,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>185</v>
       </c>
@@ -8643,7 +8632,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>185</v>
       </c>
@@ -8672,7 +8661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>211</v>
       </c>
@@ -8701,7 +8690,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>211</v>
       </c>
@@ -8730,7 +8719,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>211</v>
       </c>
@@ -8759,7 +8748,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>220</v>
       </c>
@@ -8788,7 +8777,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>220</v>
       </c>
@@ -8817,7 +8806,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -8846,7 +8835,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>220</v>
       </c>
@@ -8875,7 +8864,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>220</v>
       </c>
@@ -8904,7 +8893,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>220</v>
       </c>
@@ -8933,7 +8922,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>220</v>
       </c>
@@ -8962,7 +8951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>247</v>
       </c>
@@ -8991,7 +8980,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>247</v>
       </c>
@@ -9020,7 +9009,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>247</v>
       </c>
@@ -9049,7 +9038,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>247</v>
       </c>
@@ -9078,7 +9067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>247</v>
       </c>
@@ -9107,7 +9096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>247</v>
       </c>
@@ -9136,7 +9125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>247</v>
       </c>
@@ -9165,7 +9154,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>269</v>
       </c>
@@ -9194,7 +9183,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>273</v>
       </c>
@@ -9223,7 +9212,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>273</v>
       </c>
@@ -9252,7 +9241,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>273</v>
       </c>
@@ -9281,7 +9270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>273</v>
       </c>
@@ -9310,7 +9299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>273</v>
       </c>
@@ -9339,7 +9328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>273</v>
       </c>
@@ -9368,7 +9357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>273</v>
       </c>
@@ -9397,7 +9386,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>294</v>
       </c>
@@ -9426,7 +9415,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>294</v>
       </c>
@@ -9455,7 +9444,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>294</v>
       </c>
@@ -9484,7 +9473,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>294</v>
       </c>
@@ -9513,7 +9502,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>294</v>
       </c>
@@ -9542,7 +9531,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>294</v>
       </c>
@@ -9571,7 +9560,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>294</v>
       </c>
@@ -9600,7 +9589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>292</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>292</v>
       </c>
@@ -9658,7 +9647,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>292</v>
       </c>
@@ -9687,7 +9676,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>322</v>
       </c>
@@ -9716,7 +9705,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>322</v>
       </c>
@@ -9745,7 +9734,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>322</v>
       </c>
@@ -9774,7 +9763,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>322</v>
       </c>
@@ -9803,7 +9792,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>322</v>
       </c>
@@ -9832,7 +9821,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>342</v>
       </c>
@@ -9861,7 +9850,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>342</v>
       </c>
@@ -9890,7 +9879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>342</v>
       </c>
@@ -9919,7 +9908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>350</v>
       </c>
@@ -9948,7 +9937,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>350</v>
       </c>
@@ -9977,7 +9966,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>350</v>
       </c>
@@ -10006,7 +9995,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>350</v>
       </c>
@@ -10035,7 +10024,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>364</v>
       </c>
@@ -10064,7 +10053,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>364</v>
       </c>
@@ -10093,7 +10082,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>364</v>
       </c>
@@ -10122,7 +10111,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>364</v>
       </c>
@@ -10151,7 +10140,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>364</v>
       </c>
@@ -10180,7 +10169,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>364</v>
       </c>
@@ -10209,7 +10198,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>380</v>
       </c>
@@ -10238,7 +10227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>384</v>
       </c>
@@ -10267,7 +10256,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>384</v>
       </c>
@@ -10296,7 +10285,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>384</v>
       </c>
@@ -10325,7 +10314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>384</v>
       </c>
@@ -10354,7 +10343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>384</v>
       </c>
@@ -10383,7 +10372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>396</v>
       </c>
@@ -10412,7 +10401,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>396</v>
       </c>
@@ -10441,7 +10430,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>396</v>
       </c>
@@ -10470,7 +10459,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>396</v>
       </c>
@@ -10499,7 +10488,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>396</v>
       </c>
@@ -10528,7 +10517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>396</v>
       </c>
@@ -10557,7 +10546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>409</v>
       </c>
@@ -10586,7 +10575,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>409</v>
       </c>
@@ -10615,7 +10604,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>409</v>
       </c>
@@ -10644,7 +10633,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>409</v>
       </c>
@@ -10673,7 +10662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>409</v>
       </c>
@@ -10702,7 +10691,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>409</v>
       </c>
@@ -10731,7 +10720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>409</v>
       </c>
@@ -10760,7 +10749,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>409</v>
       </c>
@@ -10789,7 +10778,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>409</v>
       </c>
@@ -10818,7 +10807,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>409</v>
       </c>
@@ -10847,7 +10836,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>409</v>
       </c>
@@ -10876,7 +10865,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>409</v>
       </c>
@@ -10905,7 +10894,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>443</v>
       </c>
@@ -10934,7 +10923,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>443</v>
       </c>
@@ -10963,7 +10952,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>443</v>
       </c>
@@ -10992,7 +10981,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>443</v>
       </c>
@@ -11021,7 +11010,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>443</v>
       </c>
@@ -11050,7 +11039,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>443</v>
       </c>
@@ -11079,7 +11068,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>443</v>
       </c>
@@ -11108,7 +11097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>443</v>
       </c>
@@ -11137,7 +11126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>443</v>
       </c>
@@ -11166,7 +11155,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>443</v>
       </c>
@@ -11195,7 +11184,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>346</v>
       </c>
@@ -11224,7 +11213,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>346</v>
       </c>
@@ -11253,7 +11242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>346</v>
       </c>
@@ -11282,7 +11271,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>346</v>
       </c>
@@ -11311,7 +11300,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>346</v>
       </c>
@@ -11340,7 +11329,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>346</v>
       </c>
@@ -11369,7 +11358,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>346</v>
       </c>
@@ -11398,7 +11387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>346</v>
       </c>
@@ -11427,7 +11416,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>346</v>
       </c>
@@ -11456,7 +11445,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>346</v>
       </c>
@@ -11485,7 +11474,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>346</v>
       </c>
@@ -11514,7 +11503,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>346</v>
       </c>
@@ -11543,7 +11532,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>79</v>
       </c>
@@ -11572,7 +11561,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>79</v>
       </c>
@@ -11601,7 +11590,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>506</v>
       </c>
@@ -11630,7 +11619,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>506</v>
       </c>
@@ -11659,7 +11648,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>506</v>
       </c>
@@ -11688,7 +11677,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>517</v>
       </c>
@@ -11717,7 +11706,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>517</v>
       </c>
@@ -11746,7 +11735,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>517</v>
       </c>
@@ -11775,7 +11764,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>517</v>
       </c>
@@ -11804,7 +11793,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>517</v>
       </c>
@@ -11833,7 +11822,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>517</v>
       </c>
@@ -11862,7 +11851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>517</v>
       </c>
@@ -11891,7 +11880,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>517</v>
       </c>
@@ -11920,7 +11909,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>420</v>
       </c>
@@ -11949,7 +11938,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>420</v>
       </c>
@@ -11978,7 +11967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>420</v>
       </c>
@@ -12007,7 +11996,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>420</v>
       </c>
@@ -12036,7 +12025,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>420</v>
       </c>
@@ -12065,7 +12054,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>420</v>
       </c>
@@ -12094,7 +12083,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>420</v>
       </c>
@@ -12123,7 +12112,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>420</v>
       </c>
@@ -12152,7 +12141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>564</v>
       </c>
@@ -12181,7 +12170,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>564</v>
       </c>
@@ -12210,7 +12199,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>564</v>
       </c>
@@ -12239,7 +12228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>564</v>
       </c>
@@ -12268,7 +12257,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>564</v>
       </c>
@@ -12297,7 +12286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>564</v>
       </c>
@@ -12326,7 +12315,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>564</v>
       </c>
@@ -12355,7 +12344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>564</v>
       </c>
@@ -12384,7 +12373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>564</v>
       </c>
@@ -12413,7 +12402,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>583</v>
       </c>
@@ -12442,7 +12431,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>583</v>
       </c>
@@ -12471,7 +12460,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>583</v>
       </c>
@@ -12500,7 +12489,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>583</v>
       </c>
@@ -12529,7 +12518,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>583</v>
       </c>
@@ -12558,7 +12547,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>583</v>
       </c>
@@ -12587,7 +12576,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>583</v>
       </c>
@@ -12616,7 +12605,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>583</v>
       </c>
@@ -12645,7 +12634,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>583</v>
       </c>
@@ -12674,7 +12663,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>583</v>
       </c>
@@ -12703,7 +12692,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>583</v>
       </c>
@@ -12732,7 +12721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>583</v>
       </c>
@@ -12761,7 +12750,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>583</v>
       </c>
@@ -12790,7 +12779,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>618</v>
       </c>
@@ -12819,7 +12808,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>622</v>
       </c>
@@ -12848,7 +12837,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>622</v>
       </c>
@@ -12877,7 +12866,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>622</v>
       </c>
@@ -12906,7 +12895,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>622</v>
       </c>
@@ -12935,7 +12924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>622</v>
       </c>
@@ -12964,7 +12953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>622</v>
       </c>
@@ -12993,7 +12982,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>622</v>
       </c>
@@ -13022,7 +13011,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>622</v>
       </c>
@@ -13051,7 +13040,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>622</v>
       </c>
@@ -13080,7 +13069,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>458</v>
       </c>
@@ -13109,7 +13098,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>458</v>
       </c>
@@ -13138,7 +13127,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>458</v>
       </c>
@@ -13167,7 +13156,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>458</v>
       </c>
@@ -13196,7 +13185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>458</v>
       </c>
@@ -13225,7 +13214,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>458</v>
       </c>
@@ -13254,7 +13243,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>458</v>
       </c>
@@ -13283,7 +13272,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>644</v>
       </c>
@@ -13312,7 +13301,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>644</v>
       </c>
@@ -13341,7 +13330,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>644</v>
       </c>
@@ -13370,7 +13359,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>644</v>
       </c>
@@ -13399,7 +13388,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>644</v>
       </c>
@@ -13428,7 +13417,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>644</v>
       </c>
@@ -13457,7 +13446,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>644</v>
       </c>
@@ -13486,7 +13475,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>431</v>
       </c>
@@ -13515,7 +13504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>431</v>
       </c>
@@ -13544,7 +13533,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>431</v>
       </c>
@@ -13573,7 +13562,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>431</v>
       </c>
@@ -13602,7 +13591,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>686</v>
       </c>
@@ -13631,7 +13620,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>686</v>
       </c>
@@ -13660,7 +13649,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>686</v>
       </c>
@@ -13689,7 +13678,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>686</v>
       </c>
@@ -13718,7 +13707,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>686</v>
       </c>
@@ -13747,7 +13736,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>686</v>
       </c>
@@ -13776,7 +13765,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>686</v>
       </c>
@@ -13805,7 +13794,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>686</v>
       </c>
@@ -13834,7 +13823,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>686</v>
       </c>
@@ -13863,7 +13852,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>686</v>
       </c>
@@ -13892,7 +13881,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>686</v>
       </c>
@@ -13921,7 +13910,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>686</v>
       </c>
@@ -13950,7 +13939,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>686</v>
       </c>
@@ -13979,7 +13968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>686</v>
       </c>
@@ -14008,7 +13997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>719</v>
       </c>
@@ -14037,7 +14026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>723</v>
       </c>
@@ -14066,7 +14055,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>723</v>
       </c>
@@ -14095,7 +14084,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>723</v>
       </c>
@@ -14124,7 +14113,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>723</v>
       </c>
@@ -14153,7 +14142,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>723</v>
       </c>
@@ -14182,7 +14171,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>723</v>
       </c>
@@ -14211,7 +14200,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>723</v>
       </c>
@@ -14240,7 +14229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>742</v>
       </c>
@@ -14269,7 +14258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>742</v>
       </c>
@@ -14298,7 +14287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>742</v>
       </c>
@@ -14327,7 +14316,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>742</v>
       </c>
@@ -14356,7 +14345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>742</v>
       </c>
@@ -14385,7 +14374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>742</v>
       </c>
@@ -14414,7 +14403,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>757</v>
       </c>
@@ -14443,7 +14432,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>757</v>
       </c>
@@ -14472,7 +14461,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>757</v>
       </c>
@@ -14501,7 +14490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>757</v>
       </c>
@@ -14530,7 +14519,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>757</v>
       </c>
@@ -14559,7 +14548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>757</v>
       </c>
@@ -14588,7 +14577,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>757</v>
       </c>
@@ -14617,7 +14606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>757</v>
       </c>
@@ -14646,7 +14635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>774</v>
       </c>
@@ -14675,7 +14664,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>774</v>
       </c>
@@ -14704,7 +14693,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>774</v>
       </c>
@@ -14733,7 +14722,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>774</v>
       </c>
@@ -14762,7 +14751,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>774</v>
       </c>
@@ -14791,7 +14780,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>774</v>
       </c>
@@ -14820,7 +14809,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>774</v>
       </c>
@@ -14849,7 +14838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>774</v>
       </c>
@@ -14878,7 +14867,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>774</v>
       </c>
@@ -14907,7 +14896,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>791</v>
       </c>
@@ -14936,7 +14925,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>791</v>
       </c>
@@ -14965,7 +14954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>791</v>
       </c>
@@ -14994,7 +14983,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>791</v>
       </c>
@@ -15023,7 +15012,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>791</v>
       </c>
@@ -15052,7 +15041,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>791</v>
       </c>
@@ -15081,7 +15070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>791</v>
       </c>
@@ -15110,7 +15099,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>791</v>
       </c>
@@ -15139,7 +15128,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>791</v>
       </c>
@@ -15168,7 +15157,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>791</v>
       </c>
@@ -15197,7 +15186,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>816</v>
       </c>
@@ -15226,7 +15215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>818</v>
       </c>
@@ -15255,7 +15244,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>336</v>
       </c>
@@ -15284,7 +15273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -15313,7 +15302,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -15342,7 +15331,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -15371,7 +15360,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -15400,7 +15389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -15429,7 +15418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -15458,7 +15447,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -15487,7 +15476,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -15516,7 +15505,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -15545,7 +15534,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -15574,7 +15563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -15603,7 +15592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -15632,7 +15621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -15661,7 +15650,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -15690,7 +15679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -15719,7 +15708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -15748,7 +15737,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -15777,7 +15766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -15806,7 +15795,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -15835,7 +15824,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -15864,7 +15853,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -15893,7 +15882,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -15922,7 +15911,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -15951,7 +15940,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -15980,7 +15969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -16009,7 +15998,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -16038,7 +16027,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -16067,7 +16056,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -16096,7 +16085,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -16125,7 +16114,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>16</v>
       </c>
@@ -16154,7 +16143,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -16183,7 +16172,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -16212,7 +16201,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -16241,7 +16230,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -16270,7 +16259,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>16</v>
       </c>
@@ -16299,7 +16288,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -16328,7 +16317,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -16357,7 +16346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -16386,7 +16375,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -16415,7 +16404,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -16444,7 +16433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -16473,7 +16462,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -16502,7 +16491,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -16531,7 +16520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -16560,7 +16549,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -16589,7 +16578,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>16</v>
       </c>
@@ -16618,7 +16607,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>16</v>
       </c>
@@ -16647,7 +16636,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>16</v>
       </c>
@@ -16676,7 +16665,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>16</v>
       </c>
@@ -16705,7 +16694,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>16</v>
       </c>
@@ -16734,7 +16723,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>16</v>
       </c>
@@ -16763,7 +16752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>16</v>
       </c>
@@ -16792,7 +16781,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>16</v>
       </c>
@@ -16821,7 +16810,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>16</v>
       </c>
@@ -16850,7 +16839,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>16</v>
       </c>
@@ -16879,7 +16868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>16</v>
       </c>
@@ -16908,7 +16897,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>16</v>
       </c>
@@ -16937,7 +16926,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>16</v>
       </c>
@@ -16966,7 +16955,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>16</v>
       </c>
@@ -16995,7 +16984,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>16</v>
       </c>
@@ -17024,7 +17013,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>16</v>
       </c>
@@ -17053,7 +17042,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>16</v>
       </c>
@@ -17082,7 +17071,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>16</v>
       </c>
@@ -17111,7 +17100,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>16</v>
       </c>
@@ -17140,7 +17129,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>16</v>
       </c>
@@ -17169,7 +17158,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>16</v>
       </c>
@@ -17198,7 +17187,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>16</v>
       </c>
@@ -17227,7 +17216,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>16</v>
       </c>
@@ -17256,7 +17245,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>16</v>
       </c>
@@ -17285,7 +17274,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>16</v>
       </c>
@@ -17314,7 +17303,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -17343,7 +17332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>16</v>
       </c>
@@ -17372,7 +17361,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>16</v>
       </c>
@@ -17401,7 +17390,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>16</v>
       </c>
@@ -17430,7 +17419,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>16</v>
       </c>
@@ -17459,7 +17448,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>16</v>
       </c>
@@ -17488,7 +17477,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>16</v>
       </c>
@@ -17517,7 +17506,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>16</v>
       </c>
@@ -17546,7 +17535,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>16</v>
       </c>
@@ -17575,7 +17564,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>16</v>
       </c>
@@ -17604,7 +17593,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>16</v>
       </c>
@@ -17633,7 +17622,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>16</v>
       </c>
@@ -17662,7 +17651,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>16</v>
       </c>
@@ -17691,7 +17680,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>16</v>
       </c>
@@ -17720,7 +17709,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>16</v>
       </c>
@@ -17749,7 +17738,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>16</v>
       </c>
@@ -17778,7 +17767,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>16</v>
       </c>
@@ -17807,7 +17796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>16</v>
       </c>
@@ -17836,7 +17825,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>16</v>
       </c>
@@ -17865,7 +17854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>16</v>
       </c>
@@ -17894,7 +17883,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>16</v>
       </c>
@@ -17923,7 +17912,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>16</v>
       </c>
@@ -17952,7 +17941,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>16</v>
       </c>
@@ -17981,7 +17970,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>16</v>
       </c>
@@ -18010,7 +17999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>16</v>
       </c>
@@ -18039,7 +18028,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>16</v>
       </c>
@@ -18068,7 +18057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>16</v>
       </c>
@@ -18097,7 +18086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>16</v>
       </c>
@@ -18126,7 +18115,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>16</v>
       </c>
@@ -18155,7 +18144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>16</v>
       </c>
@@ -18184,7 +18173,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>16</v>
       </c>
@@ -18213,7 +18202,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>16</v>
       </c>
@@ -18242,7 +18231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>16</v>
       </c>
@@ -18271,7 +18260,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>16</v>
       </c>
@@ -18300,7 +18289,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>16</v>
       </c>
@@ -18329,7 +18318,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>16</v>
       </c>
@@ -18358,7 +18347,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>16</v>
       </c>
@@ -18387,7 +18376,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>16</v>
       </c>
@@ -18416,7 +18405,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>16</v>
       </c>
@@ -18445,7 +18434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>16</v>
       </c>
@@ -18474,7 +18463,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>16</v>
       </c>
@@ -18503,7 +18492,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>16</v>
       </c>
@@ -18532,7 +18521,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>16</v>
       </c>
@@ -18561,7 +18550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>16</v>
       </c>
@@ -18590,7 +18579,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>16</v>
       </c>
@@ -18619,7 +18608,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>16</v>
       </c>
@@ -18648,7 +18637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>16</v>
       </c>
@@ -18677,7 +18666,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -18706,7 +18695,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>16</v>
       </c>
@@ -18735,7 +18724,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>16</v>
       </c>
@@ -18764,7 +18753,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>16</v>
       </c>
@@ -18793,7 +18782,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>16</v>
       </c>
@@ -18822,7 +18811,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>16</v>
       </c>
@@ -18851,7 +18840,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>16</v>
       </c>
@@ -18880,7 +18869,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>16</v>
       </c>
@@ -18909,7 +18898,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>16</v>
       </c>
@@ -18938,7 +18927,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>16</v>
       </c>
@@ -18967,7 +18956,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>16</v>
       </c>
@@ -18996,7 +18985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>16</v>
       </c>
@@ -19025,7 +19014,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>16</v>
       </c>
@@ -19054,7 +19043,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>16</v>
       </c>
@@ -19083,7 +19072,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>16</v>
       </c>
@@ -19112,7 +19101,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>16</v>
       </c>
@@ -19141,7 +19130,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -19170,7 +19159,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>16</v>
       </c>
@@ -19199,7 +19188,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>16</v>
       </c>
@@ -19228,7 +19217,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -19257,7 +19246,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>16</v>
       </c>
@@ -19286,7 +19275,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>16</v>
       </c>
@@ -19315,7 +19304,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>16</v>
       </c>
@@ -19344,7 +19333,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>16</v>
       </c>
@@ -19373,7 +19362,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -19402,7 +19391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -19431,7 +19420,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>16</v>
       </c>
@@ -19460,7 +19449,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>16</v>
       </c>
@@ -19489,7 +19478,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>16</v>
       </c>
@@ -19518,7 +19507,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -19547,7 +19536,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -19576,7 +19565,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -19605,7 +19594,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -19634,7 +19623,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -19663,7 +19652,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -19692,7 +19681,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -19721,7 +19710,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -19750,7 +19739,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -19779,7 +19768,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -19808,7 +19797,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -19837,7 +19826,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -19866,7 +19855,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -19895,7 +19884,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -19924,7 +19913,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -19953,7 +19942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -19982,7 +19971,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -20011,7 +20000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -20040,7 +20029,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -20069,7 +20058,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -20098,7 +20087,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -20127,7 +20116,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -20156,7 +20145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -20185,7 +20174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -20214,7 +20203,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -20243,7 +20232,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -20272,7 +20261,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20301,7 +20290,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20330,7 +20319,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20359,7 +20348,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20388,7 +20377,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20417,7 +20406,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20446,7 +20435,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20475,7 +20464,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20504,7 +20493,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20533,7 +20522,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20562,7 +20551,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20591,7 +20580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20620,7 +20609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20649,7 +20638,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20678,7 +20667,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20707,7 +20696,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20736,7 +20725,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20765,7 +20754,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20794,7 +20783,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -20823,7 +20812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -20852,7 +20841,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -20881,7 +20870,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -20910,7 +20899,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -20939,7 +20928,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -20968,7 +20957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -20997,7 +20986,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21026,7 +21015,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21055,7 +21044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21084,7 +21073,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21113,7 +21102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21142,7 +21131,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21171,7 +21160,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21200,7 +21189,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21229,7 +21218,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21258,7 +21247,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21287,7 +21276,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21316,7 +21305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21345,7 +21334,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21374,7 +21363,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21403,7 +21392,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21432,7 +21421,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21461,7 +21450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21490,7 +21479,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21519,7 +21508,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21548,7 +21537,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21577,7 +21566,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21606,7 +21595,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21635,7 +21624,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21664,7 +21653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21693,7 +21682,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21722,7 +21711,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21751,7 +21740,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21780,7 +21769,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21809,7 +21798,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -21838,7 +21827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -21867,7 +21856,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -21896,7 +21885,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -21925,7 +21914,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -21954,7 +21943,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -21983,7 +21972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22012,7 +22001,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22041,7 +22030,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22070,7 +22059,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22099,7 +22088,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22128,7 +22117,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22157,7 +22146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22186,7 +22175,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22215,7 +22204,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22244,7 +22233,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22273,7 +22262,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22302,7 +22291,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22331,7 +22320,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22360,7 +22349,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22389,7 +22378,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22418,7 +22407,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22447,7 +22436,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22476,7 +22465,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22505,7 +22494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22534,7 +22523,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22563,7 +22552,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22592,7 +22581,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22621,7 +22610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22650,7 +22639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22679,7 +22668,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22708,7 +22697,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22737,7 +22726,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22766,7 +22755,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22795,7 +22784,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -22824,7 +22813,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -22853,7 +22842,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -22882,7 +22871,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -22911,7 +22900,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -22940,7 +22929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -22969,7 +22958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -22998,7 +22987,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23027,7 +23016,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23056,7 +23045,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23085,7 +23074,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23114,7 +23103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23143,7 +23132,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23172,7 +23161,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23201,7 +23190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23230,7 +23219,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23259,7 +23248,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23288,7 +23277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23317,7 +23306,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23346,7 +23335,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23375,7 +23364,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23404,7 +23393,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23433,7 +23422,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23462,7 +23451,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23491,7 +23480,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23520,7 +23509,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23549,7 +23538,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23578,7 +23567,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23607,7 +23596,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23636,7 +23625,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23665,7 +23654,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23694,7 +23683,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23723,7 +23712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23752,7 +23741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23781,7 +23770,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23810,7 +23799,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -23839,7 +23828,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -23868,7 +23857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -23897,7 +23886,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -23926,7 +23915,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -23955,7 +23944,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -23984,7 +23973,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24013,7 +24002,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24042,7 +24031,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24071,7 +24060,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24100,7 +24089,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24129,7 +24118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24158,7 +24147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24187,7 +24176,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24216,7 +24205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24245,7 +24234,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24274,7 +24263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24303,7 +24292,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24332,7 +24321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24361,7 +24350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24390,7 +24379,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24419,7 +24408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24448,7 +24437,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24477,7 +24466,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24506,7 +24495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24535,7 +24524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24564,7 +24553,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24593,7 +24582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24622,7 +24611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24651,7 +24640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24680,7 +24669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24709,7 +24698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24738,7 +24727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24767,7 +24756,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24796,7 +24785,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -24825,7 +24814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -24854,7 +24843,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -24883,7 +24872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -24912,7 +24901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -24941,7 +24930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -24970,7 +24959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -24999,7 +24988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25028,7 +25017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25057,7 +25046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25086,7 +25075,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25115,7 +25104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25144,7 +25133,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25173,7 +25162,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25202,7 +25191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25231,7 +25220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25260,7 +25249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25289,7 +25278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25318,7 +25307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25347,7 +25336,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25376,7 +25365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25405,7 +25394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25434,7 +25423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25463,7 +25452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25492,7 +25481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25521,7 +25510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25550,7 +25539,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25579,7 +25568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25608,7 +25597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25637,7 +25626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25666,7 +25655,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25695,7 +25684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25724,7 +25713,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25753,7 +25742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25782,7 +25771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25811,7 +25800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -25840,7 +25829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -25869,7 +25858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -25898,7 +25887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -25927,7 +25916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -25956,7 +25945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -25985,7 +25974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26014,7 +26003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26043,7 +26032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26072,7 +26061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26101,7 +26090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26130,7 +26119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26159,7 +26148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26188,7 +26177,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26217,7 +26206,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26246,7 +26235,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26275,7 +26264,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26304,7 +26293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26333,7 +26322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26362,7 +26351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26391,7 +26380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26420,7 +26409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26449,7 +26438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26478,7 +26467,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26507,7 +26496,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26536,7 +26525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26565,7 +26554,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26594,7 +26583,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26623,7 +26612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26652,7 +26641,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26681,7 +26670,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26710,7 +26699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26739,7 +26728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26768,7 +26757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26797,7 +26786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -26826,7 +26815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -26855,7 +26844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -26884,7 +26873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -26913,7 +26902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -26942,7 +26931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -26971,7 +26960,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27000,7 +26989,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27029,7 +27018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27058,7 +27047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27087,7 +27076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27116,7 +27105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27145,7 +27134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27174,7 +27163,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27203,7 +27192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27232,7 +27221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27261,7 +27250,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27290,7 +27279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27319,7 +27308,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27348,7 +27337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27377,7 +27366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27406,7 +27395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27435,7 +27424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27464,7 +27453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27493,7 +27482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27522,7 +27511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27551,7 +27540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27580,7 +27569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27609,7 +27598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27638,7 +27627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27667,7 +27656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27696,7 +27685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27725,7 +27714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27754,7 +27743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27783,7 +27772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27812,7 +27801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -27841,7 +27830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -27870,7 +27859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -27899,7 +27888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -27928,7 +27917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -27957,7 +27946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -27986,7 +27975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28015,7 +28004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28044,7 +28033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28073,7 +28062,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28102,7 +28091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28131,7 +28120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28160,7 +28149,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28189,7 +28178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28218,7 +28207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28247,7 +28236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28276,7 +28265,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28305,7 +28294,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28334,7 +28323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28363,7 +28352,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28392,7 +28381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28421,7 +28410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28450,7 +28439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28479,7 +28468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28508,7 +28497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28537,7 +28526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28566,7 +28555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28595,7 +28584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28624,7 +28613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28653,7 +28642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28682,7 +28671,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28711,7 +28700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28740,7 +28729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28769,7 +28758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28798,7 +28787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -28827,7 +28816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -28856,7 +28845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -28885,7 +28874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -28914,7 +28903,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -28943,7 +28932,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -28972,7 +28961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29001,7 +28990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29030,7 +29019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29059,7 +29048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29088,7 +29077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29117,7 +29106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29146,7 +29135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29175,7 +29164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29204,7 +29193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29233,7 +29222,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29262,7 +29251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29291,7 +29280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29320,7 +29309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29349,7 +29338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29378,7 +29367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29407,7 +29396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29436,7 +29425,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29465,7 +29454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29494,7 +29483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29523,7 +29512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29552,7 +29541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29581,7 +29570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29610,7 +29599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29639,7 +29628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29668,7 +29657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29697,7 +29686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29726,7 +29715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29755,7 +29744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29784,7 +29773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29813,7 +29802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -29842,7 +29831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -29871,7 +29860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -29900,7 +29889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -29929,7 +29918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -29958,7 +29947,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -29987,7 +29976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30016,7 +30005,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30045,7 +30034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30074,7 +30063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30103,7 +30092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30132,7 +30121,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30161,7 +30150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30190,7 +30179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30219,7 +30208,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30248,7 +30237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30277,7 +30266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30306,7 +30295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30335,7 +30324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30364,7 +30353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30393,7 +30382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30422,7 +30411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30451,7 +30440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30480,7 +30469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30509,7 +30498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30538,7 +30527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30567,7 +30556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30596,7 +30585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30625,7 +30614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30654,7 +30643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30683,7 +30672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30712,7 +30701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30741,7 +30730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30770,7 +30759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30799,7 +30788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -30828,7 +30817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -30857,7 +30846,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -30886,7 +30875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -30915,7 +30904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -30944,7 +30933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -30973,7 +30962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31002,7 +30991,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31031,7 +31020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31060,7 +31049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31089,7 +31078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31118,7 +31107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31147,7 +31136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31176,7 +31165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31205,7 +31194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31234,7 +31223,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31263,7 +31252,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31292,7 +31281,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31321,7 +31310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31350,7 +31339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31379,7 +31368,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31408,7 +31397,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31437,7 +31426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31466,7 +31455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31495,7 +31484,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31524,7 +31513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31553,7 +31542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31582,7 +31571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31611,7 +31600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31640,7 +31629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31669,7 +31658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31698,7 +31687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31727,7 +31716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31756,7 +31745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31785,7 +31774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31814,7 +31803,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -31843,7 +31832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -31872,7 +31861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -31901,7 +31890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -31930,7 +31919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -31959,7 +31948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -31988,7 +31977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32017,7 +32006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32046,7 +32035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32075,7 +32064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32104,7 +32093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32133,7 +32122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32162,7 +32151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>24</v>
       </c>
@@ -32191,7 +32180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>37</v>
       </c>
@@ -32220,7 +32209,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>90</v>
       </c>
@@ -32249,7 +32238,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>115</v>
       </c>
@@ -32278,7 +32267,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>53</v>
       </c>
@@ -32307,7 +32296,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>53</v>
       </c>
@@ -32336,7 +32325,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>185</v>
       </c>
@@ -32365,7 +32354,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>185</v>
       </c>
@@ -32394,7 +32383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>185</v>
       </c>
@@ -32423,7 +32412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>185</v>
       </c>
@@ -32452,7 +32441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>185</v>
       </c>
@@ -32481,7 +32470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>185</v>
       </c>
@@ -32510,7 +32499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>211</v>
       </c>
@@ -32539,7 +32528,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>211</v>
       </c>
@@ -32568,7 +32557,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>211</v>
       </c>
@@ -32597,7 +32586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>211</v>
       </c>
@@ -32626,7 +32615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>220</v>
       </c>
@@ -32655,7 +32644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>220</v>
       </c>
@@ -32684,7 +32673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>273</v>
       </c>
@@ -32713,7 +32702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>273</v>
       </c>
@@ -32742,7 +32731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>294</v>
       </c>
@@ -32771,7 +32760,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>294</v>
       </c>
@@ -32800,7 +32789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>294</v>
       </c>
@@ -32829,7 +32818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>294</v>
       </c>
@@ -32858,7 +32847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>292</v>
       </c>
@@ -32887,7 +32876,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>292</v>
       </c>
@@ -32916,7 +32905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>322</v>
       </c>
@@ -32945,7 +32934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>342</v>
       </c>
@@ -32974,7 +32963,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>342</v>
       </c>
@@ -33003,7 +32992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>342</v>
       </c>
@@ -33032,7 +33021,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>364</v>
       </c>
@@ -33061,7 +33050,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>364</v>
       </c>
@@ -33090,7 +33079,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>384</v>
       </c>
@@ -33119,7 +33108,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>384</v>
       </c>
@@ -33148,7 +33137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>384</v>
       </c>
@@ -33177,7 +33166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>384</v>
       </c>
@@ -33206,7 +33195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>396</v>
       </c>
@@ -33235,7 +33224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>409</v>
       </c>
@@ -33264,7 +33253,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>409</v>
       </c>
@@ -33293,7 +33282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>443</v>
       </c>
@@ -33322,7 +33311,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>443</v>
       </c>
@@ -33351,7 +33340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>346</v>
       </c>
@@ -33380,7 +33369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>346</v>
       </c>
@@ -33409,7 +33398,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>346</v>
       </c>
@@ -33438,7 +33427,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>346</v>
       </c>
@@ -33467,7 +33456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>42</v>
       </c>
@@ -33496,7 +33485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>517</v>
       </c>
@@ -33525,7 +33514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>420</v>
       </c>
@@ -33554,7 +33543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>420</v>
       </c>
@@ -33583,7 +33572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>420</v>
       </c>
@@ -33612,7 +33601,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>420</v>
       </c>
@@ -33641,7 +33630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>564</v>
       </c>
@@ -33670,7 +33659,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>564</v>
       </c>
@@ -33699,7 +33688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>564</v>
       </c>
@@ -33728,7 +33717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>583</v>
       </c>
@@ -33757,7 +33746,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>583</v>
       </c>
@@ -33786,7 +33775,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>583</v>
       </c>
@@ -33815,7 +33804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>583</v>
       </c>
@@ -33844,7 +33833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>618</v>
       </c>
@@ -33873,7 +33862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>622</v>
       </c>
@@ -33902,7 +33891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>458</v>
       </c>
@@ -33931,7 +33920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>458</v>
       </c>
@@ -33960,7 +33949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>644</v>
       </c>
@@ -33989,7 +33978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>644</v>
       </c>
@@ -34018,7 +34007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>644</v>
       </c>
@@ -34047,7 +34036,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>644</v>
       </c>
@@ -34076,7 +34065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>431</v>
       </c>
@@ -34105,7 +34094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>431</v>
       </c>
@@ -34134,7 +34123,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>431</v>
       </c>
@@ -34163,7 +34152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>686</v>
       </c>
@@ -34192,7 +34181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>686</v>
       </c>
@@ -34221,7 +34210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>686</v>
       </c>
@@ -34250,7 +34239,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>686</v>
       </c>
@@ -34279,7 +34268,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>686</v>
       </c>
@@ -34308,7 +34297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>686</v>
       </c>
@@ -34337,7 +34326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>686</v>
       </c>
@@ -34366,7 +34355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>742</v>
       </c>
@@ -34395,7 +34384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>757</v>
       </c>
@@ -34424,7 +34413,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>757</v>
       </c>
@@ -34453,7 +34442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>791</v>
       </c>
@@ -34482,7 +34471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>791</v>
       </c>
@@ -34511,7 +34500,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>791</v>
       </c>
@@ -34540,7 +34529,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>791</v>
       </c>
@@ -34569,7 +34558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>336</v>
       </c>
@@ -34598,7 +34587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>16</v>
       </c>
@@ -34627,7 +34616,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>16</v>
       </c>
@@ -34656,7 +34645,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>16</v>
       </c>
@@ -34685,7 +34674,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>16</v>
       </c>
@@ -34714,7 +34703,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>16</v>
       </c>
@@ -34743,7 +34732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>16</v>
       </c>
@@ -34772,7 +34761,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>16</v>
       </c>
@@ -34801,7 +34790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>16</v>
       </c>
@@ -34830,7 +34819,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>16</v>
       </c>
@@ -34859,7 +34848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>16</v>
       </c>
@@ -34888,7 +34877,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>16</v>
       </c>
@@ -34917,7 +34906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>16</v>
       </c>
@@ -34946,7 +34935,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>16</v>
       </c>
@@ -34975,7 +34964,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>16</v>
       </c>
@@ -35004,7 +34993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>16</v>
       </c>
@@ -35033,7 +35022,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>16</v>
       </c>
@@ -35062,7 +35051,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>16</v>
       </c>
@@ -35091,7 +35080,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>16</v>
       </c>
@@ -35120,7 +35109,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>16</v>
       </c>
@@ -35149,7 +35138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>16</v>
       </c>
@@ -35178,7 +35167,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>16</v>
       </c>
@@ -35207,7 +35196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>16</v>
       </c>
@@ -35236,7 +35225,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>16</v>
       </c>
@@ -35265,7 +35254,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>16</v>
       </c>
@@ -35294,7 +35283,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>16</v>
       </c>
@@ -35323,7 +35312,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35352,7 +35341,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35381,7 +35370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35410,7 +35399,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35439,7 +35428,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35468,7 +35457,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35497,7 +35486,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35526,7 +35515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35555,7 +35544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35584,7 +35573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35613,7 +35602,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35642,7 +35631,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35671,7 +35660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35700,7 +35689,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35729,7 +35718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35758,7 +35747,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35787,7 +35776,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35816,7 +35805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -35845,7 +35834,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -35874,7 +35863,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -35903,7 +35892,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -35932,7 +35921,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -35961,7 +35950,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -35990,7 +35979,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36019,7 +36008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36048,7 +36037,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36077,7 +36066,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36106,7 +36095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36135,7 +36124,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36164,7 +36153,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36193,7 +36182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36222,7 +36211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36251,7 +36240,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36280,7 +36269,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36309,7 +36298,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36338,7 +36327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36367,7 +36356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36396,7 +36385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36425,7 +36414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36454,7 +36443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36483,7 +36472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36512,7 +36501,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36541,7 +36530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36570,7 +36559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36599,7 +36588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36628,7 +36617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36657,7 +36646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36686,7 +36675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36715,7 +36704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36744,7 +36733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36773,7 +36762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36802,7 +36791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -36831,7 +36820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -36860,7 +36849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -36889,7 +36878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -36918,7 +36907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -36947,7 +36936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -36976,7 +36965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37005,7 +36994,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37034,7 +37023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37063,7 +37052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37092,7 +37081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37121,7 +37110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37150,7 +37139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37179,7 +37168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37208,7 +37197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37237,7 +37226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37266,7 +37255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37295,7 +37284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37324,7 +37313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37353,7 +37342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37382,7 +37371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37411,7 +37400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37440,7 +37429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37469,7 +37458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37498,7 +37487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37527,7 +37516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37556,7 +37545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37585,7 +37574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37614,7 +37603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37643,7 +37632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37672,7 +37661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37701,7 +37690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37730,7 +37719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37759,7 +37748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37788,7 +37777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37817,7 +37806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -37846,7 +37835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -37875,7 +37864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -37904,7 +37893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -37933,7 +37922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -37962,7 +37951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -37991,7 +37980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38020,7 +38009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38049,7 +38038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38078,7 +38067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38107,24 +38096,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1064" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1065" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1066" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1067" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1068" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1069" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1070" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1071" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1072" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1073" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1074" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1075" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1076" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1077" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1078" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1079" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1080" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="1081" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9436" uniqueCount="2289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9435" uniqueCount="2289">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -9057,12 +9057,10 @@
       <c r="F62" t="s">
         <v>65</v>
       </c>
-      <c r="G62" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="1">
+      <c r="G62" s="1">
         <v>46069</v>
       </c>
+      <c r="H62" s="1"/>
       <c r="I62" t="s">
         <v>23</v>
       </c>
@@ -38099,7 +38097,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A360:I367 A1:I5 A1026:I1029 A1025:G1025 A895:I895 A894:F894 A127:I127 A126:G126 I126 A9:I9 A8:G8 I8 A44:I49 A43:G43 I43 A59:I60 A56:G56 I56 A80:I80 A78:G78 I78 A82:G82 A81:G81 I81 A84:I86 A83:G83 I83 A99:I103 A97:F97 I97 A116:I117 A115:G115 I115 A131:I133 A129:G129 I129 A140:I145 A139:G139 I139 A162:I162 A161:G161 I161 A185:I188 A184:G184 I183:I184 A199:I200 A197:G197 I197 A229:I232 A228:G228 I228 A236:I238 A234:G235 I234:I235 A245:I246 A243:G243 I243 A252:I256 A251:G251 I251 A327:I329 A326:G326 I326 A382:I383 A381:G381 I381 A471:I478 A470:G470 I470 A480:I487 A479:G479 I479 A510:I516 A509:G509 I509 A525:I538 A523:G524 I523:I524 A620:I623 A617:G617 I617 A974:I981 A973:G973 I973 A983:I986 A982:G982 I982 A988:I1004 A987:G987 I987 A42:G42 I42 A273:I276 A272:G272 I272 A341:I341 A340:G340 I340 A343:I350 A342:G342 I342 A353:I358 A351:G351 I351 A584:I590 A583:G583 I583 A69:I72 A68:G68 I68 A149:I149 A148:G148 I148 A971:I972 A970:G970 I970 A63:I64 A61:G61 I61 A119:I120 A118:G118 I118 A241:I242 A239:G239 I239 A304:I305 A303:G303 I303 A331:I335 A330:G330 I330 A352:G352 I352 A412:I418 A411:G411 I411 A420:I422 A419:G419 I419 A424:I425 A423:G423 I423 A427:I446 A426:G426 I426 A448:I464 A447:G447 I447 A492:I507 A491:G491 I491 A508:G508 I508 A520:I522 A519:G519 I519 A540:I547 A539:G539 I539 A561:I564 A560:G560 I560 A576:I578 A575:G575 I575 A137:I138 A136:G136 I136 A147:G147 I147 A302:G302 A301:G301 I301 A401:I401 A399:G399 I399 A466:I468 A465:G465 I465 A559:G559 I559 A40:I41 A39:G39 I39 A33:I38 A31:G31 I31 A151:I151 A150:F150 I150 A271:G271 I271 A299:I300 A298:G298 I298 A359:G359 I359 A385:I385 A384:G384 I384 A574:G574 I574 A960:I963 A959:G959 I959 A965:I969 A964:G964 I964 A57:G57 I57 A209:I216 A208:G208 I208 A308:I315 A306:G307 I306:I307 A372:I380 A371:G371 I371 A400:G400 I400 A403:I407 A402:G402 I402 A580:I582 A579:G579 I579 A28:I30 A27:G27 I27 A128:G128 I128 A225:I226 A224:G224 I224 A549:I558 A548:G548 I548 A52:I55 A51:G51 I51 I82 A123:I123 A121:G121 I121 A146:G146 I146 A263:I263 A262:G262 I262 A285:I291 A284:G284 I284 A293:I297 A292:G292 I292 A490:G490 I490 A873:I875 A872:G872 I872 A164:I165 A163:G163 I163 A265:I270 A264:G264 I264 A337:I339 A336:G336 I336 A370:I370 A368:G368 I368 A489:I489 A488:G488 I488 A122:F122 H122:I122 A130:G130 I130 A135:I135 A134:G134 I134 A195:I196 A194:G194 I194 A259:I261 A258:G258 I258 A7:I7 A6:G6 I6 A202:I202 A201:G201 I201 A220:I223 A217:G218 I217:I218 A227:G227 I227 A317:I325 A316:G316 I316 A891:I893 A890:G890 I890 A952:I952 A951:G951 I951 A958:I958 A957:G957 I957 A167:I178 A166:G166 I166 A257:G257 I257 A369:G369 I369 A397:I397 A396:G396 I396 A867:I870 A865:G865 I865 A66:I67 A65:G65 I65 A74:I75 A73:F73 I73 A88:I96 A87:G87 I87 A105:F105 A104:G104 I104 A125:I125 A124:G124 I124 A278:I283 A277:G277 I277 A566:I573 A565:G565 I565 A153:I157 A152:G152 I152 A387:I394 A386:G386 I386 A395:G395 I395 A409:I410 A408:G408 I408 A469:G469 I469 A607:I609 A603:G603 I603 A655:I666 A654:H654 I302 A398:G398 I398 A518:I518 A517:G517 I517 A935:I941 A934:F934 H934:I934 A926:I927 A925:F925 H925:I925 A943:I946 A942:F942 H942 A929:I932 A928:F928 H928:I928 A918:I918 A917:F917 H917 A183:F183 A924:I924 A923:F923 H923:I923 A204:I207 A203:F203 H203:I203 A159:I160 A158:F158 H158:I158 A899:I903 A898:F898 H898 A98:F98 H98:I98 A886:I887 A884:F884 H884 A250:I250 A249:F249 H249:I249 A889:I889 A888:F888 H888 A79:F79 H79:I79 A107:I114 A106:F106 H106 A50:F50 H50:I50 A883:F883 H883 A877:I877 A876:F876 H876 A881:I881 A879:F879 H879:I879 A58:F58 H58:I58 A13:I13 A12:G12 I12 A77:I77 A76:F76 H76:I76 A219:F219 H219:I219 A180:I182 A179:F179 H179:I179 H105:I105 A248:I248 A247:F247 H247:I247 A62:G62 A244:F244 H244:I244 A882:F882 H882:I882 A11:I11 A10:H10 A15:I20 A14:H14 A22:I26 A21:H21 A32:H32 A190:I193 A189:H189 A198:H198 A233:H233 A240:H240 A592:I592 A591:H591 A596:I597 A593:H595 A599:I600 A598:H598 A602:I602 A601:H601 A604:H606 A612:I614 A610:H611 A616:I616 A615:H615 A618:H619 A625:I625 A624:H624 A627:I628 A626:H626 A630:I634 A629:H629 A636:I637 A635:H635 A640:I645 A638:H639 A647:I648 A646:H646 A650:I653 A649:H649 A668:I679 A667:H667 A681:I685 A680:H680 A687:I693 A686:H686 A695:I696 A694:H694 A698:I707 A697:H697 A709:I709 A708:H708 A711:I719 A710:H710 A725:I726 A720:H724 A728:I728 A727:H727 A730:I735 A729:H729 A737:I737 A736:H736 A739:I741 A738:H738 A743:I748 A742:H742 A751:I755 A749:H750 A757:I757 A756:H756 A759:I762 A758:H758 A764:I767 A763:H763 A769:I777 A768:H768 A779:I779 A778:H778 A781:I783 A780:H780 A785:I785 A784:H784 A787:I787 A786:H786 A791:I792 A788:H790 A794:I797 A793:H793 A800:I802 A798:H799 A805:I817 A803:H804 A819:I821 A818:H818 A823:I827 A822:H822 A830:I833 A828:H829 A835:I837 A834:H834 A839:I846 A838:H838 A850:I853 A847:H849 A855:I857 A854:H854 A859:I863 A858:H858 A864:H864 A866:H866 A871:H871 A878:H878 A880:H880 A885:H885 A897:I897 A896:H896 A905:I910 A904:H904 A912:I916 A911:H911 A920:I922 A919:H919 A933:H933 A948:I950 A947:H947 A954:I955 A953:H953 A956:H956 A1006:I1007 A1005:H1005 A1009:I1009 A1008:H1008 A1011:I1019 A1010:H1010 A1021:I1021 A1020:H1020 A1024:I1024 A1022:H1023 A1031:I1036 A1030:H1030 A1038:I1045 A1037:H1037 A1047:I1049 A1046:H1046 A1051:I1055 A1050:H1050 A1057:I1058 A1056:H1056 A1060:I1062 A1059:H1059 A1063:H1063" numberStoredAsText="1"/>
+    <ignoredError sqref="A360:I367 A1:I5 A1026:I1029 A1025:G1025 A895:I895 A894:F894 A127:I127 A126:G126 I126 A9:I9 A8:G8 I8 A44:I49 A43:G43 I43 A59:I60 A56:G56 I56 A80:I80 A78:G78 I78 A82:G82 A81:G81 I81 A84:I86 A83:G83 I83 A99:I103 A97:F97 I97 A116:I117 A115:G115 I115 A131:I133 A129:G129 I129 A140:I145 A139:G139 I139 A162:I162 A161:G161 I161 A185:I188 A184:G184 I183:I184 A199:I200 A197:G197 I197 A229:I232 A228:G228 I228 A236:I238 A234:G235 I234:I235 A245:I246 A243:G243 I243 A252:I256 A251:G251 I251 A327:I329 A326:G326 I326 A382:I383 A381:G381 I381 A471:I478 A470:G470 I470 A480:I487 A479:G479 I479 A510:I516 A509:G509 I509 A525:I538 A523:G524 I523:I524 A620:I623 A617:G617 I617 A974:I981 A973:G973 I973 A983:I986 A982:G982 I982 A988:I1004 A987:G987 I987 A42:G42 I42 A273:I276 A272:G272 I272 A341:I341 A340:G340 I340 A343:I350 A342:G342 I342 A353:I358 A351:G351 I351 A584:I590 A583:G583 I583 A69:I72 A68:G68 I68 A149:I149 A148:G148 I148 A971:I972 A970:G970 I970 A63:I64 A61:G61 I61 A119:I120 A118:G118 I118 A241:I242 A239:G239 I239 A304:I305 A303:G303 I303 A331:I335 A330:G330 I330 A352:G352 I352 A412:I418 A411:G411 I411 A420:I422 A419:G419 I419 A424:I425 A423:G423 I423 A427:I446 A426:G426 I426 A448:I464 A447:G447 I447 A492:I507 A491:G491 I491 A508:G508 I508 A520:I522 A519:G519 I519 A540:I547 A539:G539 I539 A561:I564 A560:G560 I560 A576:I578 A575:G575 I575 A137:I138 A136:G136 I136 A147:G147 I147 A302:G302 A301:G301 I301 A401:I401 A399:G399 I399 A466:I468 A465:G465 I465 A559:G559 I559 A40:I41 A39:G39 I39 A33:I38 A31:G31 I31 A151:I151 A150:F150 I150 A271:G271 I271 A299:I300 A298:G298 I298 A359:G359 I359 A385:I385 A384:G384 I384 A574:G574 I574 A960:I963 A959:G959 I959 A965:I969 A964:G964 I964 A57:G57 I57 A209:I216 A208:G208 I208 A308:I315 A306:G307 I306:I307 A372:I380 A371:G371 I371 A400:G400 I400 A403:I407 A402:G402 I402 A580:I582 A579:G579 I579 A28:I30 A27:G27 I27 A128:G128 I128 A225:I226 A224:G224 I224 A549:I558 A548:G548 I548 A52:I55 A51:G51 I51 I82 A123:I123 A121:G121 I121 A146:G146 I146 A263:I263 A262:G262 I262 A285:I291 A284:G284 I284 A293:I297 A292:G292 I292 A490:G490 I490 A873:I875 A872:G872 I872 A164:I165 A163:G163 I163 A265:I270 A264:G264 I264 A337:I339 A336:G336 I336 A370:I370 A368:G368 I368 A489:I489 A488:G488 I488 A122:F122 H122:I122 A130:G130 I130 A135:I135 A134:G134 I134 A195:I196 A194:G194 I194 A259:I261 A258:G258 I258 A7:I7 A6:G6 I6 A202:I202 A201:G201 I201 A220:I223 A217:G218 I217:I218 A227:G227 I227 A317:I325 A316:G316 I316 A891:I893 A890:G890 I890 A952:I952 A951:G951 I951 A958:I958 A957:G957 I957 A167:I178 A166:G166 I166 A257:G257 I257 A369:G369 I369 A397:I397 A396:G396 I396 A867:I870 A865:G865 I865 A66:I67 A65:G65 I65 A74:I75 A73:F73 I73 A88:I96 A87:G87 I87 A105:F105 A104:G104 I104 A125:I125 A124:G124 I124 A278:I283 A277:G277 I277 A566:I573 A565:G565 I565 A153:I157 A152:G152 I152 A387:I394 A386:G386 I386 A395:G395 I395 A409:I410 A408:G408 I408 A469:G469 I469 A607:I609 A603:G603 I603 A655:I666 A654:H654 I302 A398:G398 I398 A518:I518 A517:G517 I517 A935:I941 A934:F934 H934:I934 A926:I927 A925:F925 H925:I925 A943:I946 A942:F942 H942 A929:I932 A928:F928 H928:I928 A918:I918 A917:F917 H917 A183:F183 A924:I924 A923:F923 H923:I923 A204:I207 A203:F203 H203:I203 A159:I160 A158:F158 H158:I158 A899:I903 A898:F898 H898 A98:F98 H98:I98 A886:I887 A884:F884 H884 A250:I250 A249:F249 H249:I249 A889:I889 A888:F888 H888 A79:F79 H79:I79 A107:I114 A106:F106 H106 A50:F50 H50:I50 A883:F883 H883 A877:I877 A876:F876 H876 A881:I881 A879:F879 H879:I879 A58:F58 H58:I58 A13:I13 A12:G12 I12 A77:I77 A76:F76 H76:I76 A219:F219 H219:I219 A180:I182 A179:F179 H179:I179 H105:I105 A248:I248 A247:F247 H247:I247 A62:F62 A244:F244 H244:I244 A882:F882 H882:I882 A11:I11 A10:H10 A15:I20 A14:H14 A22:I26 A21:H21 A32:H32 A190:I193 A189:H189 A198:H198 A233:H233 A240:H240 A592:I592 A591:H591 A596:I597 A593:H595 A599:I600 A598:H598 A602:I602 A601:H601 A604:H606 A612:I614 A610:H611 A616:I616 A615:H615 A618:H619 A625:I625 A624:H624 A627:I628 A626:H626 A630:I634 A629:H629 A636:I637 A635:H635 A640:I645 A638:H639 A647:I648 A646:H646 A650:I653 A649:H649 A668:I679 A667:H667 A681:I685 A680:H680 A687:I693 A686:H686 A695:I696 A694:H694 A698:I707 A697:H697 A709:I709 A708:H708 A711:I719 A710:H710 A725:I726 A720:H724 A728:I728 A727:H727 A730:I735 A729:H729 A737:I737 A736:H736 A739:I741 A738:H738 A743:I748 A742:H742 A751:I755 A749:H750 A757:I757 A756:H756 A759:I762 A758:H758 A764:I767 A763:H763 A769:I777 A768:H768 A779:I779 A778:H778 A781:I783 A780:H780 A785:I785 A784:H784 A787:I787 A786:H786 A791:I792 A788:H790 A794:I797 A793:H793 A800:I802 A798:H799 A805:I817 A803:H804 A819:I821 A818:H818 A823:I827 A822:H822 A830:I833 A828:H829 A835:I837 A834:H834 A839:I846 A838:H838 A850:I853 A847:H849 A855:I857 A854:H854 A859:I863 A858:H858 A864:H864 A866:H866 A871:H871 A878:H878 A880:H880 A885:H885 A897:I897 A896:H896 A905:I910 A904:H904 A912:I916 A911:H911 A920:I922 A919:H919 A933:H933 A948:I950 A947:H947 A954:I955 A953:H953 A956:H956 A1006:I1007 A1005:H1005 A1009:I1009 A1008:H1008 A1011:I1019 A1010:H1010 A1021:I1021 A1020:H1020 A1024:I1024 A1022:H1023 A1031:I1036 A1030:H1030 A1038:I1045 A1037:H1037 A1047:I1049 A1046:H1046 A1051:I1055 A1050:H1050 A1057:I1058 A1056:H1056 A1060:I1062 A1059:H1059 A1063:H1063" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9378" uniqueCount="2286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9361" uniqueCount="2286">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -10064,9 +10064,7 @@
       <c r="G97" s="1">
         <v>45704</v>
       </c>
-      <c r="H97" s="1">
-        <v>46075</v>
-      </c>
+      <c r="H97" s="1"/>
       <c r="I97" t="s">
         <v>168</v>
       </c>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9536" uniqueCount="2312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9537" uniqueCount="2312">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -11391,6 +11391,9 @@
       <c r="G140" s="1">
         <v>46085</v>
       </c>
+      <c r="H140" t="s">
+        <v>109</v>
+      </c>
       <c r="I140" t="s">
         <v>578</v>
       </c>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Fusion unique" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fusion unique'!$A$1:$I$1063</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9564" uniqueCount="2331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9558" uniqueCount="2331">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7390,12 +7393,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7424,7 +7427,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7453,7 +7456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7482,7 +7485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -7511,7 +7514,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7569,7 +7572,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -7598,7 +7601,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -7627,7 +7630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -7656,7 +7659,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7685,7 +7688,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -7714,7 +7717,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -7743,7 +7746,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -7772,7 +7775,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -7801,7 +7804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -7830,7 +7833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -7859,7 +7862,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -7888,7 +7891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -7917,7 +7920,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -7946,7 +7949,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -7975,7 +7978,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -8004,7 +8007,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -8033,7 +8036,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -8062,7 +8065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>126</v>
       </c>
@@ -8091,7 +8094,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -8120,7 +8123,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>126</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -8178,7 +8181,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>140</v>
       </c>
@@ -8207,7 +8210,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>140</v>
       </c>
@@ -8236,7 +8239,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>140</v>
       </c>
@@ -8265,7 +8268,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -8294,7 +8297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>140</v>
       </c>
@@ -8323,7 +8326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -8352,7 +8355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>166</v>
       </c>
@@ -8381,7 +8384,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -8410,7 +8413,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -8439,7 +8442,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>166</v>
       </c>
@@ -8468,7 +8471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>183</v>
       </c>
@@ -8497,7 +8500,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>188</v>
       </c>
@@ -8526,7 +8529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -8555,7 +8558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -8584,7 +8587,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>195</v>
       </c>
@@ -8613,7 +8616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>195</v>
       </c>
@@ -8642,7 +8645,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>195</v>
       </c>
@@ -8671,7 +8674,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>195</v>
       </c>
@@ -8700,7 +8703,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -8729,7 +8732,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>195</v>
       </c>
@@ -8758,7 +8761,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>195</v>
       </c>
@@ -8787,7 +8790,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>217</v>
       </c>
@@ -8816,7 +8819,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -8845,7 +8848,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>223</v>
       </c>
@@ -8874,7 +8877,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>223</v>
       </c>
@@ -8903,7 +8906,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>233</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>233</v>
       </c>
@@ -8961,7 +8964,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>233</v>
       </c>
@@ -8990,7 +8993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>246</v>
       </c>
@@ -9019,7 +9022,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>246</v>
       </c>
@@ -9048,7 +9051,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>251</v>
       </c>
@@ -9077,7 +9080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>251</v>
       </c>
@@ -9106,7 +9109,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>251</v>
       </c>
@@ -9135,7 +9138,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>251</v>
       </c>
@@ -9164,7 +9167,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>251</v>
       </c>
@@ -9193,7 +9196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>251</v>
       </c>
@@ -9222,7 +9225,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>268</v>
       </c>
@@ -9251,7 +9254,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>268</v>
       </c>
@@ -9280,7 +9283,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>268</v>
       </c>
@@ -9309,7 +9312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>268</v>
       </c>
@@ -9338,7 +9341,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>268</v>
       </c>
@@ -9367,7 +9370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>283</v>
       </c>
@@ -9396,7 +9399,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>286</v>
       </c>
@@ -9425,7 +9428,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>286</v>
       </c>
@@ -9454,7 +9457,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>286</v>
       </c>
@@ -9483,7 +9486,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>302</v>
       </c>
@@ -9512,7 +9515,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>302</v>
       </c>
@@ -9541,7 +9544,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>302</v>
       </c>
@@ -9570,7 +9573,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>302</v>
       </c>
@@ -9599,7 +9602,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>302</v>
       </c>
@@ -9628,7 +9631,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>302</v>
       </c>
@@ -9657,7 +9660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>302</v>
       </c>
@@ -9686,7 +9689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>320</v>
       </c>
@@ -9715,7 +9718,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>320</v>
       </c>
@@ -9744,7 +9747,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>320</v>
       </c>
@@ -9773,7 +9776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>320</v>
       </c>
@@ -9802,7 +9805,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>320</v>
       </c>
@@ -9831,7 +9834,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>320</v>
       </c>
@@ -9860,7 +9863,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>320</v>
       </c>
@@ -9889,7 +9892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>320</v>
       </c>
@@ -9918,7 +9921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>320</v>
       </c>
@@ -9947,7 +9950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>343</v>
       </c>
@@ -9976,7 +9979,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>343</v>
       </c>
@@ -10005,7 +10008,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>271</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>271</v>
       </c>
@@ -10063,7 +10066,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>271</v>
       </c>
@@ -10092,7 +10095,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>271</v>
       </c>
@@ -10121,7 +10124,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>271</v>
       </c>
@@ -10150,7 +10153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>366</v>
       </c>
@@ -10179,7 +10182,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>366</v>
       </c>
@@ -10208,7 +10211,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>366</v>
       </c>
@@ -10237,7 +10240,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>366</v>
       </c>
@@ -10266,7 +10269,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>366</v>
       </c>
@@ -10295,7 +10298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>379</v>
       </c>
@@ -10324,7 +10327,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>379</v>
       </c>
@@ -10353,7 +10356,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>379</v>
       </c>
@@ -10382,7 +10385,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>379</v>
       </c>
@@ -10411,7 +10414,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>379</v>
       </c>
@@ -10440,7 +10443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>379</v>
       </c>
@@ -10469,7 +10472,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>397</v>
       </c>
@@ -10498,7 +10501,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>397</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>397</v>
       </c>
@@ -10556,7 +10559,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>406</v>
       </c>
@@ -10585,7 +10588,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>406</v>
       </c>
@@ -10614,7 +10617,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>406</v>
       </c>
@@ -10643,7 +10646,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>406</v>
       </c>
@@ -10672,7 +10675,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>406</v>
       </c>
@@ -10701,7 +10704,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>406</v>
       </c>
@@ -10730,7 +10733,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>406</v>
       </c>
@@ -10759,7 +10762,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>406</v>
       </c>
@@ -10788,7 +10791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>406</v>
       </c>
@@ -10817,7 +10820,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>432</v>
       </c>
@@ -10846,7 +10849,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>435</v>
       </c>
@@ -10875,7 +10878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>435</v>
       </c>
@@ -10904,7 +10907,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>435</v>
       </c>
@@ -10933,7 +10936,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>435</v>
       </c>
@@ -10962,7 +10965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>435</v>
       </c>
@@ -10991,7 +10994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>447</v>
       </c>
@@ -11020,7 +11023,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>447</v>
       </c>
@@ -11049,7 +11052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>455</v>
       </c>
@@ -11078,7 +11081,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>455</v>
       </c>
@@ -11107,7 +11110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>455</v>
       </c>
@@ -11136,7 +11139,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>455</v>
       </c>
@@ -11165,7 +11168,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>455</v>
       </c>
@@ -11194,7 +11197,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>455</v>
       </c>
@@ -11223,7 +11226,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>455</v>
       </c>
@@ -11252,7 +11255,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>455</v>
       </c>
@@ -11281,7 +11284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>455</v>
       </c>
@@ -11310,7 +11313,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>455</v>
       </c>
@@ -11339,7 +11342,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>39</v>
       </c>
@@ -11368,7 +11371,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>39</v>
       </c>
@@ -11397,7 +11400,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>484</v>
       </c>
@@ -11426,7 +11429,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>484</v>
       </c>
@@ -11455,7 +11458,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>484</v>
       </c>
@@ -11484,7 +11487,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>484</v>
       </c>
@@ -11513,7 +11516,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>484</v>
       </c>
@@ -11542,7 +11545,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>484</v>
       </c>
@@ -11571,7 +11574,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>484</v>
       </c>
@@ -11600,7 +11603,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>484</v>
       </c>
@@ -11629,7 +11632,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>484</v>
       </c>
@@ -11658,7 +11661,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>484</v>
       </c>
@@ -11687,7 +11690,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>512</v>
       </c>
@@ -11716,7 +11719,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>512</v>
       </c>
@@ -11745,7 +11748,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>512</v>
       </c>
@@ -11774,7 +11777,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>512</v>
       </c>
@@ -11803,7 +11806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>512</v>
       </c>
@@ -11832,7 +11835,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>512</v>
       </c>
@@ -11861,7 +11864,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>527</v>
       </c>
@@ -11890,7 +11893,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>530</v>
       </c>
@@ -11919,7 +11922,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>530</v>
       </c>
@@ -11948,7 +11951,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>530</v>
       </c>
@@ -11977,7 +11980,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>530</v>
       </c>
@@ -12006,7 +12009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>530</v>
       </c>
@@ -12035,7 +12038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>530</v>
       </c>
@@ -12064,7 +12067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>530</v>
       </c>
@@ -12093,7 +12096,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>530</v>
       </c>
@@ -12122,7 +12125,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>203</v>
       </c>
@@ -12151,7 +12154,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>203</v>
       </c>
@@ -12180,7 +12183,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>203</v>
       </c>
@@ -12209,7 +12212,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -12238,7 +12241,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -12267,7 +12270,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>203</v>
       </c>
@@ -12296,7 +12299,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>203</v>
       </c>
@@ -12325,7 +12328,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>203</v>
       </c>
@@ -12354,7 +12357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>203</v>
       </c>
@@ -12383,7 +12386,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>203</v>
       </c>
@@ -12412,7 +12415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>577</v>
       </c>
@@ -12441,7 +12444,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>577</v>
       </c>
@@ -12470,7 +12473,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>577</v>
       </c>
@@ -12499,7 +12502,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>577</v>
       </c>
@@ -12528,7 +12531,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>577</v>
       </c>
@@ -12557,7 +12560,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>588</v>
       </c>
@@ -12586,7 +12589,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>588</v>
       </c>
@@ -12615,7 +12618,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>588</v>
       </c>
@@ -12644,7 +12647,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>588</v>
       </c>
@@ -12673,7 +12676,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>588</v>
       </c>
@@ -12702,7 +12705,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>607</v>
       </c>
@@ -12731,7 +12734,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>607</v>
       </c>
@@ -12760,7 +12763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>607</v>
       </c>
@@ -12789,7 +12792,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>607</v>
       </c>
@@ -12818,7 +12821,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>607</v>
       </c>
@@ -12847,7 +12850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>358</v>
       </c>
@@ -12876,7 +12879,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>358</v>
       </c>
@@ -12905,7 +12908,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>358</v>
       </c>
@@ -12934,7 +12937,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>358</v>
       </c>
@@ -12963,7 +12966,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>633</v>
       </c>
@@ -12992,7 +12995,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>633</v>
       </c>
@@ -13021,7 +13024,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>633</v>
       </c>
@@ -13050,7 +13053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>633</v>
       </c>
@@ -13079,7 +13082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>633</v>
       </c>
@@ -13108,7 +13111,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>633</v>
       </c>
@@ -13137,7 +13140,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>647</v>
       </c>
@@ -13166,7 +13169,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>650</v>
       </c>
@@ -13195,7 +13198,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>650</v>
       </c>
@@ -13224,7 +13227,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>650</v>
       </c>
@@ -13253,7 +13256,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>650</v>
       </c>
@@ -13282,7 +13285,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>650</v>
       </c>
@@ -13311,7 +13314,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>650</v>
       </c>
@@ -13340,7 +13343,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>650</v>
       </c>
@@ -13369,7 +13372,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>664</v>
       </c>
@@ -13398,7 +13401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>664</v>
       </c>
@@ -13427,7 +13430,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>664</v>
       </c>
@@ -13456,7 +13459,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>664</v>
       </c>
@@ -13485,7 +13488,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>664</v>
       </c>
@@ -13514,7 +13517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>664</v>
       </c>
@@ -13543,7 +13546,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>676</v>
       </c>
@@ -13572,7 +13575,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>676</v>
       </c>
@@ -13601,7 +13604,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>676</v>
       </c>
@@ -13630,7 +13633,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>676</v>
       </c>
@@ -13659,7 +13662,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>676</v>
       </c>
@@ -13688,7 +13691,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>676</v>
       </c>
@@ -13717,7 +13720,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>676</v>
       </c>
@@ -13746,7 +13749,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>676</v>
       </c>
@@ -13775,7 +13778,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>676</v>
       </c>
@@ -13804,7 +13807,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>676</v>
       </c>
@@ -13833,7 +13836,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>676</v>
       </c>
@@ -13862,7 +13865,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>676</v>
       </c>
@@ -13891,7 +13894,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>707</v>
       </c>
@@ -13920,7 +13923,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>707</v>
       </c>
@@ -13949,7 +13952,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>707</v>
       </c>
@@ -13978,7 +13981,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>707</v>
       </c>
@@ -14007,7 +14010,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>707</v>
       </c>
@@ -14036,7 +14039,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>707</v>
       </c>
@@ -14065,7 +14068,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>707</v>
       </c>
@@ -14094,7 +14097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>707</v>
       </c>
@@ -14123,7 +14126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>707</v>
       </c>
@@ -14152,7 +14155,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>707</v>
       </c>
@@ -14181,7 +14184,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>707</v>
       </c>
@@ -14210,7 +14213,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>707</v>
       </c>
@@ -14239,7 +14242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>300</v>
       </c>
@@ -14268,7 +14271,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>300</v>
       </c>
@@ -14297,7 +14300,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>300</v>
       </c>
@@ -14326,7 +14329,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>300</v>
       </c>
@@ -14355,7 +14358,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>300</v>
       </c>
@@ -14384,7 +14387,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>300</v>
       </c>
@@ -14413,7 +14416,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>300</v>
       </c>
@@ -14442,7 +14445,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>300</v>
       </c>
@@ -14471,7 +14474,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>300</v>
       </c>
@@ -14500,7 +14503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>300</v>
       </c>
@@ -14529,7 +14532,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>300</v>
       </c>
@@ -14558,7 +14561,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>300</v>
       </c>
@@ -14587,7 +14590,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>761</v>
       </c>
@@ -14616,7 +14619,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>761</v>
       </c>
@@ -14645,7 +14648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>766</v>
       </c>
@@ -14674,7 +14677,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>766</v>
       </c>
@@ -14703,7 +14706,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>766</v>
       </c>
@@ -14732,7 +14735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>776</v>
       </c>
@@ -14761,7 +14764,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>776</v>
       </c>
@@ -14790,7 +14793,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>776</v>
       </c>
@@ -14819,7 +14822,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>776</v>
       </c>
@@ -14848,7 +14851,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>776</v>
       </c>
@@ -14877,7 +14880,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>776</v>
       </c>
@@ -14906,7 +14909,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>776</v>
       </c>
@@ -14935,7 +14938,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>776</v>
       </c>
@@ -14964,7 +14967,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>685</v>
       </c>
@@ -14993,7 +14996,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>685</v>
       </c>
@@ -15022,7 +15025,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>685</v>
       </c>
@@ -15051,7 +15054,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>685</v>
       </c>
@@ -15080,7 +15083,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>685</v>
       </c>
@@ -15109,7 +15112,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>685</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>685</v>
       </c>
@@ -15167,7 +15170,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>685</v>
       </c>
@@ -15196,7 +15199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>685</v>
       </c>
@@ -15225,7 +15228,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>815</v>
       </c>
@@ -15254,7 +15257,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>815</v>
       </c>
@@ -15283,7 +15286,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>815</v>
       </c>
@@ -15312,7 +15315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>815</v>
       </c>
@@ -15341,7 +15344,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>815</v>
       </c>
@@ -15370,7 +15373,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>815</v>
       </c>
@@ -15399,7 +15402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>815</v>
       </c>
@@ -15428,7 +15431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>815</v>
       </c>
@@ -15457,7 +15460,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>815</v>
       </c>
@@ -15486,7 +15489,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>815</v>
       </c>
@@ -15515,7 +15518,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>835</v>
       </c>
@@ -15544,7 +15547,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>835</v>
       </c>
@@ -15573,7 +15576,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>835</v>
       </c>
@@ -15602,7 +15605,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>835</v>
       </c>
@@ -15631,7 +15634,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>835</v>
       </c>
@@ -15660,7 +15663,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>835</v>
       </c>
@@ -15689,7 +15692,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>835</v>
       </c>
@@ -15718,7 +15721,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>835</v>
       </c>
@@ -15747,7 +15750,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>835</v>
       </c>
@@ -15776,7 +15779,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>835</v>
       </c>
@@ -15805,7 +15808,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>835</v>
       </c>
@@ -15834,7 +15837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>835</v>
       </c>
@@ -15863,7 +15866,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>835</v>
       </c>
@@ -15892,7 +15895,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>835</v>
       </c>
@@ -15914,14 +15917,14 @@
       <c r="G294" t="s">
         <v>271</v>
       </c>
-      <c r="H294" t="s">
-        <v>366</v>
+      <c r="H294" s="1">
+        <v>46122</v>
       </c>
       <c r="I294" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>869</v>
       </c>
@@ -15950,7 +15953,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>869</v>
       </c>
@@ -15979,7 +15982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>874</v>
       </c>
@@ -16008,7 +16011,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>874</v>
       </c>
@@ -16037,7 +16040,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>874</v>
       </c>
@@ -16066,7 +16069,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>874</v>
       </c>
@@ -16095,7 +16098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>874</v>
       </c>
@@ -16124,7 +16127,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>874</v>
       </c>
@@ -16153,7 +16156,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>874</v>
       </c>
@@ -16182,7 +16185,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>874</v>
       </c>
@@ -16211,7 +16214,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>874</v>
       </c>
@@ -16240,7 +16243,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>896</v>
       </c>
@@ -16269,7 +16272,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>896</v>
       </c>
@@ -16298,7 +16301,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>896</v>
       </c>
@@ -16327,7 +16330,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>896</v>
       </c>
@@ -16356,7 +16359,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>896</v>
       </c>
@@ -16385,7 +16388,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>896</v>
       </c>
@@ -16414,7 +16417,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>896</v>
       </c>
@@ -16443,7 +16446,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>895</v>
       </c>
@@ -16472,7 +16475,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>895</v>
       </c>
@@ -16501,7 +16504,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>895</v>
       </c>
@@ -16530,7 +16533,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>895</v>
       </c>
@@ -16559,7 +16562,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>895</v>
       </c>
@@ -16588,7 +16591,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>895</v>
       </c>
@@ -16617,7 +16620,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>895</v>
       </c>
@@ -16646,7 +16649,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>895</v>
       </c>
@@ -16675,7 +16678,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>895</v>
       </c>
@@ -16704,7 +16707,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>696</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>696</v>
       </c>
@@ -16762,7 +16765,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>696</v>
       </c>
@@ -16791,7 +16794,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>696</v>
       </c>
@@ -16820,7 +16823,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>696</v>
       </c>
@@ -16849,7 +16852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>696</v>
       </c>
@@ -16878,7 +16881,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>944</v>
       </c>
@@ -16900,14 +16903,14 @@
       <c r="G328" t="s">
         <v>183</v>
       </c>
-      <c r="H328" t="s">
-        <v>366</v>
+      <c r="H328" s="1">
+        <v>46122</v>
       </c>
       <c r="I328" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>944</v>
       </c>
@@ -16936,7 +16939,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>944</v>
       </c>
@@ -16965,7 +16968,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>944</v>
       </c>
@@ -16994,7 +16997,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>944</v>
       </c>
@@ -17023,7 +17026,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>944</v>
       </c>
@@ -17052,7 +17055,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>944</v>
       </c>
@@ -17081,7 +17084,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>944</v>
       </c>
@@ -17110,7 +17113,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>944</v>
       </c>
@@ -17139,7 +17142,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>944</v>
       </c>
@@ -17168,7 +17171,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>944</v>
       </c>
@@ -17197,7 +17200,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>944</v>
       </c>
@@ -17226,7 +17229,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>944</v>
       </c>
@@ -17255,7 +17258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>944</v>
       </c>
@@ -17284,7 +17287,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>944</v>
       </c>
@@ -17313,7 +17316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>944</v>
       </c>
@@ -17342,7 +17345,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>944</v>
       </c>
@@ -17371,7 +17374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>978</v>
       </c>
@@ -17400,7 +17403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>982</v>
       </c>
@@ -17429,7 +17432,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>982</v>
       </c>
@@ -17458,7 +17461,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>982</v>
       </c>
@@ -17487,7 +17490,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>982</v>
       </c>
@@ -17516,7 +17519,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>982</v>
       </c>
@@ -17545,7 +17548,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>982</v>
       </c>
@@ -17574,7 +17577,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>982</v>
       </c>
@@ -17603,7 +17606,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>996</v>
       </c>
@@ -17632,7 +17635,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>996</v>
       </c>
@@ -17661,7 +17664,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>996</v>
       </c>
@@ -17690,7 +17693,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>996</v>
       </c>
@@ -17719,7 +17722,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>996</v>
       </c>
@@ -17748,7 +17751,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>996</v>
       </c>
@@ -17777,7 +17780,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1011</v>
       </c>
@@ -17806,7 +17809,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1011</v>
       </c>
@@ -17835,7 +17838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1011</v>
       </c>
@@ -17864,7 +17867,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1011</v>
       </c>
@@ -17893,7 +17896,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1011</v>
       </c>
@@ -17922,7 +17925,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1011</v>
       </c>
@@ -17951,7 +17954,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1011</v>
       </c>
@@ -17980,7 +17983,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1011</v>
       </c>
@@ -18009,7 +18012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1011</v>
       </c>
@@ -18038,7 +18041,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1033</v>
       </c>
@@ -18060,14 +18063,14 @@
       <c r="G368" t="s">
         <v>45</v>
       </c>
-      <c r="H368" t="s">
-        <v>366</v>
+      <c r="H368" s="1">
+        <v>46122</v>
       </c>
       <c r="I368" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1033</v>
       </c>
@@ -18096,7 +18099,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1033</v>
       </c>
@@ -18125,7 +18128,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1033</v>
       </c>
@@ -18154,7 +18157,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1033</v>
       </c>
@@ -18183,7 +18186,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1033</v>
       </c>
@@ -18212,7 +18215,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1033</v>
       </c>
@@ -18241,7 +18244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1033</v>
       </c>
@@ -18270,7 +18273,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1033</v>
       </c>
@@ -18292,14 +18295,14 @@
       <c r="G376" t="s">
         <v>366</v>
       </c>
-      <c r="H376" t="s">
-        <v>316</v>
+      <c r="H376" s="1">
+        <v>46122</v>
       </c>
       <c r="I376" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1048</v>
       </c>
@@ -18328,7 +18331,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1048</v>
       </c>
@@ -18357,7 +18360,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1048</v>
       </c>
@@ -18386,7 +18389,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1048</v>
       </c>
@@ -18415,7 +18418,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1048</v>
       </c>
@@ -18444,7 +18447,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1048</v>
       </c>
@@ -18473,7 +18476,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1048</v>
       </c>
@@ -18502,7 +18505,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1048</v>
       </c>
@@ -18531,7 +18534,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1048</v>
       </c>
@@ -18560,7 +18563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1048</v>
       </c>
@@ -18589,7 +18592,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1048</v>
       </c>
@@ -18618,7 +18621,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1048</v>
       </c>
@@ -18647,7 +18650,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1048</v>
       </c>
@@ -18676,7 +18679,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1075</v>
       </c>
@@ -18705,7 +18708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1077</v>
       </c>
@@ -18734,7 +18737,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>548</v>
       </c>
@@ -18763,7 +18766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>548</v>
       </c>
@@ -18792,7 +18795,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -18821,7 +18824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>16</v>
       </c>
@@ -18850,7 +18853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>16</v>
       </c>
@@ -18879,7 +18882,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>16</v>
       </c>
@@ -18908,7 +18911,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>16</v>
       </c>
@@ -18937,7 +18940,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>16</v>
       </c>
@@ -18966,7 +18969,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>16</v>
       </c>
@@ -18995,7 +18998,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>16</v>
       </c>
@@ -19024,7 +19027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>16</v>
       </c>
@@ -19053,7 +19056,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>16</v>
       </c>
@@ -19082,7 +19085,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>16</v>
       </c>
@@ -19111,7 +19114,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>16</v>
       </c>
@@ -19140,7 +19143,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>16</v>
       </c>
@@ -19169,7 +19172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>16</v>
       </c>
@@ -19198,7 +19201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>16</v>
       </c>
@@ -19227,7 +19230,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>16</v>
       </c>
@@ -19256,7 +19259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -19285,7 +19288,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>16</v>
       </c>
@@ -19314,7 +19317,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>16</v>
       </c>
@@ -19343,7 +19346,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -19372,7 +19375,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>16</v>
       </c>
@@ -19401,7 +19404,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>16</v>
       </c>
@@ -19430,7 +19433,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>16</v>
       </c>
@@ -19459,7 +19462,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>16</v>
       </c>
@@ -19488,7 +19491,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -19517,7 +19520,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -19546,7 +19549,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>16</v>
       </c>
@@ -19575,7 +19578,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>16</v>
       </c>
@@ -19604,7 +19607,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>16</v>
       </c>
@@ -19633,7 +19636,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -19662,7 +19665,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -19691,7 +19694,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -19720,7 +19723,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -19749,7 +19752,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -19778,7 +19781,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -19807,7 +19810,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -19836,7 +19839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -19865,7 +19868,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -19894,7 +19897,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -19923,7 +19926,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -19952,7 +19955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -19981,7 +19984,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -20010,7 +20013,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -20039,7 +20042,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -20068,7 +20071,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -20097,7 +20100,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -20126,7 +20129,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -20155,7 +20158,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -20184,7 +20187,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -20213,7 +20216,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -20242,7 +20245,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -20271,7 +20274,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -20300,7 +20303,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -20329,7 +20332,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -20358,7 +20361,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -20387,7 +20390,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20416,7 +20419,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20445,7 +20448,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20474,7 +20477,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20503,7 +20506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20532,7 +20535,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20561,7 +20564,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20590,7 +20593,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20619,7 +20622,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20648,7 +20651,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20677,7 +20680,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20706,7 +20709,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20735,7 +20738,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20764,7 +20767,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20793,7 +20796,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20822,7 +20825,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20851,7 +20854,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20880,7 +20883,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20909,7 +20912,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -20938,7 +20941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -20967,7 +20970,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -20996,7 +20999,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21025,7 +21028,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21054,7 +21057,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21083,7 +21086,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21112,7 +21115,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21141,7 +21144,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21170,7 +21173,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21199,7 +21202,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21228,7 +21231,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21257,7 +21260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21286,7 +21289,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21315,7 +21318,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21344,7 +21347,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21373,7 +21376,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21402,7 +21405,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21431,7 +21434,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21460,7 +21463,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21489,7 +21492,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21518,7 +21521,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21547,7 +21550,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21576,7 +21579,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21605,7 +21608,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21634,7 +21637,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21663,7 +21666,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21692,7 +21695,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21721,7 +21724,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21750,7 +21753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21779,7 +21782,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21808,7 +21811,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21837,7 +21840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21866,7 +21869,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21895,7 +21898,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21924,7 +21927,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -21953,7 +21956,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -21982,7 +21985,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22011,7 +22014,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22040,7 +22043,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22069,7 +22072,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22098,7 +22101,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22127,7 +22130,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22156,7 +22159,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22185,7 +22188,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22214,7 +22217,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22243,7 +22246,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22272,7 +22275,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22301,7 +22304,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22330,7 +22333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22359,7 +22362,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22388,7 +22391,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22417,7 +22420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22446,7 +22449,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22475,7 +22478,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22504,7 +22507,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22533,7 +22536,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22562,7 +22565,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22591,7 +22594,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22620,7 +22623,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22649,7 +22652,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22678,7 +22681,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22707,7 +22710,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22736,7 +22739,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22765,7 +22768,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22794,7 +22797,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22823,7 +22826,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22852,7 +22855,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22881,7 +22884,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22910,7 +22913,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -22939,7 +22942,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -22968,7 +22971,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -22997,7 +23000,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23026,7 +23029,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23055,7 +23058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23084,7 +23087,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23113,7 +23116,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23142,7 +23145,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23171,7 +23174,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23200,7 +23203,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23229,7 +23232,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23258,7 +23261,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23287,7 +23290,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23316,7 +23319,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23345,7 +23348,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23374,7 +23377,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23403,7 +23406,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23432,7 +23435,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23461,7 +23464,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23490,7 +23493,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23519,7 +23522,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23548,7 +23551,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23577,7 +23580,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23606,7 +23609,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23635,7 +23638,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23664,7 +23667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23693,7 +23696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23722,7 +23725,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23751,7 +23754,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23780,7 +23783,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23809,7 +23812,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23838,7 +23841,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23867,7 +23870,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23896,7 +23899,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23925,7 +23928,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -23954,7 +23957,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -23983,7 +23986,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -24012,7 +24015,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -24041,7 +24044,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -24070,7 +24073,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -24099,7 +24102,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24128,7 +24131,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24157,7 +24160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24186,7 +24189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24215,7 +24218,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24244,7 +24247,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24273,7 +24276,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24302,7 +24305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24331,7 +24334,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24360,7 +24363,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24389,7 +24392,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24418,7 +24421,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24447,7 +24450,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24476,7 +24479,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24505,7 +24508,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24534,7 +24537,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24563,7 +24566,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24592,7 +24595,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24621,7 +24624,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24650,7 +24653,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24679,7 +24682,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24708,7 +24711,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24737,7 +24740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24766,7 +24769,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24795,7 +24798,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24824,7 +24827,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24853,7 +24856,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24882,7 +24885,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24911,7 +24914,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -24940,7 +24943,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -24969,7 +24972,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -24998,7 +25001,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -25027,7 +25030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -25056,7 +25059,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -25085,7 +25088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -25114,7 +25117,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25143,7 +25146,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25172,7 +25175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25201,7 +25204,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25230,7 +25233,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25259,7 +25262,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25288,7 +25291,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25317,7 +25320,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25346,7 +25349,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25375,7 +25378,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25404,7 +25407,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25433,7 +25436,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25462,7 +25465,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25491,7 +25494,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25520,7 +25523,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25549,7 +25552,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25578,7 +25581,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25607,7 +25610,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25636,7 +25639,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25665,7 +25668,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25694,7 +25697,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25723,7 +25726,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25752,7 +25755,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25781,7 +25784,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25810,7 +25813,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25839,7 +25842,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25868,7 +25871,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25897,7 +25900,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25926,7 +25929,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -25955,7 +25958,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -25984,7 +25987,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -26013,7 +26016,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -26042,7 +26045,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -26071,7 +26074,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -26100,7 +26103,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26129,7 +26132,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26158,7 +26161,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26187,7 +26190,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26216,7 +26219,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26245,7 +26248,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26274,7 +26277,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26303,7 +26306,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26332,7 +26335,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26361,7 +26364,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26390,7 +26393,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26419,7 +26422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26448,7 +26451,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26477,7 +26480,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26506,7 +26509,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26535,7 +26538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26564,7 +26567,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26593,7 +26596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26622,7 +26625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26651,7 +26654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26680,7 +26683,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26709,7 +26712,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26738,7 +26741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26767,7 +26770,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26796,7 +26799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26825,7 +26828,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26854,7 +26857,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26883,7 +26886,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26912,7 +26915,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -26941,7 +26944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -26970,7 +26973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -26999,7 +27002,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -27028,7 +27031,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -27057,7 +27060,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -27086,7 +27089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27115,7 +27118,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27144,7 +27147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27173,7 +27176,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27202,7 +27205,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27231,7 +27234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27260,7 +27263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27289,7 +27292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27318,7 +27321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27347,7 +27350,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27376,7 +27379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27405,7 +27408,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27434,7 +27437,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27463,7 +27466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27492,7 +27495,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27521,7 +27524,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27550,7 +27553,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27579,7 +27582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27608,7 +27611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27637,7 +27640,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27666,7 +27669,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27695,7 +27698,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27724,7 +27727,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27753,7 +27756,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27782,7 +27785,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27811,7 +27814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27840,7 +27843,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27869,7 +27872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27898,7 +27901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27927,7 +27930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -27956,7 +27959,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -27985,7 +27988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -28014,7 +28017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -28043,7 +28046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -28072,7 +28075,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -28101,7 +28104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28130,7 +28133,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28159,7 +28162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28188,7 +28191,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28217,7 +28220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28246,7 +28249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28275,7 +28278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28304,7 +28307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28333,7 +28336,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28362,7 +28365,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28391,7 +28394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28420,7 +28423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28449,7 +28452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28478,7 +28481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28507,7 +28510,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28536,7 +28539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28565,7 +28568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28594,7 +28597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28623,7 +28626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28652,7 +28655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28681,7 +28684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28710,7 +28713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28739,7 +28742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28768,7 +28771,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28797,7 +28800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28826,7 +28829,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28855,7 +28858,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28884,7 +28887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28913,7 +28916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -28942,7 +28945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -28971,7 +28974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -29000,7 +29003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -29029,7 +29032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -29058,7 +29061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -29087,7 +29090,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29116,7 +29119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29145,7 +29148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29174,7 +29177,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29203,7 +29206,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29232,7 +29235,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29261,7 +29264,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29290,7 +29293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29319,7 +29322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29348,7 +29351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29377,7 +29380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29406,7 +29409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29435,7 +29438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29464,7 +29467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29493,7 +29496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29522,7 +29525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29551,7 +29554,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29580,7 +29583,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29609,7 +29612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29638,7 +29641,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29667,7 +29670,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29696,7 +29699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29725,7 +29728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29754,7 +29757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29783,7 +29786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29812,7 +29815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29841,7 +29844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29870,7 +29873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29899,7 +29902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29928,7 +29931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -29957,7 +29960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -29986,7 +29989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -30015,7 +30018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -30044,7 +30047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -30073,7 +30076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -30102,7 +30105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30131,7 +30134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30160,7 +30163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30189,7 +30192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30218,7 +30221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30247,7 +30250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30276,7 +30279,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30305,7 +30308,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30334,7 +30337,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30363,7 +30366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30392,7 +30395,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30421,7 +30424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30450,7 +30453,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30479,7 +30482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30508,7 +30511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30537,7 +30540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30566,7 +30569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30595,7 +30598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30624,7 +30627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30653,7 +30656,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30682,7 +30685,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30711,7 +30714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30740,7 +30743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30769,7 +30772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30798,7 +30801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30827,7 +30830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30856,7 +30859,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30885,7 +30888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30914,7 +30917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -30943,7 +30946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -30972,7 +30975,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -31001,7 +31004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -31030,7 +31033,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -31059,7 +31062,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -31088,7 +31091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31117,7 +31120,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31146,7 +31149,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31175,7 +31178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31204,7 +31207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31233,7 +31236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31262,7 +31265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31291,7 +31294,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31320,7 +31323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31349,7 +31352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31378,7 +31381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31407,7 +31410,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31436,7 +31439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31465,7 +31468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31494,7 +31497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31523,7 +31526,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31552,7 +31555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31581,7 +31584,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31610,7 +31613,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31639,7 +31642,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31668,7 +31671,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31697,7 +31700,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31726,7 +31729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31755,7 +31758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31784,7 +31787,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31813,7 +31816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31842,7 +31845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31871,7 +31874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31900,7 +31903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31929,7 +31932,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -31958,7 +31961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -31987,7 +31990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -32016,7 +32019,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -32045,7 +32048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -32074,7 +32077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -32103,7 +32106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32132,7 +32135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32161,7 +32164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32190,7 +32193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32219,7 +32222,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32248,7 +32251,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32277,7 +32280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>16</v>
       </c>
@@ -32306,7 +32309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>16</v>
       </c>
@@ -32335,7 +32338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>16</v>
       </c>
@@ -32364,7 +32367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>16</v>
       </c>
@@ -32393,7 +32396,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>16</v>
       </c>
@@ -32422,7 +32425,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>16</v>
       </c>
@@ -32451,7 +32454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>16</v>
       </c>
@@ -32480,7 +32483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>16</v>
       </c>
@@ -32509,7 +32512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>16</v>
       </c>
@@ -32538,7 +32541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>16</v>
       </c>
@@ -32567,7 +32570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>16</v>
       </c>
@@ -32596,7 +32599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>16</v>
       </c>
@@ -32625,7 +32628,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>16</v>
       </c>
@@ -32654,7 +32657,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>16</v>
       </c>
@@ -32683,7 +32686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>16</v>
       </c>
@@ -32712,7 +32715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>16</v>
       </c>
@@ -32741,7 +32744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>16</v>
       </c>
@@ -32770,7 +32773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>16</v>
       </c>
@@ -32799,7 +32802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>16</v>
       </c>
@@ -32828,7 +32831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>16</v>
       </c>
@@ -32857,7 +32860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>16</v>
       </c>
@@ -32886,7 +32889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>16</v>
       </c>
@@ -32915,7 +32918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>16</v>
       </c>
@@ -32944,7 +32947,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>16</v>
       </c>
@@ -32973,7 +32976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>16</v>
       </c>
@@ -33002,7 +33005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>16</v>
       </c>
@@ -33031,7 +33034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>16</v>
       </c>
@@ -33060,7 +33063,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>16</v>
       </c>
@@ -33089,7 +33092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>16</v>
       </c>
@@ -33118,7 +33121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>16</v>
       </c>
@@ -33147,7 +33150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>16</v>
       </c>
@@ -33176,7 +33179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>16</v>
       </c>
@@ -33205,7 +33208,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>16</v>
       </c>
@@ -33234,7 +33237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>16</v>
       </c>
@@ -33263,7 +33266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>16</v>
       </c>
@@ -33292,7 +33295,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>47</v>
       </c>
@@ -33321,7 +33324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>140</v>
       </c>
@@ -33350,7 +33353,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>140</v>
       </c>
@@ -33379,7 +33382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>166</v>
       </c>
@@ -33408,7 +33411,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>166</v>
       </c>
@@ -33437,7 +33440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>2055</v>
       </c>
@@ -33466,7 +33469,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>183</v>
       </c>
@@ -33495,7 +33498,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>195</v>
       </c>
@@ -33524,7 +33527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>251</v>
       </c>
@@ -33553,7 +33556,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>283</v>
       </c>
@@ -33582,7 +33585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>271</v>
       </c>
@@ -33611,7 +33614,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>447</v>
       </c>
@@ -33640,7 +33643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>447</v>
       </c>
@@ -33669,7 +33672,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>455</v>
       </c>
@@ -33698,7 +33701,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>455</v>
       </c>
@@ -33727,7 +33730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>455</v>
       </c>
@@ -33756,7 +33759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>455</v>
       </c>
@@ -33785,7 +33788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>39</v>
       </c>
@@ -33814,7 +33817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>39</v>
       </c>
@@ -33843,7 +33846,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>39</v>
       </c>
@@ -33872,7 +33875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>39</v>
       </c>
@@ -33901,7 +33904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>530</v>
       </c>
@@ -33930,7 +33933,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>530</v>
       </c>
@@ -33959,7 +33962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>530</v>
       </c>
@@ -33988,7 +33991,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>203</v>
       </c>
@@ -34017,7 +34020,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>203</v>
       </c>
@@ -34046,7 +34049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>588</v>
       </c>
@@ -34075,7 +34078,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>607</v>
       </c>
@@ -34104,7 +34107,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>633</v>
       </c>
@@ -34133,7 +34136,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>650</v>
       </c>
@@ -34162,7 +34165,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>650</v>
       </c>
@@ -34191,7 +34194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>664</v>
       </c>
@@ -34220,7 +34223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>676</v>
       </c>
@@ -34249,7 +34252,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>676</v>
       </c>
@@ -34278,7 +34281,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>300</v>
       </c>
@@ -34307,7 +34310,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>300</v>
       </c>
@@ -34336,7 +34339,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>300</v>
       </c>
@@ -34365,7 +34368,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>300</v>
       </c>
@@ -34394,7 +34397,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>772</v>
       </c>
@@ -34423,7 +34426,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>776</v>
       </c>
@@ -34452,7 +34455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>685</v>
       </c>
@@ -34481,7 +34484,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>685</v>
       </c>
@@ -34510,7 +34513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>685</v>
       </c>
@@ -34539,7 +34542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>815</v>
       </c>
@@ -34568,7 +34571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>815</v>
       </c>
@@ -34597,7 +34600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>835</v>
       </c>
@@ -34626,7 +34629,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>835</v>
       </c>
@@ -34655,7 +34658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>835</v>
       </c>
@@ -34684,7 +34687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>874</v>
       </c>
@@ -34713,7 +34716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>896</v>
       </c>
@@ -34742,7 +34745,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>896</v>
       </c>
@@ -34771,7 +34774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>895</v>
       </c>
@@ -34800,7 +34803,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>895</v>
       </c>
@@ -34829,7 +34832,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>696</v>
       </c>
@@ -34858,7 +34861,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>944</v>
       </c>
@@ -34887,7 +34890,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>944</v>
       </c>
@@ -34916,7 +34919,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>944</v>
       </c>
@@ -34945,7 +34948,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>944</v>
       </c>
@@ -34974,7 +34977,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>996</v>
       </c>
@@ -35003,7 +35006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>1011</v>
       </c>
@@ -35032,7 +35035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>1048</v>
       </c>
@@ -35061,7 +35064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>16</v>
       </c>
@@ -35090,7 +35093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>16</v>
       </c>
@@ -35119,7 +35122,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>16</v>
       </c>
@@ -35148,7 +35151,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>16</v>
       </c>
@@ -35177,7 +35180,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>16</v>
       </c>
@@ -35206,7 +35209,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>16</v>
       </c>
@@ -35235,7 +35238,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>16</v>
       </c>
@@ -35264,7 +35267,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>16</v>
       </c>
@@ -35293,7 +35296,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>16</v>
       </c>
@@ -35322,7 +35325,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>16</v>
       </c>
@@ -35351,7 +35354,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>16</v>
       </c>
@@ -35380,7 +35383,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>16</v>
       </c>
@@ -35409,7 +35412,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>16</v>
       </c>
@@ -35438,7 +35441,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35467,7 +35470,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35496,7 +35499,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35525,7 +35528,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35554,7 +35557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35583,7 +35586,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35612,7 +35615,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35641,7 +35644,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35670,7 +35673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35699,7 +35702,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35728,7 +35731,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35757,7 +35760,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35786,7 +35789,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35815,7 +35818,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35844,7 +35847,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35873,7 +35876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35902,7 +35905,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35931,7 +35934,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -35960,7 +35963,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -35989,7 +35992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -36018,7 +36021,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -36047,7 +36050,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -36076,7 +36079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -36105,7 +36108,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36134,7 +36137,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36163,7 +36166,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36192,7 +36195,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36221,7 +36224,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36250,7 +36253,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36279,7 +36282,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36308,7 +36311,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36337,7 +36340,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36366,7 +36369,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36395,7 +36398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36424,7 +36427,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36453,7 +36456,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36482,7 +36485,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36511,7 +36514,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36540,7 +36543,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36569,7 +36572,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36598,7 +36601,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36627,7 +36630,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36656,7 +36659,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36685,7 +36688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36714,7 +36717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36743,7 +36746,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36772,7 +36775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36801,7 +36804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36830,7 +36833,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36859,7 +36862,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36888,7 +36891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36917,7 +36920,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -36946,7 +36949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -36975,7 +36978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -37004,7 +37007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -37033,7 +37036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -37062,7 +37065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -37091,7 +37094,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37120,7 +37123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37149,7 +37152,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37178,7 +37181,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37207,7 +37210,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37236,7 +37239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37265,7 +37268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37294,7 +37297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37323,7 +37326,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37352,7 +37355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37381,7 +37384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37410,7 +37413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37439,7 +37442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37468,7 +37471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37497,7 +37500,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37526,7 +37529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37555,7 +37558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37584,7 +37587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37613,7 +37616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37642,7 +37645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37671,7 +37674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37700,7 +37703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37729,7 +37732,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37758,7 +37761,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37787,7 +37790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37816,7 +37819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37845,7 +37848,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37874,7 +37877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37903,7 +37906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37932,7 +37935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -37961,7 +37964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -37990,7 +37993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -38019,7 +38022,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -38048,7 +38051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -38077,7 +38080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -38106,7 +38109,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38135,7 +38138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38164,7 +38167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38193,7 +38196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38223,9 +38226,10 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I6 A112:I903 A111:F111 H111:I111 A8:I40 A7:F7 H7 A42:I45 A41:F41 H41:I41 A47:I110 A46:F46 H46:I46 A905:I1063 A904:F904 H904" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I6 A112:I293 A111:F111 H111:I111 A8:I40 A7:F7 H7 A42:I45 A41:F41 H41:I41 A47:I110 A46:F46 H46:I46 A905:I1063 A904:F904 H904 A295:I327 A294:G294 I294 A329:I367 A328:G328 I328 A369:I375 A368:G368 I368 A377:I903 A376:G376 I376" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9519" uniqueCount="2332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9510" uniqueCount="2332">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7681,8 +7681,8 @@
       <c r="G10" s="1">
         <v>46113</v>
       </c>
-      <c r="H10" t="s">
-        <v>14</v>
+      <c r="H10" s="1">
+        <v>46122</v>
       </c>
       <c r="I10" t="s">
         <v>68</v>
@@ -7855,8 +7855,8 @@
       <c r="G16" s="1">
         <v>46114</v>
       </c>
-      <c r="H16" t="s">
-        <v>14</v>
+      <c r="H16" s="1">
+        <v>46122</v>
       </c>
       <c r="I16" t="s">
         <v>68</v>
@@ -7971,8 +7971,8 @@
       <c r="G20" s="1">
         <v>46115</v>
       </c>
-      <c r="H20" t="s">
-        <v>16</v>
+      <c r="H20" s="1">
+        <v>46122</v>
       </c>
       <c r="I20" t="s">
         <v>68</v>
@@ -8232,8 +8232,8 @@
       <c r="G29" s="1">
         <v>45833</v>
       </c>
-      <c r="H29" t="s">
-        <v>14</v>
+      <c r="H29" s="1">
+        <v>46122</v>
       </c>
       <c r="I29" t="s">
         <v>68</v>
@@ -8754,8 +8754,8 @@
       <c r="G47" t="s">
         <v>79</v>
       </c>
-      <c r="H47" t="s">
-        <v>16</v>
+      <c r="H47" s="1">
+        <v>46122</v>
       </c>
       <c r="I47" t="s">
         <v>68</v>
@@ -11132,8 +11132,8 @@
       <c r="G129" s="1">
         <v>46112</v>
       </c>
-      <c r="H129" t="s">
-        <v>14</v>
+      <c r="H129" s="1">
+        <v>46122</v>
       </c>
       <c r="I129" t="s">
         <v>68</v>
@@ -11306,8 +11306,8 @@
       <c r="G135" t="s">
         <v>39</v>
       </c>
-      <c r="H135" t="s">
-        <v>14</v>
+      <c r="H135" s="1">
+        <v>46122</v>
       </c>
       <c r="I135" t="s">
         <v>68</v>
@@ -18759,8 +18759,8 @@
       <c r="G392" t="s">
         <v>220</v>
       </c>
-      <c r="H392" t="s">
-        <v>14</v>
+      <c r="H392" s="1">
+        <v>46122</v>
       </c>
       <c r="I392" t="s">
         <v>68</v>
@@ -20702,8 +20702,8 @@
       <c r="G459" t="s">
         <v>287</v>
       </c>
-      <c r="H459" t="s">
-        <v>14</v>
+      <c r="H459" s="1">
+        <v>46122</v>
       </c>
       <c r="I459" t="s">
         <v>68</v>
@@ -38226,6 +38226,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:I1" numberStoredAsText="1"/>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9557" uniqueCount="2337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9556" uniqueCount="2337">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7411,9 +7411,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -7722,8 +7722,8 @@
       <c r="F11" t="s">
         <v>44</v>
       </c>
-      <c r="G11" t="s">
-        <v>70</v>
+      <c r="G11" s="1">
+        <v>46121</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
@@ -7732,7 +7732,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>113</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>128</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>128</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>162</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>165</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>165</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>165</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>165</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>165</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>165</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>193</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>193</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>193</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>203</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>203</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>203</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>203</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>203</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>203</v>
       </c>
@@ -8863,7 +8863,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>189</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>189</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>189</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>189</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>189</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>189</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>254</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>260</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>260</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>260</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>267</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>267</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>267</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>267</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>267</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>267</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>267</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>267</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>292</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>297</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>297</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>297</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>306</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>306</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>318</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>318</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>323</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>323</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>323</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>323</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>323</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>323</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>343</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>343</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>343</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>343</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>353</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>353</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>353</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>161</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>161</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>161</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>161</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>161</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>161</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>161</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -10255,7 +10255,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>137</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>137</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>137</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>137</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>137</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>137</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>137</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>407</v>
       </c>
@@ -10516,7 +10516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>407</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>415</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>415</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>415</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>415</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>415</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>415</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>431</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>431</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>431</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>431</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>431</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>444</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>444</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>444</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>444</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>444</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>444</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>462</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>462</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>462</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>471</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>471</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>471</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>471</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>471</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>471</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>471</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>471</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>471</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>495</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>498</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>498</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>498</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>498</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>498</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>509</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>509</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>516</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>516</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>516</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>516</v>
       </c>
@@ -11734,7 +11734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>516</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>516</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>516</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>516</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>516</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>516</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>124</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>124</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>124</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>550</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>550</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>550</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>550</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>550</v>
       </c>
@@ -12140,7 +12140,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>550</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>550</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>550</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>550</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>550</v>
       </c>
@@ -12285,7 +12285,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>578</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>578</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>578</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>578</v>
       </c>
@@ -12401,7 +12401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>578</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>578</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>591</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>594</v>
       </c>
@@ -12517,7 +12517,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>594</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>594</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>594</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>594</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>594</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>594</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>594</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>612</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>612</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>612</v>
       </c>
@@ -12807,7 +12807,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>612</v>
       </c>
@@ -12836,7 +12836,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>612</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>612</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>612</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>612</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>612</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>612</v>
       </c>
@@ -13010,7 +13010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>640</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>640</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>640</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>640</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>640</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>650</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>650</v>
       </c>
@@ -13213,7 +13213,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>650</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>650</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>650</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>669</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>669</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>669</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>669</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>669</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>679</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>679</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>679</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>679</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>693</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>693</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>693</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>693</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>693</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>693</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>706</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>709</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>709</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>709</v>
       </c>
@@ -13851,7 +13851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>709</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>709</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>709</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>709</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>722</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>722</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>722</v>
       </c>
@@ -14054,7 +14054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>722</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>722</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>722</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>735</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>735</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>735</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>735</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>735</v>
       </c>
@@ -14286,7 +14286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>735</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>735</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>735</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>735</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>735</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>735</v>
       </c>
@@ -14460,7 +14460,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>735</v>
       </c>
@@ -14489,7 +14489,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>735</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>766</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>766</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>766</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>766</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>766</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>766</v>
       </c>
@@ -14692,7 +14692,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>766</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>766</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>766</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>766</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>766</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>766</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>367</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>367</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>367</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>367</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>367</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>367</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>367</v>
       </c>
@@ -15069,7 +15069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>367</v>
       </c>
@@ -15098,7 +15098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>367</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>367</v>
       </c>
@@ -15156,7 +15156,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>367</v>
       </c>
@@ -15185,7 +15185,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>367</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>821</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>821</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>826</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>826</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>826</v>
       </c>
@@ -15359,7 +15359,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>836</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>836</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>836</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>836</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>836</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>836</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>836</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>836</v>
       </c>
@@ -15591,7 +15591,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>743</v>
       </c>
@@ -15620,7 +15620,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>743</v>
       </c>
@@ -15649,7 +15649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>743</v>
       </c>
@@ -15678,7 +15678,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>743</v>
       </c>
@@ -15707,7 +15707,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>743</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>743</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>743</v>
       </c>
@@ -15794,7 +15794,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>743</v>
       </c>
@@ -15823,7 +15823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>743</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>876</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>876</v>
       </c>
@@ -15910,7 +15910,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>876</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>876</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>876</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>876</v>
       </c>
@@ -16026,7 +16026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>876</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>876</v>
       </c>
@@ -16084,7 +16084,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>876</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>876</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>896</v>
       </c>
@@ -16171,7 +16171,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>896</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>896</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>896</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>896</v>
       </c>
@@ -16287,7 +16287,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>896</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>896</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>896</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>896</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>896</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>896</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>896</v>
       </c>
@@ -16490,7 +16490,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>896</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>896</v>
       </c>
@@ -16548,7 +16548,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>930</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>930</v>
       </c>
@@ -16606,7 +16606,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>227</v>
       </c>
@@ -16635,7 +16635,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>227</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>227</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>227</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>227</v>
       </c>
@@ -16751,7 +16751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>227</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>227</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>227</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>227</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>952</v>
       </c>
@@ -16896,7 +16896,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>952</v>
       </c>
@@ -16925,7 +16925,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>952</v>
       </c>
@@ -16954,7 +16954,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>952</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>952</v>
       </c>
@@ -17012,7 +17012,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>952</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>952</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>951</v>
       </c>
@@ -17099,7 +17099,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>951</v>
       </c>
@@ -17128,7 +17128,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>951</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>951</v>
       </c>
@@ -17186,7 +17186,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>951</v>
       </c>
@@ -17215,7 +17215,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>951</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>951</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>951</v>
       </c>
@@ -17302,7 +17302,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>951</v>
       </c>
@@ -17331,7 +17331,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>753</v>
       </c>
@@ -17360,7 +17360,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>753</v>
       </c>
@@ -17389,7 +17389,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>753</v>
       </c>
@@ -17418,7 +17418,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>753</v>
       </c>
@@ -17447,7 +17447,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>753</v>
       </c>
@@ -17476,7 +17476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>753</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1000</v>
       </c>
@@ -17534,7 +17534,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1000</v>
       </c>
@@ -17563,7 +17563,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1000</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1000</v>
       </c>
@@ -17621,7 +17621,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1000</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1000</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1000</v>
       </c>
@@ -17708,7 +17708,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1000</v>
       </c>
@@ -17737,7 +17737,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1000</v>
       </c>
@@ -17766,7 +17766,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1000</v>
       </c>
@@ -17795,7 +17795,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1000</v>
       </c>
@@ -17824,7 +17824,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1000</v>
       </c>
@@ -17853,7 +17853,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1000</v>
       </c>
@@ -17882,7 +17882,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1000</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1000</v>
       </c>
@@ -17940,7 +17940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1000</v>
       </c>
@@ -17969,7 +17969,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1000</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1034</v>
       </c>
@@ -18027,7 +18027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>99</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>99</v>
       </c>
@@ -18085,7 +18085,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>99</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>99</v>
       </c>
@@ -18143,7 +18143,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>99</v>
       </c>
@@ -18172,7 +18172,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>99</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>99</v>
       </c>
@@ -18230,7 +18230,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1052</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1052</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1052</v>
       </c>
@@ -18317,7 +18317,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1052</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1052</v>
       </c>
@@ -18375,7 +18375,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1052</v>
       </c>
@@ -18404,7 +18404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1067</v>
       </c>
@@ -18433,7 +18433,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1067</v>
       </c>
@@ -18462,7 +18462,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1067</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1067</v>
       </c>
@@ -18520,7 +18520,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1067</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1067</v>
       </c>
@@ -18578,7 +18578,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1067</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1067</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1067</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1088</v>
       </c>
@@ -18694,7 +18694,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1088</v>
       </c>
@@ -18723,7 +18723,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1088</v>
       </c>
@@ -18752,7 +18752,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1088</v>
       </c>
@@ -18781,7 +18781,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1088</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1088</v>
       </c>
@@ -18839,7 +18839,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1088</v>
       </c>
@@ -18868,7 +18868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1088</v>
       </c>
@@ -18897,7 +18897,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1088</v>
       </c>
@@ -18926,7 +18926,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1103</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1103</v>
       </c>
@@ -18984,7 +18984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1103</v>
       </c>
@@ -19013,7 +19013,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1103</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1103</v>
       </c>
@@ -19071,7 +19071,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1103</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1103</v>
       </c>
@@ -19129,7 +19129,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1103</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1103</v>
       </c>
@@ -19187,7 +19187,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1103</v>
       </c>
@@ -19216,7 +19216,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1103</v>
       </c>
@@ -19245,7 +19245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1103</v>
       </c>
@@ -19274,7 +19274,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1103</v>
       </c>
@@ -19303,7 +19303,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>117</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1130</v>
       </c>
@@ -19361,7 +19361,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1133</v>
       </c>
@@ -19390,7 +19390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1133</v>
       </c>
@@ -19419,7 +19419,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>18</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>18</v>
       </c>
@@ -19477,7 +19477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>18</v>
       </c>
@@ -19506,7 +19506,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>18</v>
       </c>
@@ -19535,7 +19535,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>18</v>
       </c>
@@ -19564,7 +19564,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>18</v>
       </c>
@@ -19593,7 +19593,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>18</v>
       </c>
@@ -19622,7 +19622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>18</v>
       </c>
@@ -19651,7 +19651,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>18</v>
       </c>
@@ -19680,7 +19680,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>18</v>
       </c>
@@ -19709,7 +19709,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>18</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>18</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>18</v>
       </c>
@@ -19796,7 +19796,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>18</v>
       </c>
@@ -19825,7 +19825,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>18</v>
       </c>
@@ -19854,7 +19854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>18</v>
       </c>
@@ -19883,7 +19883,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>18</v>
       </c>
@@ -19912,7 +19912,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>18</v>
       </c>
@@ -19941,7 +19941,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>18</v>
       </c>
@@ -19970,7 +19970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>18</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>18</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>18</v>
       </c>
@@ -20057,7 +20057,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>18</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>18</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>18</v>
       </c>
@@ -20144,7 +20144,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>18</v>
       </c>
@@ -20173,7 +20173,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>18</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>18</v>
       </c>
@@ -20231,7 +20231,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>18</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>18</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>18</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>18</v>
       </c>
@@ -20347,7 +20347,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>18</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>18</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>18</v>
       </c>
@@ -20434,7 +20434,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>18</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>18</v>
       </c>
@@ -20492,7 +20492,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>18</v>
       </c>
@@ -20521,7 +20521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>18</v>
       </c>
@@ -20550,7 +20550,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>18</v>
       </c>
@@ -20579,7 +20579,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>18</v>
       </c>
@@ -20608,7 +20608,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>18</v>
       </c>
@@ -20637,7 +20637,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>18</v>
       </c>
@@ -20666,7 +20666,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>18</v>
       </c>
@@ -20695,7 +20695,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>18</v>
       </c>
@@ -20724,7 +20724,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>18</v>
       </c>
@@ -20753,7 +20753,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>18</v>
       </c>
@@ -20782,7 +20782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>18</v>
       </c>
@@ -20811,7 +20811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>18</v>
       </c>
@@ -20840,7 +20840,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>18</v>
       </c>
@@ -20869,7 +20869,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>18</v>
       </c>
@@ -20898,7 +20898,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>18</v>
       </c>
@@ -20927,7 +20927,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>18</v>
       </c>
@@ -20956,7 +20956,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>18</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>18</v>
       </c>
@@ -21014,7 +21014,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>18</v>
       </c>
@@ -21043,7 +21043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>18</v>
       </c>
@@ -21072,7 +21072,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>18</v>
       </c>
@@ -21101,7 +21101,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>18</v>
       </c>
@@ -21130,7 +21130,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>18</v>
       </c>
@@ -21159,7 +21159,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>18</v>
       </c>
@@ -21188,7 +21188,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>18</v>
       </c>
@@ -21217,7 +21217,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>18</v>
       </c>
@@ -21246,7 +21246,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>18</v>
       </c>
@@ -21275,7 +21275,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>18</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>18</v>
       </c>
@@ -21333,7 +21333,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>18</v>
       </c>
@@ -21362,7 +21362,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>18</v>
       </c>
@@ -21391,7 +21391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>18</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>18</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>18</v>
       </c>
@@ -21478,7 +21478,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>18</v>
       </c>
@@ -21507,7 +21507,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>18</v>
       </c>
@@ -21536,7 +21536,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>18</v>
       </c>
@@ -21565,7 +21565,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>18</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>18</v>
       </c>
@@ -21623,7 +21623,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>18</v>
       </c>
@@ -21652,7 +21652,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>18</v>
       </c>
@@ -21681,7 +21681,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>18</v>
       </c>
@@ -21710,7 +21710,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>18</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>18</v>
       </c>
@@ -21768,7 +21768,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>18</v>
       </c>
@@ -21797,7 +21797,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>18</v>
       </c>
@@ -21826,7 +21826,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>18</v>
       </c>
@@ -21855,7 +21855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>18</v>
       </c>
@@ -21884,7 +21884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>18</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>18</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>18</v>
       </c>
@@ -21971,7 +21971,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>18</v>
       </c>
@@ -22000,7 +22000,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>18</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>18</v>
       </c>
@@ -22058,7 +22058,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>18</v>
       </c>
@@ -22087,7 +22087,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>18</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>18</v>
       </c>
@@ -22145,7 +22145,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>18</v>
       </c>
@@ -22174,7 +22174,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>18</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>18</v>
       </c>
@@ -22232,7 +22232,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>18</v>
       </c>
@@ -22261,7 +22261,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>18</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>18</v>
       </c>
@@ -22319,7 +22319,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>18</v>
       </c>
@@ -22348,7 +22348,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>18</v>
       </c>
@@ -22377,7 +22377,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>18</v>
       </c>
@@ -22406,7 +22406,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>18</v>
       </c>
@@ -22435,7 +22435,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>18</v>
       </c>
@@ -22464,7 +22464,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>18</v>
       </c>
@@ -22493,7 +22493,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>18</v>
       </c>
@@ -22522,7 +22522,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>18</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>18</v>
       </c>
@@ -22580,7 +22580,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>18</v>
       </c>
@@ -22609,7 +22609,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>18</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>18</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>18</v>
       </c>
@@ -22696,7 +22696,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>18</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>18</v>
       </c>
@@ -22754,7 +22754,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>18</v>
       </c>
@@ -22783,7 +22783,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>18</v>
       </c>
@@ -22812,7 +22812,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>18</v>
       </c>
@@ -22841,7 +22841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>18</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>18</v>
       </c>
@@ -22899,7 +22899,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>18</v>
       </c>
@@ -22928,7 +22928,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>18</v>
       </c>
@@ -22957,7 +22957,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>18</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>18</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>18</v>
       </c>
@@ -23044,7 +23044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>18</v>
       </c>
@@ -23073,7 +23073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>18</v>
       </c>
@@ -23102,7 +23102,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>18</v>
       </c>
@@ -23131,7 +23131,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>18</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>18</v>
       </c>
@@ -23189,7 +23189,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>18</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>18</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>18</v>
       </c>
@@ -23276,7 +23276,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>18</v>
       </c>
@@ -23305,7 +23305,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>18</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>18</v>
       </c>
@@ -23363,7 +23363,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>18</v>
       </c>
@@ -23392,7 +23392,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>18</v>
       </c>
@@ -23421,7 +23421,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>18</v>
       </c>
@@ -23450,7 +23450,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>18</v>
       </c>
@@ -23479,7 +23479,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>18</v>
       </c>
@@ -23508,7 +23508,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>18</v>
       </c>
@@ -23537,7 +23537,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>18</v>
       </c>
@@ -23566,7 +23566,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>18</v>
       </c>
@@ -23595,7 +23595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>18</v>
       </c>
@@ -23624,7 +23624,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>18</v>
       </c>
@@ -23653,7 +23653,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>18</v>
       </c>
@@ -23682,7 +23682,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>18</v>
       </c>
@@ -23711,7 +23711,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>18</v>
       </c>
@@ -23740,7 +23740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>18</v>
       </c>
@@ -23769,7 +23769,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>18</v>
       </c>
@@ -23798,7 +23798,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>18</v>
       </c>
@@ -23827,7 +23827,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>18</v>
       </c>
@@ -23856,7 +23856,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>18</v>
       </c>
@@ -23885,7 +23885,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>18</v>
       </c>
@@ -23914,7 +23914,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>18</v>
       </c>
@@ -23943,7 +23943,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>18</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>18</v>
       </c>
@@ -24001,7 +24001,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>18</v>
       </c>
@@ -24030,7 +24030,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>18</v>
       </c>
@@ -24059,7 +24059,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>18</v>
       </c>
@@ -24088,7 +24088,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>18</v>
       </c>
@@ -24117,7 +24117,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>18</v>
       </c>
@@ -24146,7 +24146,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>18</v>
       </c>
@@ -24175,7 +24175,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>18</v>
       </c>
@@ -24204,7 +24204,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>18</v>
       </c>
@@ -24233,7 +24233,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>18</v>
       </c>
@@ -24262,7 +24262,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>18</v>
       </c>
@@ -24291,7 +24291,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>18</v>
       </c>
@@ -24320,7 +24320,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>18</v>
       </c>
@@ -24349,7 +24349,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>18</v>
       </c>
@@ -24378,7 +24378,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>18</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>18</v>
       </c>
@@ -24436,7 +24436,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>18</v>
       </c>
@@ -24465,7 +24465,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>18</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>18</v>
       </c>
@@ -24523,7 +24523,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>18</v>
       </c>
@@ -24552,7 +24552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>18</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>18</v>
       </c>
@@ -24610,7 +24610,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>18</v>
       </c>
@@ -24639,7 +24639,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>18</v>
       </c>
@@ -24668,7 +24668,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>18</v>
       </c>
@@ -24697,7 +24697,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>18</v>
       </c>
@@ -24726,7 +24726,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>18</v>
       </c>
@@ -24755,7 +24755,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>18</v>
       </c>
@@ -24784,7 +24784,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>18</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>18</v>
       </c>
@@ -24842,7 +24842,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>18</v>
       </c>
@@ -24871,7 +24871,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>18</v>
       </c>
@@ -24900,7 +24900,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>18</v>
       </c>
@@ -24929,7 +24929,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>18</v>
       </c>
@@ -24958,7 +24958,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>18</v>
       </c>
@@ -24987,7 +24987,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>18</v>
       </c>
@@ -25016,7 +25016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>18</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>18</v>
       </c>
@@ -25074,7 +25074,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>18</v>
       </c>
@@ -25103,7 +25103,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>18</v>
       </c>
@@ -25132,7 +25132,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>18</v>
       </c>
@@ -25161,7 +25161,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>18</v>
       </c>
@@ -25190,7 +25190,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>18</v>
       </c>
@@ -25219,7 +25219,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>18</v>
       </c>
@@ -25248,7 +25248,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>18</v>
       </c>
@@ -25277,7 +25277,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>18</v>
       </c>
@@ -25306,7 +25306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>18</v>
       </c>
@@ -25335,7 +25335,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>18</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>18</v>
       </c>
@@ -25393,7 +25393,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>18</v>
       </c>
@@ -25422,7 +25422,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>18</v>
       </c>
@@ -25451,7 +25451,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>18</v>
       </c>
@@ -25480,7 +25480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>18</v>
       </c>
@@ -25509,7 +25509,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>18</v>
       </c>
@@ -25538,7 +25538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>18</v>
       </c>
@@ -25567,7 +25567,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>18</v>
       </c>
@@ -25596,7 +25596,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>18</v>
       </c>
@@ -25625,7 +25625,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>18</v>
       </c>
@@ -25654,7 +25654,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>18</v>
       </c>
@@ -25683,7 +25683,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>18</v>
       </c>
@@ -25712,7 +25712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>18</v>
       </c>
@@ -25741,7 +25741,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>18</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>18</v>
       </c>
@@ -25799,7 +25799,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>18</v>
       </c>
@@ -25828,7 +25828,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>18</v>
       </c>
@@ -25857,7 +25857,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>18</v>
       </c>
@@ -25886,7 +25886,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>18</v>
       </c>
@@ -25915,7 +25915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>18</v>
       </c>
@@ -25944,7 +25944,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>18</v>
       </c>
@@ -25973,7 +25973,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>18</v>
       </c>
@@ -26002,7 +26002,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>18</v>
       </c>
@@ -26031,7 +26031,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>18</v>
       </c>
@@ -26060,7 +26060,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>18</v>
       </c>
@@ -26089,7 +26089,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>18</v>
       </c>
@@ -26118,7 +26118,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>18</v>
       </c>
@@ -26147,7 +26147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>18</v>
       </c>
@@ -26176,7 +26176,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>18</v>
       </c>
@@ -26205,7 +26205,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>18</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>18</v>
       </c>
@@ -26263,7 +26263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>18</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>18</v>
       </c>
@@ -26321,7 +26321,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>18</v>
       </c>
@@ -26350,7 +26350,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>18</v>
       </c>
@@ -26379,7 +26379,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>18</v>
       </c>
@@ -26408,7 +26408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>18</v>
       </c>
@@ -26437,7 +26437,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>18</v>
       </c>
@@ -26466,7 +26466,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>18</v>
       </c>
@@ -26495,7 +26495,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>18</v>
       </c>
@@ -26524,7 +26524,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>18</v>
       </c>
@@ -26553,7 +26553,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>18</v>
       </c>
@@ -26582,7 +26582,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>18</v>
       </c>
@@ -26611,7 +26611,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>18</v>
       </c>
@@ -26640,7 +26640,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>18</v>
       </c>
@@ -26669,7 +26669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>18</v>
       </c>
@@ -26698,7 +26698,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>18</v>
       </c>
@@ -26727,7 +26727,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>18</v>
       </c>
@@ -26756,7 +26756,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>18</v>
       </c>
@@ -26785,7 +26785,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>18</v>
       </c>
@@ -26814,7 +26814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>18</v>
       </c>
@@ -26843,7 +26843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>18</v>
       </c>
@@ -26872,7 +26872,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>18</v>
       </c>
@@ -26901,7 +26901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>18</v>
       </c>
@@ -26930,7 +26930,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>18</v>
       </c>
@@ -26959,7 +26959,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>18</v>
       </c>
@@ -26988,7 +26988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>18</v>
       </c>
@@ -27017,7 +27017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>18</v>
       </c>
@@ -27046,7 +27046,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>18</v>
       </c>
@@ -27075,7 +27075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>18</v>
       </c>
@@ -27104,7 +27104,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>18</v>
       </c>
@@ -27133,7 +27133,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>18</v>
       </c>
@@ -27162,7 +27162,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>18</v>
       </c>
@@ -27191,7 +27191,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>18</v>
       </c>
@@ -27220,7 +27220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>18</v>
       </c>
@@ -27249,7 +27249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>18</v>
       </c>
@@ -27278,7 +27278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>18</v>
       </c>
@@ -27307,7 +27307,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>18</v>
       </c>
@@ -27336,7 +27336,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>18</v>
       </c>
@@ -27365,7 +27365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>18</v>
       </c>
@@ -27394,7 +27394,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>18</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>18</v>
       </c>
@@ -27452,7 +27452,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>18</v>
       </c>
@@ -27481,7 +27481,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>18</v>
       </c>
@@ -27510,7 +27510,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>18</v>
       </c>
@@ -27539,7 +27539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>18</v>
       </c>
@@ -27568,7 +27568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>18</v>
       </c>
@@ -27597,7 +27597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>18</v>
       </c>
@@ -27626,7 +27626,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>18</v>
       </c>
@@ -27655,7 +27655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>18</v>
       </c>
@@ -27684,7 +27684,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>18</v>
       </c>
@@ -27713,7 +27713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>18</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>18</v>
       </c>
@@ -27771,7 +27771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>18</v>
       </c>
@@ -27800,7 +27800,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>18</v>
       </c>
@@ -27829,7 +27829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>18</v>
       </c>
@@ -27858,7 +27858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>18</v>
       </c>
@@ -27887,7 +27887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>18</v>
       </c>
@@ -27916,7 +27916,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>18</v>
       </c>
@@ -27945,7 +27945,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>18</v>
       </c>
@@ -27974,7 +27974,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>18</v>
       </c>
@@ -28003,7 +28003,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>18</v>
       </c>
@@ -28032,7 +28032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>18</v>
       </c>
@@ -28061,7 +28061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>18</v>
       </c>
@@ -28090,7 +28090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>18</v>
       </c>
@@ -28119,7 +28119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>18</v>
       </c>
@@ -28148,7 +28148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>18</v>
       </c>
@@ -28177,7 +28177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>18</v>
       </c>
@@ -28206,7 +28206,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>18</v>
       </c>
@@ -28235,7 +28235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>18</v>
       </c>
@@ -28264,7 +28264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>18</v>
       </c>
@@ -28293,7 +28293,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>18</v>
       </c>
@@ -28322,7 +28322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>18</v>
       </c>
@@ -28351,7 +28351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>18</v>
       </c>
@@ -28380,7 +28380,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>18</v>
       </c>
@@ -28409,7 +28409,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>18</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>18</v>
       </c>
@@ -28467,7 +28467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>18</v>
       </c>
@@ -28496,7 +28496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>18</v>
       </c>
@@ -28525,7 +28525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>18</v>
       </c>
@@ -28554,7 +28554,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>18</v>
       </c>
@@ -28583,7 +28583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>18</v>
       </c>
@@ -28612,7 +28612,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>18</v>
       </c>
@@ -28641,7 +28641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>18</v>
       </c>
@@ -28670,7 +28670,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>18</v>
       </c>
@@ -28699,7 +28699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>18</v>
       </c>
@@ -28728,7 +28728,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>18</v>
       </c>
@@ -28757,7 +28757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>18</v>
       </c>
@@ -28786,7 +28786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>18</v>
       </c>
@@ -28815,7 +28815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>18</v>
       </c>
@@ -28844,7 +28844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>18</v>
       </c>
@@ -28873,7 +28873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>18</v>
       </c>
@@ -28902,7 +28902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>18</v>
       </c>
@@ -28931,7 +28931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>18</v>
       </c>
@@ -28960,7 +28960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>18</v>
       </c>
@@ -28989,7 +28989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>18</v>
       </c>
@@ -29018,7 +29018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>18</v>
       </c>
@@ -29047,7 +29047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>18</v>
       </c>
@@ -29076,7 +29076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>18</v>
       </c>
@@ -29105,7 +29105,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>18</v>
       </c>
@@ -29134,7 +29134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>18</v>
       </c>
@@ -29163,7 +29163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>18</v>
       </c>
@@ -29192,7 +29192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>18</v>
       </c>
@@ -29221,7 +29221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>18</v>
       </c>
@@ -29250,7 +29250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>18</v>
       </c>
@@ -29279,7 +29279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>18</v>
       </c>
@@ -29308,7 +29308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>18</v>
       </c>
@@ -29337,7 +29337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>18</v>
       </c>
@@ -29366,7 +29366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>18</v>
       </c>
@@ -29395,7 +29395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>18</v>
       </c>
@@ -29424,7 +29424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>18</v>
       </c>
@@ -29453,7 +29453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>18</v>
       </c>
@@ -29482,7 +29482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>18</v>
       </c>
@@ -29511,7 +29511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>18</v>
       </c>
@@ -29540,7 +29540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>18</v>
       </c>
@@ -29569,7 +29569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>18</v>
       </c>
@@ -29598,7 +29598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>18</v>
       </c>
@@ -29627,7 +29627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>18</v>
       </c>
@@ -29656,7 +29656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>18</v>
       </c>
@@ -29685,7 +29685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>18</v>
       </c>
@@ -29714,7 +29714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>18</v>
       </c>
@@ -29743,7 +29743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>18</v>
       </c>
@@ -29772,7 +29772,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>18</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>18</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>18</v>
       </c>
@@ -29859,7 +29859,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>18</v>
       </c>
@@ -29888,7 +29888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>18</v>
       </c>
@@ -29917,7 +29917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>18</v>
       </c>
@@ -29946,7 +29946,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>18</v>
       </c>
@@ -29975,7 +29975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>18</v>
       </c>
@@ -30004,7 +30004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>18</v>
       </c>
@@ -30033,7 +30033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>18</v>
       </c>
@@ -30062,7 +30062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>18</v>
       </c>
@@ -30091,7 +30091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>18</v>
       </c>
@@ -30120,7 +30120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>18</v>
       </c>
@@ -30149,7 +30149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>18</v>
       </c>
@@ -30178,7 +30178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>18</v>
       </c>
@@ -30207,7 +30207,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>18</v>
       </c>
@@ -30236,7 +30236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>18</v>
       </c>
@@ -30265,7 +30265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>18</v>
       </c>
@@ -30294,7 +30294,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>18</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>18</v>
       </c>
@@ -30352,7 +30352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>18</v>
       </c>
@@ -30381,7 +30381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>18</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>18</v>
       </c>
@@ -30439,7 +30439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>18</v>
       </c>
@@ -30468,7 +30468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>18</v>
       </c>
@@ -30497,7 +30497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>18</v>
       </c>
@@ -30526,7 +30526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>18</v>
       </c>
@@ -30555,7 +30555,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>18</v>
       </c>
@@ -30584,7 +30584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>18</v>
       </c>
@@ -30613,7 +30613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>18</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>18</v>
       </c>
@@ -30671,7 +30671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>18</v>
       </c>
@@ -30700,7 +30700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>18</v>
       </c>
@@ -30729,7 +30729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>18</v>
       </c>
@@ -30758,7 +30758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>18</v>
       </c>
@@ -30787,7 +30787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>18</v>
       </c>
@@ -30816,7 +30816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>18</v>
       </c>
@@ -30845,7 +30845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>18</v>
       </c>
@@ -30874,7 +30874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>18</v>
       </c>
@@ -30903,7 +30903,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>18</v>
       </c>
@@ -30932,7 +30932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>18</v>
       </c>
@@ -30961,7 +30961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>18</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>18</v>
       </c>
@@ -31019,7 +31019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>18</v>
       </c>
@@ -31048,7 +31048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>18</v>
       </c>
@@ -31077,7 +31077,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>18</v>
       </c>
@@ -31106,7 +31106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>18</v>
       </c>
@@ -31135,7 +31135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>18</v>
       </c>
@@ -31164,7 +31164,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>18</v>
       </c>
@@ -31193,7 +31193,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>18</v>
       </c>
@@ -31222,7 +31222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>18</v>
       </c>
@@ -31251,7 +31251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>18</v>
       </c>
@@ -31280,7 +31280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>18</v>
       </c>
@@ -31309,7 +31309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>18</v>
       </c>
@@ -31338,7 +31338,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>18</v>
       </c>
@@ -31367,7 +31367,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>18</v>
       </c>
@@ -31396,7 +31396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>18</v>
       </c>
@@ -31425,7 +31425,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>18</v>
       </c>
@@ -31454,7 +31454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>18</v>
       </c>
@@ -31483,7 +31483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>18</v>
       </c>
@@ -31512,7 +31512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>18</v>
       </c>
@@ -31541,7 +31541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>18</v>
       </c>
@@ -31570,7 +31570,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>18</v>
       </c>
@@ -31599,7 +31599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>18</v>
       </c>
@@ -31628,7 +31628,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>18</v>
       </c>
@@ -31657,7 +31657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>18</v>
       </c>
@@ -31686,7 +31686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>18</v>
       </c>
@@ -31715,7 +31715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>18</v>
       </c>
@@ -31744,7 +31744,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>18</v>
       </c>
@@ -31773,7 +31773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>18</v>
       </c>
@@ -31802,7 +31802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>18</v>
       </c>
@@ -31831,7 +31831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>18</v>
       </c>
@@ -31860,7 +31860,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>18</v>
       </c>
@@ -31889,7 +31889,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>18</v>
       </c>
@@ -31918,7 +31918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>18</v>
       </c>
@@ -31947,7 +31947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>18</v>
       </c>
@@ -31976,7 +31976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>18</v>
       </c>
@@ -32005,7 +32005,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>18</v>
       </c>
@@ -32034,7 +32034,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>18</v>
       </c>
@@ -32063,7 +32063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>18</v>
       </c>
@@ -32092,7 +32092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>18</v>
       </c>
@@ -32121,7 +32121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>18</v>
       </c>
@@ -32150,7 +32150,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>18</v>
       </c>
@@ -32179,7 +32179,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>18</v>
       </c>
@@ -32208,7 +32208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>18</v>
       </c>
@@ -32237,7 +32237,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>18</v>
       </c>
@@ -32266,7 +32266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>18</v>
       </c>
@@ -32295,7 +32295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>18</v>
       </c>
@@ -32324,7 +32324,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>18</v>
       </c>
@@ -32353,7 +32353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>18</v>
       </c>
@@ -32382,7 +32382,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>18</v>
       </c>
@@ -32411,7 +32411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>18</v>
       </c>
@@ -32440,7 +32440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>18</v>
       </c>
@@ -32469,7 +32469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>18</v>
       </c>
@@ -32498,7 +32498,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>18</v>
       </c>
@@ -32527,7 +32527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>18</v>
       </c>
@@ -32556,7 +32556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>18</v>
       </c>
@@ -32585,7 +32585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>18</v>
       </c>
@@ -32614,7 +32614,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>18</v>
       </c>
@@ -32643,7 +32643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>18</v>
       </c>
@@ -32672,7 +32672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>18</v>
       </c>
@@ -32701,7 +32701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>18</v>
       </c>
@@ -32730,7 +32730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>18</v>
       </c>
@@ -32759,7 +32759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>18</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>18</v>
       </c>
@@ -32817,7 +32817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>18</v>
       </c>
@@ -32846,7 +32846,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>18</v>
       </c>
@@ -32875,7 +32875,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>18</v>
       </c>
@@ -32904,7 +32904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>18</v>
       </c>
@@ -32933,7 +32933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>18</v>
       </c>
@@ -32962,7 +32962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>18</v>
       </c>
@@ -32991,7 +32991,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>18</v>
       </c>
@@ -33020,7 +33020,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>18</v>
       </c>
@@ -33049,7 +33049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>18</v>
       </c>
@@ -33078,7 +33078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>18</v>
       </c>
@@ -33107,7 +33107,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>18</v>
       </c>
@@ -33136,7 +33136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>18</v>
       </c>
@@ -33165,7 +33165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>18</v>
       </c>
@@ -33194,7 +33194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>18</v>
       </c>
@@ -33223,7 +33223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>18</v>
       </c>
@@ -33252,7 +33252,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>18</v>
       </c>
@@ -33281,7 +33281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>18</v>
       </c>
@@ -33310,7 +33310,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>18</v>
       </c>
@@ -33339,7 +33339,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>18</v>
       </c>
@@ -33368,7 +33368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>18</v>
       </c>
@@ -33397,7 +33397,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>18</v>
       </c>
@@ -33426,7 +33426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>18</v>
       </c>
@@ -33455,7 +33455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>18</v>
       </c>
@@ -33484,7 +33484,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>9</v>
       </c>
@@ -33513,7 +33513,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>32</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>58</v>
       </c>
@@ -33571,7 +33571,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>88</v>
       </c>
@@ -33600,7 +33600,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>128</v>
       </c>
@@ -33629,7 +33629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>189</v>
       </c>
@@ -33658,7 +33658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>2073</v>
       </c>
@@ -33687,7 +33687,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>254</v>
       </c>
@@ -33716,7 +33716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>267</v>
       </c>
@@ -33745,7 +33745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>323</v>
       </c>
@@ -33774,7 +33774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>357</v>
       </c>
@@ -33803,7 +33803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>509</v>
       </c>
@@ -33832,7 +33832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>509</v>
       </c>
@@ -33861,7 +33861,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>516</v>
       </c>
@@ -33890,7 +33890,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>516</v>
       </c>
@@ -33919,7 +33919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>516</v>
       </c>
@@ -33948,7 +33948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>516</v>
       </c>
@@ -33977,7 +33977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>124</v>
       </c>
@@ -34006,7 +34006,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>124</v>
       </c>
@@ -34035,7 +34035,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>124</v>
       </c>
@@ -34064,7 +34064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>594</v>
       </c>
@@ -34093,7 +34093,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>594</v>
       </c>
@@ -34122,7 +34122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>594</v>
       </c>
@@ -34151,7 +34151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>612</v>
       </c>
@@ -34180,7 +34180,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>612</v>
       </c>
@@ -34209,7 +34209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>650</v>
       </c>
@@ -34238,7 +34238,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>669</v>
       </c>
@@ -34267,7 +34267,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>693</v>
       </c>
@@ -34296,7 +34296,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>709</v>
       </c>
@@ -34325,7 +34325,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>709</v>
       </c>
@@ -34354,7 +34354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>722</v>
       </c>
@@ -34383,7 +34383,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>735</v>
       </c>
@@ -34412,7 +34412,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>367</v>
       </c>
@@ -34441,7 +34441,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>367</v>
       </c>
@@ -34470,7 +34470,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>367</v>
       </c>
@@ -34499,7 +34499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>367</v>
       </c>
@@ -34528,7 +34528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>832</v>
       </c>
@@ -34557,7 +34557,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>836</v>
       </c>
@@ -34586,7 +34586,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>743</v>
       </c>
@@ -34615,7 +34615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>743</v>
       </c>
@@ -34644,7 +34644,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>743</v>
       </c>
@@ -34673,7 +34673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>876</v>
       </c>
@@ -34702,7 +34702,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>876</v>
       </c>
@@ -34731,7 +34731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>896</v>
       </c>
@@ -34760,7 +34760,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>896</v>
       </c>
@@ -34789,7 +34789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>896</v>
       </c>
@@ -34818,7 +34818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>227</v>
       </c>
@@ -34847,7 +34847,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>952</v>
       </c>
@@ -34876,7 +34876,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>952</v>
       </c>
@@ -34905,7 +34905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>951</v>
       </c>
@@ -34934,7 +34934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>951</v>
       </c>
@@ -34963,7 +34963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>753</v>
       </c>
@@ -34992,7 +34992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>1000</v>
       </c>
@@ -35021,7 +35021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>1000</v>
       </c>
@@ -35050,7 +35050,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>1000</v>
       </c>
@@ -35079,7 +35079,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>1000</v>
       </c>
@@ -35108,7 +35108,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>1052</v>
       </c>
@@ -35137,7 +35137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>1067</v>
       </c>
@@ -35166,7 +35166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>1103</v>
       </c>
@@ -35195,7 +35195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>18</v>
       </c>
@@ -35224,7 +35224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>18</v>
       </c>
@@ -35253,7 +35253,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>18</v>
       </c>
@@ -35282,7 +35282,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>18</v>
       </c>
@@ -35311,7 +35311,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>18</v>
       </c>
@@ -35340,7 +35340,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>18</v>
       </c>
@@ -35369,7 +35369,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>18</v>
       </c>
@@ -35398,7 +35398,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>18</v>
       </c>
@@ -35427,7 +35427,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>18</v>
       </c>
@@ -35456,7 +35456,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>18</v>
       </c>
@@ -35485,7 +35485,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>18</v>
       </c>
@@ -35514,7 +35514,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>18</v>
       </c>
@@ -35543,7 +35543,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>18</v>
       </c>
@@ -35572,7 +35572,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>18</v>
       </c>
@@ -35601,7 +35601,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>18</v>
       </c>
@@ -35630,7 +35630,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>18</v>
       </c>
@@ -35659,7 +35659,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>18</v>
       </c>
@@ -35688,7 +35688,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>18</v>
       </c>
@@ -35717,7 +35717,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>18</v>
       </c>
@@ -35746,7 +35746,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>18</v>
       </c>
@@ -35775,7 +35775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>18</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>18</v>
       </c>
@@ -35833,7 +35833,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>18</v>
       </c>
@@ -35862,7 +35862,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>18</v>
       </c>
@@ -35891,7 +35891,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>18</v>
       </c>
@@ -35920,7 +35920,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>18</v>
       </c>
@@ -35949,7 +35949,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>18</v>
       </c>
@@ -35978,7 +35978,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>18</v>
       </c>
@@ -36007,7 +36007,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>18</v>
       </c>
@@ -36036,7 +36036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>18</v>
       </c>
@@ -36065,7 +36065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>18</v>
       </c>
@@ -36094,7 +36094,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>18</v>
       </c>
@@ -36123,7 +36123,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>18</v>
       </c>
@@ -36152,7 +36152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>18</v>
       </c>
@@ -36181,7 +36181,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>18</v>
       </c>
@@ -36210,7 +36210,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>18</v>
       </c>
@@ -36239,7 +36239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>18</v>
       </c>
@@ -36268,7 +36268,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>18</v>
       </c>
@@ -36297,7 +36297,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>18</v>
       </c>
@@ -36326,7 +36326,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>18</v>
       </c>
@@ -36355,7 +36355,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>18</v>
       </c>
@@ -36384,7 +36384,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>18</v>
       </c>
@@ -36413,7 +36413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>18</v>
       </c>
@@ -36442,7 +36442,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>18</v>
       </c>
@@ -36471,7 +36471,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>18</v>
       </c>
@@ -36500,7 +36500,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>18</v>
       </c>
@@ -36529,7 +36529,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>18</v>
       </c>
@@ -36558,7 +36558,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>18</v>
       </c>
@@ -36587,7 +36587,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>18</v>
       </c>
@@ -36616,7 +36616,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>18</v>
       </c>
@@ -36645,7 +36645,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>18</v>
       </c>
@@ -36674,7 +36674,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>18</v>
       </c>
@@ -36703,7 +36703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>18</v>
       </c>
@@ -36732,7 +36732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>18</v>
       </c>
@@ -36761,7 +36761,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>18</v>
       </c>
@@ -36790,7 +36790,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>18</v>
       </c>
@@ -36819,7 +36819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>18</v>
       </c>
@@ -36848,7 +36848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>18</v>
       </c>
@@ -36877,7 +36877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>18</v>
       </c>
@@ -36906,7 +36906,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>18</v>
       </c>
@@ -36935,7 +36935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>18</v>
       </c>
@@ -36964,7 +36964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>18</v>
       </c>
@@ -36993,7 +36993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>18</v>
       </c>
@@ -37022,7 +37022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>18</v>
       </c>
@@ -37051,7 +37051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>18</v>
       </c>
@@ -37080,7 +37080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>18</v>
       </c>
@@ -37109,7 +37109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>18</v>
       </c>
@@ -37138,7 +37138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>18</v>
       </c>
@@ -37167,7 +37167,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>18</v>
       </c>
@@ -37196,7 +37196,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>18</v>
       </c>
@@ -37225,7 +37225,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>18</v>
       </c>
@@ -37254,7 +37254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>18</v>
       </c>
@@ -37283,7 +37283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>18</v>
       </c>
@@ -37312,7 +37312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>18</v>
       </c>
@@ -37341,7 +37341,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>18</v>
       </c>
@@ -37370,7 +37370,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>18</v>
       </c>
@@ -37399,7 +37399,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>18</v>
       </c>
@@ -37428,7 +37428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>18</v>
       </c>
@@ -37457,7 +37457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>18</v>
       </c>
@@ -37486,7 +37486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>18</v>
       </c>
@@ -37515,7 +37515,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>18</v>
       </c>
@@ -37544,7 +37544,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>18</v>
       </c>
@@ -37573,7 +37573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>18</v>
       </c>
@@ -37602,7 +37602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>18</v>
       </c>
@@ -37631,7 +37631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>18</v>
       </c>
@@ -37660,7 +37660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>18</v>
       </c>
@@ -37689,7 +37689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>18</v>
       </c>
@@ -37718,7 +37718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>18</v>
       </c>
@@ -37747,7 +37747,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>18</v>
       </c>
@@ -37776,7 +37776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>18</v>
       </c>
@@ -37805,7 +37805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>18</v>
       </c>
@@ -37834,7 +37834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>18</v>
       </c>
@@ -37863,7 +37863,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>18</v>
       </c>
@@ -37892,7 +37892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>18</v>
       </c>
@@ -37921,7 +37921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>18</v>
       </c>
@@ -37950,7 +37950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>18</v>
       </c>
@@ -37979,7 +37979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>18</v>
       </c>
@@ -38008,7 +38008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>18</v>
       </c>
@@ -38037,7 +38037,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>18</v>
       </c>
@@ -38066,7 +38066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>18</v>
       </c>
@@ -38095,7 +38095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>18</v>
       </c>
@@ -38124,7 +38124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>18</v>
       </c>
@@ -38153,7 +38153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>18</v>
       </c>
@@ -38182,7 +38182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>18</v>
       </c>
@@ -38211,7 +38211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>18</v>
       </c>
@@ -38241,9 +38241,10 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I18 A20:I24 A19:G19 I19 A26:I28 A25:G25 I25 A30:I37 A29:G29 I29 A39:I59 A38:G38 I38 A61:I140 A60:G60 I60 A142:I146 A141:G141 I141 A148:I288 A147:G147 I147 A407:I470 A406:G406 I406 A472:I1063 A471:G471 I471 A290:I405 A289:G289 I289" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I10 A20:I24 A19:G19 I19 A26:I28 A25:G25 I25 A30:I37 A29:G29 I29 A39:I59 A38:G38 I38 A61:I140 A60:G60 I60 A142:I146 A141:G141 I141 A148:I288 A147:G147 I147 A407:I470 A406:G406 I406 A472:I1063 A471:G471 I471 A290:I405 A289:G289 I289 A12:I18 A11:F11 H11:I11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9556" uniqueCount="2337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9551" uniqueCount="2337">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -13496,8 +13496,8 @@
       <c r="G210" t="s">
         <v>161</v>
       </c>
-      <c r="H210" t="s">
-        <v>367</v>
+      <c r="H210" s="1">
+        <v>46127</v>
       </c>
       <c r="I210" t="s">
         <v>686</v>
@@ -14656,8 +14656,8 @@
       <c r="G250" t="s">
         <v>161</v>
       </c>
-      <c r="H250" t="s">
-        <v>367</v>
+      <c r="H250" s="1">
+        <v>46127</v>
       </c>
       <c r="I250" t="s">
         <v>686</v>
@@ -14772,8 +14772,8 @@
       <c r="G254" t="s">
         <v>498</v>
       </c>
-      <c r="H254" t="s">
-        <v>367</v>
+      <c r="H254" s="1">
+        <v>46127</v>
       </c>
       <c r="I254" t="s">
         <v>686</v>
@@ -16686,8 +16686,8 @@
       <c r="G320" t="s">
         <v>214</v>
       </c>
-      <c r="H320" t="s">
-        <v>367</v>
+      <c r="H320" s="1">
+        <v>46127</v>
       </c>
       <c r="I320" t="s">
         <v>686</v>
@@ -18774,8 +18774,8 @@
       <c r="G392" t="s">
         <v>162</v>
       </c>
-      <c r="H392" t="s">
-        <v>367</v>
+      <c r="H392" s="1">
+        <v>46127</v>
       </c>
       <c r="I392" t="s">
         <v>686</v>
@@ -38244,7 +38244,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I10 A20:I24 A19:G19 I19 A26:I28 A25:G25 I25 A30:I37 A29:G29 I29 A39:I59 A38:G38 I38 A61:I140 A60:G60 I60 A142:I146 A141:G141 I141 A148:I288 A147:G147 I147 A407:I470 A406:G406 I406 A472:I1063 A471:G471 I471 A290:I405 A289:G289 I289 A12:I18 A11:F11 H11:I11" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I10 A20:I24 A19:G19 I19 A26:I28 A25:G25 I25 A30:I37 A29:G29 I29 A39:I59 A38:G38 I38 A61:I140 A60:G60 I60 A142:I146 A141:G141 I141 A148:I209 A147:G147 I147 A407:I470 A406:G406 I406 A472:I1063 A471:G471 I471 A290:I319 A289:G289 I289 A12:I18 A11:F11 H11:I11 A211:I249 A210:G210 I210 A251:I253 A250:G250 I250 A255:I288 A254:G254 I254 A321:I391 A320:G320 I320 A393:I405 A392:G392 I392" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9541" uniqueCount="2334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9538" uniqueCount="2334">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7402,9 +7402,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>91</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>106</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>106</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>130</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>141</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>141</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>141</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>154</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>154</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>154</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>154</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>154</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>188</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>188</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>188</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>188</v>
       </c>
@@ -8680,7 +8680,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>188</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>214</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>214</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>214</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>227</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>227</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>227</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>227</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>227</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>227</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>227</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>210</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>210</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>210</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>210</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>210</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>210</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>276</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>282</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>282</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -9376,7 +9376,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>288</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>288</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>288</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>288</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>288</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>288</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>288</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>288</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>312</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>317</v>
       </c>
@@ -9666,7 +9666,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>317</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>317</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>254</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>254</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>337</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>337</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>342</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>342</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>342</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>342</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>342</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>253</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>253</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>253</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>253</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>253</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>367</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>367</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>367</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>382</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>382</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>382</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>382</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>382</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>382</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>382</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>162</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>162</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>162</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>162</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>162</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>162</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>162</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>162</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>162</v>
       </c>
@@ -10710,7 +10710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>421</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>421</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>429</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>429</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>429</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>429</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>429</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>429</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>446</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>446</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>446</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>446</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>446</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>459</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>459</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>459</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>459</v>
       </c>
@@ -11203,7 +11203,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>459</v>
       </c>
@@ -11232,7 +11232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>459</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>477</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>477</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>477</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>486</v>
       </c>
@@ -11377,7 +11377,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>486</v>
       </c>
@@ -11406,7 +11406,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>486</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>486</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>486</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>486</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>486</v>
       </c>
@@ -11551,7 +11551,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>486</v>
       </c>
@@ -11580,7 +11580,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>486</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>509</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>512</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>512</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>512</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>512</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>512</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>523</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>523</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>530</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>530</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>530</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>530</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>530</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>530</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>530</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>530</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>530</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>530</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>150</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>150</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>150</v>
       </c>
@@ -12218,7 +12218,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>563</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>563</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>563</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>563</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>563</v>
       </c>
@@ -12363,7 +12363,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>563</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>563</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>563</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>563</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>563</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>590</v>
       </c>
@@ -12537,7 +12537,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>590</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>590</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>590</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>590</v>
       </c>
@@ -12653,7 +12653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>590</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>603</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>606</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>606</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>606</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>606</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>606</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>606</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>606</v>
       </c>
@@ -12914,7 +12914,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>606</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>295</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>295</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>295</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>295</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>295</v>
       </c>
@@ -13088,7 +13088,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>295</v>
       </c>
@@ -13117,7 +13117,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>295</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>295</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>295</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>295</v>
       </c>
@@ -13233,7 +13233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>653</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>653</v>
       </c>
@@ -13291,7 +13291,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>653</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>653</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>653</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>664</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>664</v>
       </c>
@@ -13436,7 +13436,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>664</v>
       </c>
@@ -13465,7 +13465,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>664</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>664</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>683</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>683</v>
       </c>
@@ -13581,7 +13581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>683</v>
       </c>
@@ -13610,7 +13610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>683</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>683</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>436</v>
       </c>
@@ -13697,7 +13697,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>436</v>
       </c>
@@ -13726,7 +13726,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>436</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>436</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>707</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>707</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>707</v>
       </c>
@@ -13871,7 +13871,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>707</v>
       </c>
@@ -13900,7 +13900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>707</v>
       </c>
@@ -13929,7 +13929,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>707</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>720</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>723</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>723</v>
       </c>
@@ -14045,7 +14045,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>723</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>723</v>
       </c>
@@ -14103,7 +14103,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>723</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>723</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>723</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>736</v>
       </c>
@@ -14219,7 +14219,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>736</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>736</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>736</v>
       </c>
@@ -14306,7 +14306,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>736</v>
       </c>
@@ -14335,7 +14335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>736</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>749</v>
       </c>
@@ -14393,7 +14393,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>749</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>749</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>749</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>749</v>
       </c>
@@ -14509,7 +14509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>749</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>749</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>749</v>
       </c>
@@ -14596,7 +14596,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>749</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>749</v>
       </c>
@@ -14654,7 +14654,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>749</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>749</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>749</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>780</v>
       </c>
@@ -14770,7 +14770,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>780</v>
       </c>
@@ -14799,7 +14799,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>780</v>
       </c>
@@ -14828,7 +14828,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>780</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>780</v>
       </c>
@@ -14886,7 +14886,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>780</v>
       </c>
@@ -14915,7 +14915,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>780</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>780</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>780</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>780</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>780</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>780</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>380</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>380</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>380</v>
       </c>
@@ -15176,7 +15176,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>380</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>380</v>
       </c>
@@ -15234,7 +15234,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>380</v>
       </c>
@@ -15263,7 +15263,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>380</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>380</v>
       </c>
@@ -15321,7 +15321,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>380</v>
       </c>
@@ -15350,7 +15350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>380</v>
       </c>
@@ -15379,7 +15379,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>380</v>
       </c>
@@ -15408,7 +15408,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>380</v>
       </c>
@@ -15437,7 +15437,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>834</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>834</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>839</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>839</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>839</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>849</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>849</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>849</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>849</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>849</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>849</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>849</v>
       </c>
@@ -15785,7 +15785,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>849</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>757</v>
       </c>
@@ -15843,7 +15843,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>757</v>
       </c>
@@ -15872,7 +15872,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>757</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>757</v>
       </c>
@@ -15930,7 +15930,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>757</v>
       </c>
@@ -15959,7 +15959,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>757</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>757</v>
       </c>
@@ -16046,7 +16046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>757</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>888</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>888</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>888</v>
       </c>
@@ -16162,7 +16162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>888</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>888</v>
       </c>
@@ -16220,7 +16220,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>888</v>
       </c>
@@ -16249,7 +16249,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>888</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>888</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>888</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>888</v>
       </c>
@@ -16365,7 +16365,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>908</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>908</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>908</v>
       </c>
@@ -16452,7 +16452,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>908</v>
       </c>
@@ -16481,7 +16481,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>908</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>908</v>
       </c>
@@ -16539,7 +16539,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>908</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>908</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>908</v>
       </c>
@@ -16626,7 +16626,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>908</v>
       </c>
@@ -16655,7 +16655,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>908</v>
       </c>
@@ -16684,7 +16684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>908</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>908</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>908</v>
       </c>
@@ -16771,7 +16771,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>942</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>942</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>249</v>
       </c>
@@ -16858,7 +16858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>249</v>
       </c>
@@ -16887,7 +16887,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>249</v>
       </c>
@@ -16916,7 +16916,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>249</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>249</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>249</v>
       </c>
@@ -17003,7 +17003,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>249</v>
       </c>
@@ -17032,7 +17032,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>249</v>
       </c>
@@ -17061,7 +17061,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>249</v>
       </c>
@@ -17090,7 +17090,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>964</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>964</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>964</v>
       </c>
@@ -17177,7 +17177,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>964</v>
       </c>
@@ -17206,7 +17206,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>964</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>964</v>
       </c>
@@ -17264,7 +17264,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>964</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>963</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>963</v>
       </c>
@@ -17351,7 +17351,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>963</v>
       </c>
@@ -17380,7 +17380,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>963</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>963</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>963</v>
       </c>
@@ -17467,7 +17467,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>963</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>963</v>
       </c>
@@ -17525,7 +17525,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>963</v>
       </c>
@@ -17554,7 +17554,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>767</v>
       </c>
@@ -17583,7 +17583,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>767</v>
       </c>
@@ -17612,7 +17612,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>767</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>767</v>
       </c>
@@ -17670,7 +17670,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>767</v>
       </c>
@@ -17699,7 +17699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>767</v>
       </c>
@@ -17728,7 +17728,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1013</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1013</v>
       </c>
@@ -17786,7 +17786,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1013</v>
       </c>
@@ -17815,7 +17815,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1013</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1013</v>
       </c>
@@ -17873,7 +17873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1013</v>
       </c>
@@ -17902,7 +17902,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1013</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1013</v>
       </c>
@@ -17960,7 +17960,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1013</v>
       </c>
@@ -17989,7 +17989,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1013</v>
       </c>
@@ -18018,7 +18018,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1013</v>
       </c>
@@ -18047,7 +18047,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1013</v>
       </c>
@@ -18076,7 +18076,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1013</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1013</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1013</v>
       </c>
@@ -18163,7 +18163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1013</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1013</v>
       </c>
@@ -18221,7 +18221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1047</v>
       </c>
@@ -18250,7 +18250,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1051</v>
       </c>
@@ -18279,7 +18279,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1051</v>
       </c>
@@ -18308,7 +18308,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1051</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1051</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1051</v>
       </c>
@@ -18395,7 +18395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1051</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1051</v>
       </c>
@@ -18453,7 +18453,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1065</v>
       </c>
@@ -18482,7 +18482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1065</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1065</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1065</v>
       </c>
@@ -18569,7 +18569,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1065</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1065</v>
       </c>
@@ -18627,7 +18627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1080</v>
       </c>
@@ -18656,7 +18656,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1080</v>
       </c>
@@ -18685,7 +18685,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1080</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1080</v>
       </c>
@@ -18743,7 +18743,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1080</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1080</v>
       </c>
@@ -18801,7 +18801,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1080</v>
       </c>
@@ -18830,7 +18830,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1080</v>
       </c>
@@ -18859,7 +18859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1080</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1102</v>
       </c>
@@ -18917,7 +18917,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1102</v>
       </c>
@@ -18946,7 +18946,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1102</v>
       </c>
@@ -18975,7 +18975,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1102</v>
       </c>
@@ -19004,7 +19004,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1102</v>
       </c>
@@ -19033,7 +19033,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1102</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1102</v>
       </c>
@@ -19091,7 +19091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1102</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1102</v>
       </c>
@@ -19149,7 +19149,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1117</v>
       </c>
@@ -19178,7 +19178,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1117</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1117</v>
       </c>
@@ -19236,7 +19236,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1117</v>
       </c>
@@ -19265,7 +19265,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1117</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1117</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1117</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1117</v>
       </c>
@@ -19381,7 +19381,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1117</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1117</v>
       </c>
@@ -19439,7 +19439,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1117</v>
       </c>
@@ -19468,7 +19468,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1117</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1117</v>
       </c>
@@ -19526,7 +19526,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1142</v>
       </c>
@@ -19555,7 +19555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1144</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>624</v>
       </c>
@@ -19613,7 +19613,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>624</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -19700,7 +19700,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -19729,7 +19729,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -19787,7 +19787,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -19816,7 +19816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -19903,7 +19903,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -19990,7 +19990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -20048,7 +20048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -20077,7 +20077,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -20135,7 +20135,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -20164,7 +20164,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -20222,7 +20222,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -20251,7 +20251,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -20280,7 +20280,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -20309,7 +20309,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -20367,7 +20367,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20425,7 +20425,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20454,7 +20454,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20483,7 +20483,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20512,7 +20512,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20541,7 +20541,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20599,7 +20599,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20657,7 +20657,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20686,7 +20686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20744,7 +20744,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20773,7 +20773,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20802,7 +20802,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20860,7 +20860,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20889,7 +20889,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20918,7 +20918,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -20947,7 +20947,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -21005,7 +21005,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21034,7 +21034,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21063,7 +21063,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21121,7 +21121,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21179,7 +21179,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21266,7 +21266,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21295,7 +21295,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21353,7 +21353,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21375,14 +21375,14 @@
       <c r="G482" t="s">
         <v>451</v>
       </c>
-      <c r="H482" t="s">
-        <v>16</v>
+      <c r="H482" s="1">
+        <v>46123</v>
       </c>
       <c r="I482" t="s">
         <v>1280</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21411,7 +21411,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21440,7 +21440,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21498,7 +21498,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21527,7 +21527,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21585,7 +21585,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21614,7 +21614,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21643,7 +21643,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21701,7 +21701,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21730,7 +21730,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21788,7 +21788,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21817,7 +21817,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21875,7 +21875,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21904,7 +21904,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21933,7 +21933,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -21962,7 +21962,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22020,7 +22020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22049,7 +22049,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22107,7 +22107,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22136,7 +22136,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22165,7 +22165,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22223,7 +22223,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22252,7 +22252,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22281,7 +22281,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22310,7 +22310,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22339,7 +22339,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22397,7 +22397,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22426,7 +22426,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22484,7 +22484,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22513,7 +22513,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22571,7 +22571,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22600,7 +22600,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22629,7 +22629,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22658,7 +22658,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22687,7 +22687,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22716,7 +22716,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22745,7 +22745,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22774,7 +22774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22832,7 +22832,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22861,7 +22861,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22890,7 +22890,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22919,7 +22919,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -22977,7 +22977,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -23006,7 +23006,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23035,7 +23035,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23064,7 +23064,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23093,7 +23093,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23122,7 +23122,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23151,7 +23151,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23180,7 +23180,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23209,7 +23209,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23267,7 +23267,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23296,7 +23296,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23325,7 +23325,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23354,7 +23354,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23383,7 +23383,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23441,7 +23441,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23470,7 +23470,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23499,7 +23499,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23528,7 +23528,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23557,7 +23557,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23586,7 +23586,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23615,7 +23615,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23644,7 +23644,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23673,7 +23673,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23731,7 +23731,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23760,7 +23760,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23789,7 +23789,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23818,7 +23818,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23847,7 +23847,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23876,7 +23876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23905,7 +23905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23934,7 +23934,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -23963,7 +23963,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -24021,7 +24021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -24050,7 +24050,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -24079,7 +24079,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -24108,7 +24108,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24137,7 +24137,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24166,7 +24166,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24195,7 +24195,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24224,7 +24224,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24253,7 +24253,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24282,7 +24282,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24311,7 +24311,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24340,7 +24340,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24369,7 +24369,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24398,7 +24398,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24427,7 +24427,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24456,7 +24456,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24485,7 +24485,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24514,7 +24514,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24543,7 +24543,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24572,7 +24572,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24601,7 +24601,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24659,7 +24659,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24688,7 +24688,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24717,7 +24717,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24746,7 +24746,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24775,7 +24775,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24804,7 +24804,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24862,7 +24862,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24891,7 +24891,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -24949,7 +24949,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -24978,7 +24978,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -25007,7 +25007,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -25036,7 +25036,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -25065,7 +25065,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -25094,7 +25094,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -25123,7 +25123,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25152,7 +25152,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25181,7 +25181,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25210,7 +25210,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25239,7 +25239,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25268,7 +25268,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25297,7 +25297,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25326,7 +25326,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25355,7 +25355,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25384,7 +25384,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25413,7 +25413,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25442,7 +25442,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25471,7 +25471,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25500,7 +25500,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25529,7 +25529,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25558,7 +25558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25587,7 +25587,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25616,7 +25616,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25645,7 +25645,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25674,7 +25674,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25703,7 +25703,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25732,7 +25732,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25761,7 +25761,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25790,7 +25790,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25819,7 +25819,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25848,7 +25848,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25877,7 +25877,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25935,7 +25935,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -25964,7 +25964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -25993,7 +25993,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -26022,7 +26022,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -26051,7 +26051,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -26080,7 +26080,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -26109,7 +26109,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26167,7 +26167,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26196,7 +26196,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26225,7 +26225,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26254,7 +26254,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26283,7 +26283,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26312,7 +26312,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26341,7 +26341,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26370,7 +26370,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26399,7 +26399,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26428,7 +26428,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26457,7 +26457,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26486,7 +26486,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26515,7 +26515,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26544,7 +26544,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26573,7 +26573,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26602,7 +26602,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26631,7 +26631,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26660,7 +26660,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26689,7 +26689,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26718,7 +26718,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26747,7 +26747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26776,7 +26776,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26805,7 +26805,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26834,7 +26834,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26863,7 +26863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26892,7 +26892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26921,7 +26921,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -26950,7 +26950,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -26979,7 +26979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -27008,7 +27008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -27037,7 +27037,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -27066,7 +27066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -27095,7 +27095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27124,7 +27124,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27153,7 +27153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27182,7 +27182,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27211,7 +27211,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27240,7 +27240,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27269,7 +27269,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27298,7 +27298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27327,7 +27327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27356,7 +27356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27385,7 +27385,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27414,7 +27414,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27443,7 +27443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27472,7 +27472,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27501,7 +27501,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27530,7 +27530,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27559,7 +27559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27588,7 +27588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27617,7 +27617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27646,7 +27646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27675,7 +27675,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27704,7 +27704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27733,7 +27733,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27762,7 +27762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27791,7 +27791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27820,7 +27820,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27849,7 +27849,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27878,7 +27878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27907,7 +27907,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27936,7 +27936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -27994,7 +27994,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -28023,7 +28023,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -28081,7 +28081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -28110,7 +28110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28139,7 +28139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28168,7 +28168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28197,7 +28197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28226,7 +28226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28255,7 +28255,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28284,7 +28284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28313,7 +28313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28342,7 +28342,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28371,7 +28371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28400,7 +28400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28429,7 +28429,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28458,7 +28458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28487,7 +28487,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28516,7 +28516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28545,7 +28545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28574,7 +28574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28603,7 +28603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28632,7 +28632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28661,7 +28661,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28690,7 +28690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28719,7 +28719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28748,7 +28748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28777,7 +28777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28806,7 +28806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28835,7 +28835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28864,7 +28864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28922,7 +28922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -28951,7 +28951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -28980,7 +28980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -29009,7 +29009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -29038,7 +29038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -29067,7 +29067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -29096,7 +29096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29125,7 +29125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29154,7 +29154,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29183,7 +29183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29212,7 +29212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29241,7 +29241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29270,7 +29270,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29299,7 +29299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29328,7 +29328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29357,7 +29357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29386,7 +29386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29415,7 +29415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29444,7 +29444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29502,7 +29502,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29531,7 +29531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29560,7 +29560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29618,7 +29618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29647,7 +29647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29676,7 +29676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29705,7 +29705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29734,7 +29734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29792,7 +29792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29821,7 +29821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29850,7 +29850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29879,7 +29879,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29906,7 +29906,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29935,7 +29935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -29964,7 +29964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -29993,7 +29993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -30022,7 +30022,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -30051,7 +30051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -30080,7 +30080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30167,7 +30167,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30196,7 +30196,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30225,7 +30225,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30254,7 +30254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30283,7 +30283,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30312,7 +30312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30341,7 +30341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30370,7 +30370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30399,7 +30399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30428,7 +30428,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30457,7 +30457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30486,7 +30486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30544,7 +30544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30573,7 +30573,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30602,7 +30602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30631,7 +30631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30660,7 +30660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30689,7 +30689,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30718,7 +30718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30747,7 +30747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30805,7 +30805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30834,7 +30834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30863,7 +30863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30892,7 +30892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30921,7 +30921,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -30950,7 +30950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -30979,7 +30979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -31008,7 +31008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -31037,7 +31037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -31066,7 +31066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -31095,7 +31095,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31153,7 +31153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31182,7 +31182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31211,7 +31211,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31240,7 +31240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31269,7 +31269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31298,7 +31298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31327,7 +31327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31356,7 +31356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31385,7 +31385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31414,7 +31414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31472,7 +31472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31501,7 +31501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31530,7 +31530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31559,7 +31559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31617,7 +31617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31646,7 +31646,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31675,7 +31675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31704,7 +31704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31733,7 +31733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31762,7 +31762,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31791,7 +31791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31820,7 +31820,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31849,7 +31849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31878,7 +31878,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31907,7 +31907,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31936,7 +31936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -31965,7 +31965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -31994,7 +31994,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -32023,7 +32023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -32052,7 +32052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -32081,7 +32081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32139,7 +32139,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32168,7 +32168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32197,7 +32197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32226,7 +32226,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32255,7 +32255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32284,7 +32284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>16</v>
       </c>
@@ -32313,7 +32313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>16</v>
       </c>
@@ -32342,7 +32342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>16</v>
       </c>
@@ -32371,7 +32371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>16</v>
       </c>
@@ -32400,7 +32400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>16</v>
       </c>
@@ -32429,7 +32429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>16</v>
       </c>
@@ -32458,7 +32458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>16</v>
       </c>
@@ -32487,7 +32487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>16</v>
       </c>
@@ -32516,7 +32516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>16</v>
       </c>
@@ -32545,7 +32545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>16</v>
       </c>
@@ -32574,7 +32574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>16</v>
       </c>
@@ -32603,7 +32603,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>16</v>
       </c>
@@ -32632,7 +32632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>16</v>
       </c>
@@ -32661,7 +32661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>16</v>
       </c>
@@ -32690,7 +32690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>16</v>
       </c>
@@ -32719,7 +32719,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>16</v>
       </c>
@@ -32748,7 +32748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>16</v>
       </c>
@@ -32777,7 +32777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>16</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>16</v>
       </c>
@@ -32835,7 +32835,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>16</v>
       </c>
@@ -32864,7 +32864,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>16</v>
       </c>
@@ -32893,7 +32893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>16</v>
       </c>
@@ -32922,7 +32922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>16</v>
       </c>
@@ -32951,7 +32951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>16</v>
       </c>
@@ -32980,7 +32980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>16</v>
       </c>
@@ -33009,7 +33009,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>16</v>
       </c>
@@ -33038,7 +33038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>16</v>
       </c>
@@ -33067,7 +33067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>16</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>16</v>
       </c>
@@ -33125,7 +33125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>16</v>
       </c>
@@ -33154,7 +33154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>16</v>
       </c>
@@ -33183,7 +33183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>16</v>
       </c>
@@ -33212,7 +33212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>16</v>
       </c>
@@ -33241,7 +33241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>16</v>
       </c>
@@ -33270,7 +33270,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>16</v>
       </c>
@@ -33299,7 +33299,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>16</v>
       </c>
@@ -33328,7 +33328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>16</v>
       </c>
@@ -33357,7 +33357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>16</v>
       </c>
@@ -33386,7 +33386,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>16</v>
       </c>
@@ -33415,7 +33415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>16</v>
       </c>
@@ -33444,7 +33444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>16</v>
       </c>
@@ -33473,7 +33473,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>9</v>
       </c>
@@ -33502,7 +33502,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>53</v>
       </c>
@@ -33531,7 +33531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>70</v>
       </c>
@@ -33560,7 +33560,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>91</v>
       </c>
@@ -33589,7 +33589,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>117</v>
       </c>
@@ -33618,7 +33618,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>154</v>
       </c>
@@ -33647,7 +33647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>210</v>
       </c>
@@ -33676,7 +33676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>2069</v>
       </c>
@@ -33705,7 +33705,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>276</v>
       </c>
@@ -33734,7 +33734,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>288</v>
       </c>
@@ -33763,7 +33763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>342</v>
       </c>
@@ -33792,7 +33792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>2077</v>
       </c>
@@ -33821,7 +33821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>523</v>
       </c>
@@ -33850,7 +33850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>523</v>
       </c>
@@ -33879,7 +33879,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>530</v>
       </c>
@@ -33908,7 +33908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>530</v>
       </c>
@@ -33937,7 +33937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>530</v>
       </c>
@@ -33966,7 +33966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>530</v>
       </c>
@@ -33995,7 +33995,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>150</v>
       </c>
@@ -34024,7 +34024,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>150</v>
       </c>
@@ -34053,7 +34053,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>150</v>
       </c>
@@ -34082,7 +34082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>606</v>
       </c>
@@ -34111,7 +34111,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>606</v>
       </c>
@@ -34140,7 +34140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>606</v>
       </c>
@@ -34169,7 +34169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>295</v>
       </c>
@@ -34198,7 +34198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>295</v>
       </c>
@@ -34227,7 +34227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>664</v>
       </c>
@@ -34256,7 +34256,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>683</v>
       </c>
@@ -34278,14 +34278,14 @@
       <c r="G927" t="s">
         <v>16</v>
       </c>
-      <c r="H927" t="s">
-        <v>16</v>
+      <c r="H927" s="1">
+        <v>46123</v>
       </c>
       <c r="I927" t="s">
         <v>1280</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>707</v>
       </c>
@@ -34314,7 +34314,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>723</v>
       </c>
@@ -34343,7 +34343,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>723</v>
       </c>
@@ -34372,7 +34372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>736</v>
       </c>
@@ -34401,7 +34401,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>749</v>
       </c>
@@ -34430,7 +34430,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>380</v>
       </c>
@@ -34459,7 +34459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>380</v>
       </c>
@@ -34488,7 +34488,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>380</v>
       </c>
@@ -34517,7 +34517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>380</v>
       </c>
@@ -34546,7 +34546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>845</v>
       </c>
@@ -34575,7 +34575,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>849</v>
       </c>
@@ -34604,7 +34604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>757</v>
       </c>
@@ -34633,7 +34633,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>757</v>
       </c>
@@ -34662,7 +34662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>757</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>888</v>
       </c>
@@ -34720,7 +34720,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>888</v>
       </c>
@@ -34749,7 +34749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>908</v>
       </c>
@@ -34778,7 +34778,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>908</v>
       </c>
@@ -34807,7 +34807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>908</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>249</v>
       </c>
@@ -34865,7 +34865,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>964</v>
       </c>
@@ -34894,7 +34894,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>964</v>
       </c>
@@ -34923,7 +34923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>963</v>
       </c>
@@ -34952,7 +34952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>963</v>
       </c>
@@ -34981,7 +34981,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>767</v>
       </c>
@@ -35010,7 +35010,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>1013</v>
       </c>
@@ -35039,7 +35039,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>1013</v>
       </c>
@@ -35068,7 +35068,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>1013</v>
       </c>
@@ -35097,7 +35097,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>1013</v>
       </c>
@@ -35126,7 +35126,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>1065</v>
       </c>
@@ -35155,7 +35155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>1080</v>
       </c>
@@ -35184,7 +35184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>1117</v>
       </c>
@@ -35213,7 +35213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>16</v>
       </c>
@@ -35242,7 +35242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>16</v>
       </c>
@@ -35271,7 +35271,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>16</v>
       </c>
@@ -35300,7 +35300,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>16</v>
       </c>
@@ -35329,7 +35329,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>16</v>
       </c>
@@ -35358,7 +35358,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>16</v>
       </c>
@@ -35387,7 +35387,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>16</v>
       </c>
@@ -35416,7 +35416,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>16</v>
       </c>
@@ -35445,7 +35445,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35474,7 +35474,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35503,7 +35503,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35532,7 +35532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35561,7 +35561,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35590,7 +35590,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35619,7 +35619,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35648,7 +35648,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35677,7 +35677,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35706,7 +35706,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35735,7 +35735,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35764,7 +35764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35793,7 +35793,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35851,7 +35851,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35880,7 +35880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35909,7 +35909,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35938,7 +35938,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -35967,7 +35967,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -35996,7 +35996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -36025,7 +36025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -36054,7 +36054,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -36083,7 +36083,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -36112,7 +36112,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36141,7 +36141,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36170,7 +36170,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36199,7 +36199,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36228,7 +36228,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36257,7 +36257,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36286,7 +36286,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36315,7 +36315,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36337,14 +36337,14 @@
       <c r="G998" t="s">
         <v>16</v>
       </c>
-      <c r="H998" t="s">
-        <v>16</v>
+      <c r="H998" s="1">
+        <v>46123</v>
       </c>
       <c r="I998" t="s">
         <v>1280</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36373,7 +36373,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36402,7 +36402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36431,7 +36431,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36460,7 +36460,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36489,7 +36489,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36518,7 +36518,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36547,7 +36547,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36576,7 +36576,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36605,7 +36605,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36634,7 +36634,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36663,7 +36663,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36692,7 +36692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36721,7 +36721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36750,7 +36750,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36779,7 +36779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36808,7 +36808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36837,7 +36837,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36866,7 +36866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36895,7 +36895,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36924,7 +36924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -36953,7 +36953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -36982,7 +36982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -37011,7 +37011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -37040,7 +37040,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -37069,7 +37069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -37098,7 +37098,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37127,7 +37127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37156,7 +37156,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37185,7 +37185,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37214,7 +37214,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37243,7 +37243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37272,7 +37272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37301,7 +37301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37330,7 +37330,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37359,7 +37359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37388,7 +37388,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37417,7 +37417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37446,7 +37446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37475,7 +37475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37504,7 +37504,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37533,7 +37533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37562,7 +37562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37591,7 +37591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37620,7 +37620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37649,7 +37649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37678,7 +37678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37707,7 +37707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37736,7 +37736,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37765,7 +37765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37794,7 +37794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37823,7 +37823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37852,7 +37852,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37881,7 +37881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37910,7 +37910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37939,7 +37939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -37968,7 +37968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -37997,7 +37997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -38026,7 +38026,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -38055,7 +38055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -38084,7 +38084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -38113,7 +38113,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38142,7 +38142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38171,7 +38171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38200,7 +38200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38233,7 +38233,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I9 A15:I17 A14 C14:I14 A777:I901 A776:F776 A19:I26 A18:F18 H18:I18 A11:F11 A10:F10 H10:I10 A13:I13 A12:F12 H12:I12 A28:I36 A27:F27 H27:I27 A38:I41 A37:F37 H37:I37 A292:I386 A291:F291 H291:I291 A150:I168 A149:F149 H149:I149 A401:I404 A400:F400 H400:I400 A210:I231 A208:F208 H208:I208 A252:I282 A251:F251 H251:I251 A903:I1063 A902:F902 H902:I902 A284:I290 A283:F283 H283:I283 A132:I148 A131:F131 H131:I131 A170:I192 A169:F169 H169:I169 A388:I399 A387:F387 H387:I387 A209:F209 H209:I209 A51:I111 A49:F49 H49:I49 A406:I775 A405:F405 H405:I405 A43:I48 A42:F42 H42:I42 A50:F50 H50:I50 A194:I207 A193:F193 H193 A233:I236 A232:F232 H232:I232 A113:I130 A112:F112 H112 H11:I11 A238:I250 A237:F237 H237:I237" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I9 A15:I17 A14 C14:I14 A777:I901 A776:F776 A19:I26 A18:F18 H18:I18 A11:F11 A10:F10 H10:I10 A13:I13 A12:F12 H12:I12 A28:I36 A27:F27 H27:I27 A38:I41 A37:F37 H37:I37 A292:I386 A291:F291 H291:I291 A150:I168 A149:F149 H149:I149 A401:I404 A400:F400 H400:I400 A210:I231 A208:F208 H208:I208 A252:I282 A251:F251 H251:I251 A903:I926 A902:F902 H902:I902 A284:I290 A283:F283 H283:I283 A132:I148 A131:F131 H131:I131 A170:I192 A169:F169 H169:I169 A388:I399 A387:F387 H387:I387 A209:F209 H209:I209 A51:I111 A49:F49 H49:I49 A406:I481 A405:F405 H405:I405 A43:I48 A42:F42 H42:I42 A50:F50 H50:I50 A194:I207 A193:F193 H193 A233:I236 A232:F232 H232:I232 A113:I130 A112:F112 H112 H11:I11 A238:I250 A237:F237 H237:I237 A483:I775 A482:G482 I482 A928:I997 A927:G927 I927 A999:I1063 A998:G998 I998" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9538" uniqueCount="2334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9537" uniqueCount="2334">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -22448,8 +22448,8 @@
       <c r="G519" t="s">
         <v>388</v>
       </c>
-      <c r="H519" t="s">
-        <v>16</v>
+      <c r="H519" s="1">
+        <v>46128</v>
       </c>
       <c r="I519" t="s">
         <v>1361</v>
@@ -38233,7 +38233,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I9 A15:I17 A14 C14:I14 A777:I901 A776:F776 A19:I26 A18:F18 H18:I18 A11:F11 A10:F10 H10:I10 A13:I13 A12:F12 H12:I12 A28:I36 A27:F27 H27:I27 A38:I41 A37:F37 H37:I37 A292:I386 A291:F291 H291:I291 A150:I168 A149:F149 H149:I149 A401:I404 A400:F400 H400:I400 A210:I231 A208:F208 H208:I208 A252:I282 A251:F251 H251:I251 A903:I926 A902:F902 H902:I902 A284:I290 A283:F283 H283:I283 A132:I148 A131:F131 H131:I131 A170:I192 A169:F169 H169:I169 A388:I399 A387:F387 H387:I387 A209:F209 H209:I209 A51:I111 A49:F49 H49:I49 A406:I481 A405:F405 H405:I405 A43:I48 A42:F42 H42:I42 A50:F50 H50:I50 A194:I207 A193:F193 H193 A233:I236 A232:F232 H232:I232 A113:I130 A112:F112 H112 H11:I11 A238:I250 A237:F237 H237:I237 A483:I775 A482:G482 I482 A928:I997 A927:G927 I927 A999:I1063 A998:G998 I998" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I9 A15:I17 A14 C14:I14 A777:I901 A776:F776 A19:I26 A18:F18 H18:I18 A11:F11 A10:F10 H10:I10 A13:I13 A12:F12 H12:I12 A28:I36 A27:F27 H27:I27 A38:I41 A37:F37 H37:I37 A292:I386 A291:F291 H291:I291 A150:I168 A149:F149 H149:I149 A401:I404 A400:F400 H400:I400 A210:I231 A208:F208 H208:I208 A252:I282 A251:F251 H251:I251 A903:I926 A902:F902 H902:I902 A284:I290 A283:F283 H283:I283 A132:I148 A131:F131 H131:I131 A170:I192 A169:F169 H169:I169 A388:I399 A387:F387 H387:I387 A209:F209 H209:I209 A51:I111 A49:F49 H49:I49 A406:I481 A405:F405 H405:I405 A43:I48 A42:F42 H42:I42 A50:F50 H50:I50 A194:I207 A193:F193 H193 A233:I236 A232:F232 H232:I232 A113:I130 A112:F112 H112 H11:I11 A238:I250 A237:F237 H237:I237 A483:I518 A482:G482 I482 A928:I997 A927:G927 I927 A999:I1063 A998:G998 I998 A520:I775 A519:G519 I519" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9545" uniqueCount="2343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9536" uniqueCount="2343">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7429,9 +7429,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>121</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>136</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>147</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>158</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>158</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -8439,14 +8439,14 @@
       <c r="G35" t="s">
         <v>112</v>
       </c>
-      <c r="H35" t="s">
-        <v>174</v>
+      <c r="H35" s="1">
+        <v>46135</v>
       </c>
       <c r="I35" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>170</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>170</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>182</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>182</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>182</v>
       </c>
@@ -8584,14 +8584,14 @@
       <c r="G40" t="s">
         <v>196</v>
       </c>
-      <c r="H40" t="s">
-        <v>174</v>
+      <c r="H40" s="1">
+        <v>46135</v>
       </c>
       <c r="I40" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>182</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>182</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>210</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>210</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>210</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>210</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>210</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>237</v>
       </c>
@@ -8932,14 +8932,14 @@
       <c r="G52" t="s">
         <v>240</v>
       </c>
-      <c r="H52" t="s">
-        <v>174</v>
+      <c r="H52" s="1">
+        <v>46135</v>
       </c>
       <c r="I52" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>237</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>237</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>247</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>247</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>247</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>247</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>247</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>247</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>247</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>233</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>233</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>233</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>233</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>233</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>289</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>295</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>295</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>295</v>
       </c>
@@ -9454,14 +9454,14 @@
       <c r="G70" t="s">
         <v>182</v>
       </c>
-      <c r="H70" t="s">
-        <v>174</v>
+      <c r="H70" s="1">
+        <v>46135</v>
       </c>
       <c r="I70" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>302</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>302</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>302</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>302</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>302</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>302</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>302</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>320</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>325</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>325</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>325</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>334</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>334</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>334</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>346</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>346</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>346</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>354</v>
       </c>
@@ -9983,7 +9983,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>354</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>354</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>354</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>354</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>354</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>374</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>374</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>374</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>374</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>387</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>387</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>393</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>393</v>
       </c>
@@ -10389,7 +10389,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>393</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>393</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>408</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>408</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>408</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>408</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>408</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>408</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>408</v>
       </c>
@@ -10650,7 +10650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>425</v>
       </c>
@@ -10679,7 +10679,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>425</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>425</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>425</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>425</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>425</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>425</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>425</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>425</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>450</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>450</v>
       </c>
@@ -10969,7 +10969,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>450</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>461</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>461</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>461</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>461</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>461</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>461</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>477</v>
       </c>
@@ -11201,7 +11201,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>477</v>
       </c>
@@ -11230,7 +11230,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>477</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>477</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>477</v>
       </c>
@@ -11317,7 +11317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>489</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>489</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>489</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>489</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>489</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>489</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>506</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>506</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>506</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>515</v>
       </c>
@@ -11607,7 +11607,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>515</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>515</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>515</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>515</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>515</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>515</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>515</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>515</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>536</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>539</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>539</v>
       </c>
@@ -11926,7 +11926,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>539</v>
       </c>
@@ -11948,14 +11948,14 @@
       <c r="G156" t="s">
         <v>65</v>
       </c>
-      <c r="H156" t="s">
-        <v>174</v>
+      <c r="H156" s="1">
+        <v>46135</v>
       </c>
       <c r="I156" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>539</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>539</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>550</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>550</v>
       </c>
@@ -12071,7 +12071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>557</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>557</v>
       </c>
@@ -12122,14 +12122,14 @@
       <c r="G162" t="s">
         <v>151</v>
       </c>
-      <c r="H162" t="s">
-        <v>174</v>
+      <c r="H162" s="1">
+        <v>46135</v>
       </c>
       <c r="I162" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>557</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>557</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>557</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>557</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>557</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>557</v>
       </c>
@@ -12303,7 +12303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>557</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>557</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>591</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>591</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>591</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>591</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>591</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>591</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>591</v>
       </c>
@@ -12651,7 +12651,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>591</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>591</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>591</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>618</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>618</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>618</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>618</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>618</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>618</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>630</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>634</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>634</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>634</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>634</v>
       </c>
@@ -13057,7 +13057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>634</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>634</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>634</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>634</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>652</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>652</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>652</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>652</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>652</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>652</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>652</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>652</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>652</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>652</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>679</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>679</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>679</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>679</v>
       </c>
@@ -13579,7 +13579,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>679</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>689</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>689</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>689</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>689</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>689</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>708</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>708</v>
       </c>
@@ -13811,7 +13811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>708</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>708</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>708</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>717</v>
       </c>
@@ -13927,7 +13927,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>717</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>717</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>717</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>732</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>732</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>732</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>732</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>732</v>
       </c>
@@ -14159,7 +14159,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>732</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>745</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>748</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>748</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>748</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>748</v>
       </c>
@@ -14333,7 +14333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>748</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>748</v>
       </c>
@@ -14391,7 +14391,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>748</v>
       </c>
@@ -14420,7 +14420,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>761</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>761</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>761</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>761</v>
       </c>
@@ -14536,7 +14536,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>761</v>
       </c>
@@ -14565,7 +14565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>761</v>
       </c>
@@ -14594,7 +14594,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>774</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>774</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>774</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>774</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>774</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>774</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>774</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>774</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>774</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>774</v>
       </c>
@@ -14884,7 +14884,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>774</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>774</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>774</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>805</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>805</v>
       </c>
@@ -15029,7 +15029,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>805</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>805</v>
       </c>
@@ -15087,7 +15087,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>805</v>
       </c>
@@ -15116,7 +15116,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>805</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>805</v>
       </c>
@@ -15174,7 +15174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>805</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>805</v>
       </c>
@@ -15232,7 +15232,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>805</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>805</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>805</v>
       </c>
@@ -15319,7 +15319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>406</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>406</v>
       </c>
@@ -15377,7 +15377,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>406</v>
       </c>
@@ -15406,7 +15406,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>406</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>406</v>
       </c>
@@ -15464,7 +15464,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>406</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>406</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>406</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>406</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>406</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>406</v>
       </c>
@@ -15638,7 +15638,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>406</v>
       </c>
@@ -15667,7 +15667,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>860</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>860</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>865</v>
       </c>
@@ -15754,7 +15754,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>865</v>
       </c>
@@ -15783,7 +15783,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>865</v>
       </c>
@@ -15812,7 +15812,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>875</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>875</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>875</v>
       </c>
@@ -15899,7 +15899,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>875</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>875</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>875</v>
       </c>
@@ -15986,7 +15986,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>875</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>782</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>782</v>
       </c>
@@ -16073,7 +16073,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>782</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>782</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>782</v>
       </c>
@@ -16160,7 +16160,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>782</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>782</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>782</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>782</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>913</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>913</v>
       </c>
@@ -16334,7 +16334,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>913</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>913</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>913</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>913</v>
       </c>
@@ -16450,7 +16450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>913</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>913</v>
       </c>
@@ -16508,7 +16508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>913</v>
       </c>
@@ -16537,7 +16537,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>913</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>932</v>
       </c>
@@ -16595,7 +16595,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>932</v>
       </c>
@@ -16624,7 +16624,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>932</v>
       </c>
@@ -16653,7 +16653,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>932</v>
       </c>
@@ -16682,7 +16682,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>932</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>932</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>932</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>932</v>
       </c>
@@ -16798,7 +16798,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>932</v>
       </c>
@@ -16827,7 +16827,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>932</v>
       </c>
@@ -16856,7 +16856,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>932</v>
       </c>
@@ -16885,7 +16885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>932</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>932</v>
       </c>
@@ -16943,7 +16943,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>932</v>
       </c>
@@ -16972,7 +16972,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>966</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>966</v>
       </c>
@@ -17030,7 +17030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>269</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>269</v>
       </c>
@@ -17088,7 +17088,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>269</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>269</v>
       </c>
@@ -17146,7 +17146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>269</v>
       </c>
@@ -17175,7 +17175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>269</v>
       </c>
@@ -17204,7 +17204,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>269</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>269</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>269</v>
       </c>
@@ -17291,7 +17291,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>988</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>988</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>988</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>988</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>988</v>
       </c>
@@ -17436,7 +17436,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>988</v>
       </c>
@@ -17465,7 +17465,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>988</v>
       </c>
@@ -17494,7 +17494,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>987</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>987</v>
       </c>
@@ -17552,7 +17552,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>987</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>987</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>987</v>
       </c>
@@ -17639,7 +17639,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>987</v>
       </c>
@@ -17668,7 +17668,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>987</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>987</v>
       </c>
@@ -17726,7 +17726,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>987</v>
       </c>
@@ -17755,7 +17755,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>792</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>792</v>
       </c>
@@ -17813,7 +17813,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>792</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>792</v>
       </c>
@@ -17871,7 +17871,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>792</v>
       </c>
@@ -17900,7 +17900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>792</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1036</v>
       </c>
@@ -17958,7 +17958,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1036</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1036</v>
       </c>
@@ -18016,7 +18016,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1036</v>
       </c>
@@ -18045,7 +18045,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1036</v>
       </c>
@@ -18074,7 +18074,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1036</v>
       </c>
@@ -18103,7 +18103,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1036</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1036</v>
       </c>
@@ -18161,7 +18161,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1036</v>
       </c>
@@ -18190,7 +18190,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1036</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1036</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1036</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1036</v>
       </c>
@@ -18306,7 +18306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1036</v>
       </c>
@@ -18335,7 +18335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1036</v>
       </c>
@@ -18364,7 +18364,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1036</v>
       </c>
@@ -18393,7 +18393,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1036</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1070</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>156</v>
       </c>
@@ -18480,7 +18480,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>156</v>
       </c>
@@ -18509,7 +18509,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>156</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>156</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>156</v>
       </c>
@@ -18596,7 +18596,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>156</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>156</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1088</v>
       </c>
@@ -18683,7 +18683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1088</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1088</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1088</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1088</v>
       </c>
@@ -18799,7 +18799,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1088</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1103</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1103</v>
       </c>
@@ -18886,7 +18886,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1103</v>
       </c>
@@ -18915,7 +18915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1103</v>
       </c>
@@ -18944,7 +18944,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1103</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1103</v>
       </c>
@@ -19002,7 +19002,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1103</v>
       </c>
@@ -19031,7 +19031,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1103</v>
       </c>
@@ -19060,7 +19060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1103</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1124</v>
       </c>
@@ -19118,7 +19118,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1124</v>
       </c>
@@ -19147,7 +19147,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1124</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1124</v>
       </c>
@@ -19205,7 +19205,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1124</v>
       </c>
@@ -19234,7 +19234,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1124</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1124</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1124</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1124</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1139</v>
       </c>
@@ -19379,7 +19379,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1139</v>
       </c>
@@ -19408,7 +19408,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1139</v>
       </c>
@@ -19437,7 +19437,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1139</v>
       </c>
@@ -19466,7 +19466,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1139</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1139</v>
       </c>
@@ -19524,7 +19524,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1139</v>
       </c>
@@ -19553,7 +19553,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1139</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1139</v>
       </c>
@@ -19604,14 +19604,14 @@
       <c r="G420" t="s">
         <v>302</v>
       </c>
-      <c r="H420" t="s">
-        <v>174</v>
+      <c r="H420" s="1">
+        <v>46135</v>
       </c>
       <c r="I420" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1139</v>
       </c>
@@ -19640,7 +19640,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1139</v>
       </c>
@@ -19669,7 +19669,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1139</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1139</v>
       </c>
@@ -19727,7 +19727,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>633</v>
       </c>
@@ -19756,7 +19756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1166</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1170</v>
       </c>
@@ -19814,7 +19814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1170</v>
       </c>
@@ -19843,7 +19843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -19901,7 +19901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -19930,7 +19930,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -20017,7 +20017,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -20075,7 +20075,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -20104,7 +20104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -20133,7 +20133,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -20162,7 +20162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -20220,7 +20220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -20278,7 +20278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -20365,7 +20365,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -20423,7 +20423,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20452,7 +20452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20539,7 +20539,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20626,7 +20626,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20684,7 +20684,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20713,7 +20713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20829,7 +20829,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -20974,7 +20974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -21032,7 +21032,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21119,7 +21119,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21148,7 +21148,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21206,7 +21206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21235,7 +21235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21293,7 +21293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21322,7 +21322,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21351,7 +21351,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21409,7 +21409,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21467,7 +21467,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21518,14 +21518,14 @@
       <c r="G486" t="s">
         <v>366</v>
       </c>
-      <c r="H486" t="s">
-        <v>174</v>
+      <c r="H486" s="1">
+        <v>46135</v>
       </c>
       <c r="I486" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21641,7 +21641,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21670,7 +21670,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21699,7 +21699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21728,7 +21728,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21786,7 +21786,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21815,7 +21815,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21844,7 +21844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21873,7 +21873,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21902,7 +21902,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21931,7 +21931,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21960,7 +21960,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -21989,7 +21989,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22047,7 +22047,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22076,7 +22076,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22105,7 +22105,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22163,7 +22163,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22192,7 +22192,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22279,7 +22279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22308,7 +22308,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22337,7 +22337,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22366,7 +22366,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22395,7 +22395,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22453,7 +22453,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22482,7 +22482,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22511,7 +22511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22540,7 +22540,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22569,7 +22569,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22598,7 +22598,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22627,7 +22627,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22685,7 +22685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22772,7 +22772,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22801,7 +22801,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22830,7 +22830,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22859,7 +22859,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22888,7 +22888,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22946,7 +22946,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23062,7 +23062,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23120,7 +23120,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23149,7 +23149,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23207,7 +23207,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23236,7 +23236,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23294,7 +23294,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23381,7 +23381,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23410,7 +23410,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23439,7 +23439,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23468,7 +23468,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23497,7 +23497,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23526,7 +23526,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23555,7 +23555,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23584,7 +23584,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23613,7 +23613,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23642,7 +23642,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23671,7 +23671,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23729,7 +23729,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23787,7 +23787,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23816,7 +23816,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23845,7 +23845,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23874,7 +23874,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23903,7 +23903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23932,7 +23932,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23961,7 +23961,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -23990,7 +23990,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -24048,7 +24048,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -24077,7 +24077,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -24106,7 +24106,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -24135,7 +24135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24164,7 +24164,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24251,7 +24251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24338,7 +24338,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24367,7 +24367,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24396,7 +24396,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24425,7 +24425,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24454,7 +24454,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24483,7 +24483,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24512,7 +24512,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24541,7 +24541,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24570,7 +24570,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24599,7 +24599,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24628,7 +24628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24657,7 +24657,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24686,7 +24686,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24715,7 +24715,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24744,7 +24744,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24773,7 +24773,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24802,7 +24802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24831,7 +24831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24860,7 +24860,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24889,7 +24889,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24918,7 +24918,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24947,7 +24947,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -24976,7 +24976,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -25005,7 +25005,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -25034,7 +25034,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -25063,7 +25063,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -25092,7 +25092,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -25121,7 +25121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -25150,7 +25150,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25179,7 +25179,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25266,7 +25266,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25295,7 +25295,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25324,7 +25324,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25353,7 +25353,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25382,7 +25382,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25411,7 +25411,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25440,7 +25440,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25469,7 +25469,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25498,7 +25498,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25527,7 +25527,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25556,7 +25556,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25585,7 +25585,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25614,7 +25614,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25643,7 +25643,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25730,7 +25730,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25759,7 +25759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25788,7 +25788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25817,7 +25817,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25846,7 +25846,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25875,7 +25875,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25904,7 +25904,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25933,7 +25933,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25962,7 +25962,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -26020,7 +26020,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -26049,7 +26049,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -26078,7 +26078,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -26107,7 +26107,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -26136,7 +26136,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26165,7 +26165,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26194,7 +26194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26223,7 +26223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26252,7 +26252,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26281,7 +26281,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26310,7 +26310,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26339,7 +26339,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26368,7 +26368,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26397,7 +26397,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26426,7 +26426,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26455,7 +26455,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26484,7 +26484,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26513,7 +26513,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26571,7 +26571,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26600,7 +26600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26629,7 +26629,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26658,7 +26658,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26687,7 +26687,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26716,7 +26716,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26745,7 +26745,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26774,7 +26774,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26803,7 +26803,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26832,7 +26832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26861,7 +26861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26890,7 +26890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26919,7 +26919,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26948,7 +26948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -26977,7 +26977,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -27006,7 +27006,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -27035,7 +27035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -27064,7 +27064,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -27093,7 +27093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -27122,7 +27122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27151,7 +27151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27180,7 +27180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27209,7 +27209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27238,7 +27238,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27267,7 +27267,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27296,7 +27296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27325,7 +27325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27354,7 +27354,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27383,7 +27383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27441,7 +27441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27470,7 +27470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27499,7 +27499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27528,7 +27528,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27557,7 +27557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27586,7 +27586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27615,7 +27615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27644,7 +27644,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27673,7 +27673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27702,7 +27702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27760,7 +27760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27789,7 +27789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27818,7 +27818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27847,7 +27847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27876,7 +27876,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27905,7 +27905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27934,7 +27934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27963,7 +27963,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -27992,7 +27992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -28021,7 +28021,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -28050,7 +28050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -28108,7 +28108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -28137,7 +28137,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28166,7 +28166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28195,7 +28195,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28224,7 +28224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28282,7 +28282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28311,7 +28311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28340,7 +28340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28369,7 +28369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28398,7 +28398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28427,7 +28427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28456,7 +28456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28485,7 +28485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28514,7 +28514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28543,7 +28543,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28572,7 +28572,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28601,7 +28601,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28630,7 +28630,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28659,7 +28659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28688,7 +28688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28717,7 +28717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28746,7 +28746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28775,7 +28775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28804,7 +28804,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28833,7 +28833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28862,7 +28862,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28891,7 +28891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28920,7 +28920,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28949,7 +28949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -28978,7 +28978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -29007,7 +29007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -29036,7 +29036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -29065,7 +29065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -29094,7 +29094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -29123,7 +29123,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29152,7 +29152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29181,7 +29181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29210,7 +29210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29239,7 +29239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29268,7 +29268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29297,7 +29297,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29326,7 +29326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29355,7 +29355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29384,7 +29384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29413,7 +29413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29442,7 +29442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29471,7 +29471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29500,7 +29500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29529,7 +29529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29558,7 +29558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29587,7 +29587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29616,7 +29616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29645,7 +29645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29674,7 +29674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29703,7 +29703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29732,7 +29732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29761,7 +29761,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29790,7 +29790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29819,7 +29819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29848,7 +29848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29877,7 +29877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29906,7 +29906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29935,7 +29935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29964,7 +29964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -29993,7 +29993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -30022,7 +30022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -30051,7 +30051,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -30080,7 +30080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30167,7 +30167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30196,7 +30196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30225,7 +30225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30254,7 +30254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30283,7 +30283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30312,7 +30312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30341,7 +30341,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30370,7 +30370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30399,7 +30399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30428,7 +30428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30457,7 +30457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30486,7 +30486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30544,7 +30544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30573,7 +30573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30602,7 +30602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30631,7 +30631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30660,7 +30660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30689,7 +30689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30718,7 +30718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30747,7 +30747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30805,7 +30805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30834,7 +30834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30863,7 +30863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30892,7 +30892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30921,7 +30921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30950,7 +30950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -30979,7 +30979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -31008,7 +31008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -31037,7 +31037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -31066,7 +31066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -31095,7 +31095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31153,7 +31153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31182,7 +31182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31211,7 +31211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31240,7 +31240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31269,7 +31269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31298,7 +31298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31327,7 +31327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31356,7 +31356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31385,7 +31385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31414,7 +31414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31472,7 +31472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31501,7 +31501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31530,7 +31530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31559,7 +31559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31617,7 +31617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31646,7 +31646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31675,7 +31675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31704,7 +31704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31733,7 +31733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31762,7 +31762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31791,7 +31791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31820,7 +31820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31849,7 +31849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31878,7 +31878,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31907,7 +31907,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31936,7 +31936,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31965,7 +31965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -31994,7 +31994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -32023,7 +32023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -32052,7 +32052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -32081,7 +32081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -32139,7 +32139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32168,7 +32168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32197,7 +32197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32226,7 +32226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32255,7 +32255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32284,7 +32284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32313,7 +32313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>16</v>
       </c>
@@ -32342,7 +32342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>16</v>
       </c>
@@ -32371,7 +32371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>16</v>
       </c>
@@ -32400,7 +32400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>16</v>
       </c>
@@ -32429,7 +32429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>16</v>
       </c>
@@ -32458,7 +32458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>16</v>
       </c>
@@ -32487,7 +32487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>16</v>
       </c>
@@ -32516,7 +32516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>16</v>
       </c>
@@ -32545,7 +32545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>16</v>
       </c>
@@ -32574,7 +32574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>16</v>
       </c>
@@ -32603,7 +32603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>16</v>
       </c>
@@ -32632,7 +32632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>16</v>
       </c>
@@ -32661,7 +32661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>16</v>
       </c>
@@ -32690,7 +32690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>16</v>
       </c>
@@ -32719,7 +32719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>16</v>
       </c>
@@ -32748,7 +32748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>16</v>
       </c>
@@ -32777,7 +32777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>16</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>16</v>
       </c>
@@ -32835,7 +32835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>16</v>
       </c>
@@ -32864,7 +32864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>16</v>
       </c>
@@ -32893,7 +32893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>16</v>
       </c>
@@ -32922,7 +32922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>16</v>
       </c>
@@ -32951,7 +32951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>16</v>
       </c>
@@ -32980,7 +32980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>16</v>
       </c>
@@ -33009,7 +33009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>16</v>
       </c>
@@ -33038,7 +33038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>16</v>
       </c>
@@ -33067,7 +33067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>16</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>16</v>
       </c>
@@ -33125,7 +33125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>16</v>
       </c>
@@ -33154,7 +33154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>16</v>
       </c>
@@ -33183,7 +33183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>16</v>
       </c>
@@ -33212,7 +33212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>16</v>
       </c>
@@ -33241,7 +33241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>16</v>
       </c>
@@ -33270,7 +33270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>16</v>
       </c>
@@ -33299,7 +33299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>16</v>
       </c>
@@ -33328,7 +33328,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>16</v>
       </c>
@@ -33357,7 +33357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>16</v>
       </c>
@@ -33386,7 +33386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>16</v>
       </c>
@@ -33415,7 +33415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>16</v>
       </c>
@@ -33444,7 +33444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>16</v>
       </c>
@@ -33473,7 +33473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>9</v>
       </c>
@@ -33502,7 +33502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>9</v>
       </c>
@@ -33531,7 +33531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>18</v>
       </c>
@@ -33560,7 +33560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>47</v>
       </c>
@@ -33589,7 +33589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>59</v>
       </c>
@@ -33618,7 +33618,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>88</v>
       </c>
@@ -33647,7 +33647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>121</v>
       </c>
@@ -33676,7 +33676,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>147</v>
       </c>
@@ -33705,7 +33705,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>182</v>
       </c>
@@ -33727,14 +33727,14 @@
       <c r="G907" t="s">
         <v>16</v>
       </c>
-      <c r="H907" t="s">
-        <v>174</v>
+      <c r="H907" s="1">
+        <v>46135</v>
       </c>
       <c r="I907" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>182</v>
       </c>
@@ -33763,7 +33763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>233</v>
       </c>
@@ -33792,7 +33792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>289</v>
       </c>
@@ -33821,7 +33821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>302</v>
       </c>
@@ -33850,7 +33850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>354</v>
       </c>
@@ -33879,7 +33879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>387</v>
       </c>
@@ -33908,7 +33908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>408</v>
       </c>
@@ -33937,7 +33937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>550</v>
       </c>
@@ -33966,7 +33966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>550</v>
       </c>
@@ -33995,7 +33995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>557</v>
       </c>
@@ -34024,7 +34024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>557</v>
       </c>
@@ -34053,7 +34053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>557</v>
       </c>
@@ -34082,7 +34082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>557</v>
       </c>
@@ -34111,7 +34111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>39</v>
       </c>
@@ -34140,7 +34140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>39</v>
       </c>
@@ -34169,7 +34169,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>39</v>
       </c>
@@ -34198,7 +34198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>634</v>
       </c>
@@ -34227,7 +34227,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>634</v>
       </c>
@@ -34256,7 +34256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>634</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>652</v>
       </c>
@@ -34314,7 +34314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>652</v>
       </c>
@@ -34343,7 +34343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>689</v>
       </c>
@@ -34372,7 +34372,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>708</v>
       </c>
@@ -34401,7 +34401,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>732</v>
       </c>
@@ -34430,7 +34430,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>748</v>
       </c>
@@ -34459,7 +34459,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>748</v>
       </c>
@@ -34488,7 +34488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>761</v>
       </c>
@@ -34517,7 +34517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>774</v>
       </c>
@@ -34546,7 +34546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>406</v>
       </c>
@@ -34575,7 +34575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>406</v>
       </c>
@@ -34604,7 +34604,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>406</v>
       </c>
@@ -34633,7 +34633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>406</v>
       </c>
@@ -34662,7 +34662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>871</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>875</v>
       </c>
@@ -34720,7 +34720,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>875</v>
       </c>
@@ -34749,7 +34749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>782</v>
       </c>
@@ -34778,7 +34778,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>782</v>
       </c>
@@ -34807,7 +34807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>782</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>913</v>
       </c>
@@ -34865,7 +34865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>913</v>
       </c>
@@ -34894,7 +34894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>932</v>
       </c>
@@ -34923,7 +34923,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>932</v>
       </c>
@@ -34952,7 +34952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>932</v>
       </c>
@@ -34981,7 +34981,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>269</v>
       </c>
@@ -35010,7 +35010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>988</v>
       </c>
@@ -35039,7 +35039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>988</v>
       </c>
@@ -35068,7 +35068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>987</v>
       </c>
@@ -35097,7 +35097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>987</v>
       </c>
@@ -35126,7 +35126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>792</v>
       </c>
@@ -35155,7 +35155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>1036</v>
       </c>
@@ -35184,7 +35184,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>1036</v>
       </c>
@@ -35213,7 +35213,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>1036</v>
       </c>
@@ -35242,7 +35242,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>1036</v>
       </c>
@@ -35271,7 +35271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>1088</v>
       </c>
@@ -35300,7 +35300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>1103</v>
       </c>
@@ -35329,7 +35329,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>1139</v>
       </c>
@@ -35358,7 +35358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>16</v>
       </c>
@@ -35387,7 +35387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>16</v>
       </c>
@@ -35416,7 +35416,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>16</v>
       </c>
@@ -35445,7 +35445,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>16</v>
       </c>
@@ -35474,7 +35474,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35503,7 +35503,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35532,7 +35532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35561,7 +35561,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35590,7 +35590,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35619,7 +35619,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35648,7 +35648,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35677,7 +35677,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35706,7 +35706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35735,7 +35735,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35764,7 +35764,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35793,7 +35793,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35851,7 +35851,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35880,7 +35880,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35909,7 +35909,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35938,7 +35938,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35967,7 +35967,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -35996,7 +35996,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -36025,7 +36025,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -36054,7 +36054,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -36083,7 +36083,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -36112,7 +36112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -36141,7 +36141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36170,7 +36170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36199,7 +36199,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36228,7 +36228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36257,7 +36257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36286,7 +36286,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36315,7 +36315,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36344,7 +36344,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36373,7 +36373,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36402,7 +36402,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36431,7 +36431,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36460,7 +36460,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36489,7 +36489,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36518,7 +36518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36547,7 +36547,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36576,7 +36576,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36605,7 +36605,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36634,7 +36634,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36663,7 +36663,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36692,7 +36692,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36721,7 +36721,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36750,7 +36750,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36779,7 +36779,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36808,7 +36808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36837,7 +36837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36866,7 +36866,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36895,7 +36895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36924,7 +36924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36953,7 +36953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -36982,7 +36982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -37011,7 +37011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -37040,7 +37040,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -37069,7 +37069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -37098,7 +37098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -37127,7 +37127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37156,7 +37156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37185,7 +37185,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37214,7 +37214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37243,7 +37243,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37272,7 +37272,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37301,7 +37301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37330,7 +37330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37359,7 +37359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37388,7 +37388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37417,7 +37417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37446,7 +37446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37475,7 +37475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37504,7 +37504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37533,7 +37533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37562,7 +37562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37591,7 +37591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37620,7 +37620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37649,7 +37649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37678,7 +37678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37707,7 +37707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37736,7 +37736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37765,7 +37765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37794,7 +37794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37823,7 +37823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37852,7 +37852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37881,7 +37881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37910,7 +37910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37939,7 +37939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37968,7 +37968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -37997,7 +37997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -38026,7 +38026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -38055,7 +38055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -38084,7 +38084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -38113,7 +38113,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -38142,7 +38142,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38171,7 +38171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38200,7 +38200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38229,7 +38229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38262,7 +38262,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I5 A61:I64 A60:G60 I60 A66:I79 A65:G65 I65 A7:I59 A6:G6 I6 A81:I87 A80:G80 I80 A160:I169 A159:G159 I159 A171:I181 A170:G170 I170 A274:I283 A273:G273 I273 A285:I298 A284:G284 I284 A456:I495 A455:G455 I455 A534:I584 A533:G533 I533 A586:I654 A585:G585 I585 A656:I1006 A655:G655 I655 A89:I92 A88:G88 I88 A371:I411 A370:G370 I370 A497:I532 A496:G496 I496 A1008:I1063 A1007:G1007 I1007 A94:I104 A93:G93 I93 A106:I158 A105:G105 I105 A233:I259 A232:G232 I232 A427:I454 A426:G426 I426 A216:I231 A215:G215 I215 A183:I214 A182:G182 I182 A261:I272 A260:G260 I260 A300:I369 A299:G299 I299 A413:I425 A412:G412 I412" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I5 A61:I64 A60:G60 I60 A66:I69 A65:G65 I65 A7:I34 A6:G6 I6 A81:I87 A80:G80 I80 A160:I161 A159:G159 I159 A171:I181 A170:G170 I170 A274:I283 A273:G273 I273 A285:I298 A284:G284 I284 A456:I485 A455:G455 I455 A534:I584 A533:G533 I533 A586:I654 A585:G585 I585 A656:I906 A655:G655 I655 A89:I92 A88:G88 I88 A371:I411 A370:G370 I370 A497:I532 A496:G496 I496 A1008:I1063 A1007:G1007 I1007 A94:I104 A93:G93 I93 A106:I155 A105:G105 I105 A233:I259 A232:G232 I232 A427:I454 A426:G426 I426 A216:I231 A215:G215 I215 A183:I214 A182:G182 I182 A261:I272 A260:G260 I260 A300:I369 A299:G299 I299 A413:I419 A412:G412 I412 A36:I39 A35:G35 I35 A41:I51 A40:G40 I40 A53:I59 A52:G52 I52 A71:I79 A70:G70 I70 A157:I158 A156:G156 I156 A163:I169 A162:G162 I162 A421:I425 A420:G420 I420 A487:I495 A486:G486 I486 A908:I1006 A907:G907 I907" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9555" uniqueCount="2343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9551" uniqueCount="2343">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -9512,8 +9512,8 @@
       <c r="G72" t="s">
         <v>295</v>
       </c>
-      <c r="H72" t="s">
-        <v>305</v>
+      <c r="H72" s="1">
+        <v>46138</v>
       </c>
       <c r="I72" t="s">
         <v>306</v>
@@ -13166,8 +13166,8 @@
       <c r="G198" t="s">
         <v>646</v>
       </c>
-      <c r="H198" t="s">
-        <v>305</v>
+      <c r="H198" s="1">
+        <v>46138</v>
       </c>
       <c r="I198" t="s">
         <v>306</v>
@@ -22907,8 +22907,8 @@
       <c r="G534" t="s">
         <v>1402</v>
       </c>
-      <c r="H534" t="s">
-        <v>305</v>
+      <c r="H534" s="1">
+        <v>46138</v>
       </c>
       <c r="I534" t="s">
         <v>306</v>
@@ -23777,8 +23777,8 @@
       <c r="G564" t="s">
         <v>339</v>
       </c>
-      <c r="H564" t="s">
-        <v>305</v>
+      <c r="H564" s="1">
+        <v>46138</v>
       </c>
       <c r="I564" t="s">
         <v>306</v>
@@ -38258,7 +38258,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I35 A325:I350 A324:F324 A352:I422 A351:G351 I351 A37:I40 A36:G36 I36 A42:I52 A41:G41 I41 A54:I70 A53:G53 I53 A72:I156 A71:G71 I71 A158:I162 A157:G157 I157 A164:I323 A163:G163 I163 A424:I488 A423:G423 I423 A490:I908 A489:G489 I489 A910:I1063 A909:G909 I909" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I35 A325:I350 A324:F324 A352:I422 A351:G351 I351 A37:I40 A36:G36 I36 A42:I52 A41:G41 I41 A54:I70 A53:G53 I53 A73:I156 A71:G71 I71 A158:I162 A157:G157 I157 A164:I197 A163:G163 I163 A424:I488 A423:G423 I423 A490:I533 A489:G489 I489 A910:I1063 A909:G909 I909 A72:G72 I72 A199:I323 A198:G198 I198 A535:I563 A534:G534 I534 A565:I908 A564:G564 I564" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -17601,7 +17601,7 @@
         <v>215</v>
       </c>
       <c r="H351" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="I351" t="s">
         <v>1008</v>
@@ -38256,6 +38256,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:I35 A325:I350 A324:F324 A352:I422 A351:G351 I351 A37:I40 A36:G36 I36 A42:I52 A41:G41 I41 A54:I70 A53:G53 I53 A73:I156 A71:G71 I71 A158:I162 A157:G157 I157 A164:I197 A163:G163 I163 A424:I488 A423:G423 I423 A490:I533 A489:G489 I489 A910:I1063 A909:G909 I909 A72:G72 I72 A199:I323 A198:G198 I198 A535:I563 A534:G534 I534 A565:I908 A564:G564 I564" numberStoredAsText="1"/>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9551" uniqueCount="2343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9541" uniqueCount="2343">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -9509,8 +9509,8 @@
       <c r="F72" t="s">
         <v>304</v>
       </c>
-      <c r="G72" t="s">
-        <v>295</v>
+      <c r="G72" s="1">
+        <v>46135</v>
       </c>
       <c r="H72" s="1">
         <v>46138</v>
@@ -10408,8 +10408,8 @@
       <c r="F103" t="s">
         <v>67</v>
       </c>
-      <c r="G103" t="s">
-        <v>395</v>
+      <c r="G103" s="1">
+        <v>45771</v>
       </c>
       <c r="H103" t="s">
         <v>330</v>
@@ -11945,8 +11945,8 @@
       <c r="F156" t="s">
         <v>542</v>
       </c>
-      <c r="G156" t="s">
-        <v>51</v>
+      <c r="G156" s="1">
+        <v>46135</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
@@ -12148,8 +12148,8 @@
       <c r="F163" t="s">
         <v>560</v>
       </c>
-      <c r="G163" t="s">
-        <v>156</v>
+      <c r="G163" s="1">
+        <v>46135</v>
       </c>
       <c r="H163" s="1">
         <v>46137</v>
@@ -12206,8 +12206,8 @@
       <c r="F165" t="s">
         <v>180</v>
       </c>
-      <c r="G165" t="s">
-        <v>504</v>
+      <c r="G165" s="1">
+        <v>46136</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
@@ -12960,8 +12960,8 @@
       <c r="F191" t="s">
         <v>96</v>
       </c>
-      <c r="G191" t="s">
-        <v>40</v>
+      <c r="G191" s="1">
+        <v>46135</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
@@ -13772,8 +13772,8 @@
       <c r="F219" t="s">
         <v>648</v>
       </c>
-      <c r="G219" t="s">
-        <v>537</v>
+      <c r="G219" s="1">
+        <v>46136</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
@@ -14932,8 +14932,8 @@
       <c r="F259" t="s">
         <v>23</v>
       </c>
-      <c r="G259" t="s">
-        <v>105</v>
+      <c r="G259" s="1">
+        <v>46136</v>
       </c>
       <c r="H259" t="s">
         <v>548</v>
@@ -15454,8 +15454,8 @@
       <c r="F277" t="s">
         <v>839</v>
       </c>
-      <c r="G277" t="s">
-        <v>235</v>
+      <c r="G277" s="1">
+        <v>46135</v>
       </c>
       <c r="H277" t="s">
         <v>280</v>
@@ -21483,8 +21483,8 @@
       <c r="F485" t="s">
         <v>96</v>
       </c>
-      <c r="G485" t="s">
-        <v>1054</v>
+      <c r="G485" s="1">
+        <v>46136</v>
       </c>
       <c r="H485" t="s">
         <v>230</v>
@@ -38259,7 +38259,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I35 A325:I350 A324:F324 A352:I422 A351:G351 I351 A37:I40 A36:G36 I36 A42:I52 A41:G41 I41 A54:I70 A53:G53 I53 A73:I156 A71:G71 I71 A158:I162 A157:G157 I157 A164:I197 A163:G163 I163 A424:I488 A423:G423 I423 A490:I533 A489:G489 I489 A910:I1063 A909:G909 I909 A72:G72 I72 A199:I323 A198:G198 I198 A535:I563 A534:G534 I534 A565:I908 A564:G564 I564" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I35 A325:I350 A324:F324 A352:I422 A351:G351 I351 A37:I40 A36:G36 I36 A42:I52 A41:G41 I41 A54:I70 A53:G53 I53 A73:I102 A71:G71 I71 A158:I162 A157:G157 I157 A164:I164 A163:F163 I163 A424:I484 A423:G423 I423 A490:I533 A489:G489 I489 A910:I1063 A909:G909 I909 A72:F72 I72 A199:I218 A198:G198 I198 A535:I563 A534:G534 I534 A565:I908 A564:G564 I564 A104:I155 A103:F103 H103:I103 A192:I197 A191:F191 H191:I191 A260:I276 A259:F259 H259:I259 A278:I323 A277:F277 H277:I277 A156:F156 H156:I156 A220:I258 A219:F219 H219:I219 A486:I488 A485:F485 H485:I485 A166:I190 A165:F165 H165:I165" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9566" uniqueCount="2352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9564" uniqueCount="2352">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7456,9 +7456,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>122</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>139</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>143</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>143</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>154</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>164</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -8531,7 +8531,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>173</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>173</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>188</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>198</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>208</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>213</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>225</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>225</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>225</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>225</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>225</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>247</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>247</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>247</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>247</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>247</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>247</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>269</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>269</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>269</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>269</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>282</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>282</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>282</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>282</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>282</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>265</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>265</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>265</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>265</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>265</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>321</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>326</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>332</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>332</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>332</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>338</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>338</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>338</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>338</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>338</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>338</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>338</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>357</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>362</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>362</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>371</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>371</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>371</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>381</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>381</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>381</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>388</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>388</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>388</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>388</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>388</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>388</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>407</v>
       </c>
@@ -10503,7 +10503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>407</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>407</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>407</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>407</v>
       </c>
@@ -10619,7 +10619,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>419</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>419</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>425</v>
       </c>
@@ -10706,7 +10706,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>425</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>425</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>425</v>
       </c>
@@ -10793,7 +10793,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>440</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>440</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>440</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>440</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>440</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>440</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>440</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>405</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>405</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>405</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>405</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>405</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>405</v>
       </c>
@@ -11170,7 +11170,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>405</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>405</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>405</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>480</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>480</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>480</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>490</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>490</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>490</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>490</v>
       </c>
@@ -11460,7 +11460,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>490</v>
       </c>
@@ -11489,7 +11489,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>490</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>506</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>506</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>506</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>506</v>
       </c>
@@ -11634,7 +11634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>506</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>518</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>518</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>518</v>
       </c>
@@ -11750,7 +11750,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>518</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>518</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>518</v>
       </c>
@@ -11837,7 +11837,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>535</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>535</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>535</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>544</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>544</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>544</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>544</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>544</v>
       </c>
@@ -12069,7 +12069,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>544</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>544</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>544</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>544</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>565</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>568</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>568</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>568</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>568</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>568</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>579</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>579</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>87</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>87</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>87</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>87</v>
       </c>
@@ -12533,7 +12533,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>87</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>87</v>
       </c>
@@ -12591,7 +12591,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>87</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>87</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>87</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>87</v>
       </c>
@@ -12707,7 +12707,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>222</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>222</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>222</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>618</v>
       </c>
@@ -12823,7 +12823,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>618</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>618</v>
       </c>
@@ -12881,7 +12881,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>618</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>618</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>618</v>
       </c>
@@ -12968,7 +12968,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>618</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>618</v>
       </c>
@@ -13026,7 +13026,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>618</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>618</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>644</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>644</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>644</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>644</v>
       </c>
@@ -13200,7 +13200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>644</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>644</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>657</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>660</v>
       </c>
@@ -13316,7 +13316,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>660</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>660</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>660</v>
       </c>
@@ -13403,7 +13403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>660</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>660</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>660</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>660</v>
       </c>
@@ -13519,7 +13519,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>679</v>
       </c>
@@ -13548,7 +13548,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>679</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>679</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>679</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>679</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>679</v>
       </c>
@@ -13693,7 +13693,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>679</v>
       </c>
@@ -13722,7 +13722,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>679</v>
       </c>
@@ -13751,7 +13751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>679</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>679</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>707</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>707</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>707</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>707</v>
       </c>
@@ -13925,7 +13925,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>707</v>
       </c>
@@ -13954,7 +13954,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>717</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>717</v>
       </c>
@@ -14012,7 +14012,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>717</v>
       </c>
@@ -14041,7 +14041,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>717</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>717</v>
       </c>
@@ -14099,7 +14099,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>736</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>736</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>736</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>736</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>736</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>496</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>496</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>496</v>
       </c>
@@ -14331,7 +14331,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>496</v>
       </c>
@@ -14360,7 +14360,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>760</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>760</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>760</v>
       </c>
@@ -14447,7 +14447,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>760</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>760</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>760</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>773</v>
       </c>
@@ -14563,7 +14563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>776</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>776</v>
       </c>
@@ -14621,7 +14621,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>776</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>776</v>
       </c>
@@ -14679,7 +14679,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>776</v>
       </c>
@@ -14708,7 +14708,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>776</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>776</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>789</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>789</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>789</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>789</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>789</v>
       </c>
@@ -14911,7 +14911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>789</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>802</v>
       </c>
@@ -14969,7 +14969,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>802</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>802</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>802</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>802</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>802</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>802</v>
       </c>
@@ -15143,7 +15143,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>802</v>
       </c>
@@ -15172,7 +15172,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>802</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>802</v>
       </c>
@@ -15230,7 +15230,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>802</v>
       </c>
@@ -15259,7 +15259,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>802</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>802</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>833</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>833</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>833</v>
       </c>
@@ -15404,7 +15404,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>833</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>833</v>
       </c>
@@ -15462,7 +15462,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>833</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>833</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>833</v>
       </c>
@@ -15549,7 +15549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>833</v>
       </c>
@@ -15578,7 +15578,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>833</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>833</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>833</v>
       </c>
@@ -15665,7 +15665,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>438</v>
       </c>
@@ -15694,7 +15694,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>438</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>438</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>438</v>
       </c>
@@ -15781,7 +15781,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>438</v>
       </c>
@@ -15810,7 +15810,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>438</v>
       </c>
@@ -15839,7 +15839,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>438</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>438</v>
       </c>
@@ -15897,7 +15897,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>438</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>438</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>438</v>
       </c>
@@ -15984,7 +15984,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>438</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>887</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>887</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>892</v>
       </c>
@@ -16100,7 +16100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>892</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>892</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>901</v>
       </c>
@@ -16187,7 +16187,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>901</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>901</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>901</v>
       </c>
@@ -16274,7 +16274,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>901</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>901</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>901</v>
       </c>
@@ -16361,7 +16361,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>901</v>
       </c>
@@ -16390,7 +16390,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>810</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>810</v>
       </c>
@@ -16448,7 +16448,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>810</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>810</v>
       </c>
@@ -16506,7 +16506,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>810</v>
       </c>
@@ -16535,7 +16535,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>810</v>
       </c>
@@ -16564,7 +16564,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>810</v>
       </c>
@@ -16593,7 +16593,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>810</v>
       </c>
@@ -16622,7 +16622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>810</v>
       </c>
@@ -16651,7 +16651,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>942</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>942</v>
       </c>
@@ -16709,7 +16709,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>942</v>
       </c>
@@ -16738,7 +16738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>942</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>942</v>
       </c>
@@ -16796,7 +16796,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>942</v>
       </c>
@@ -16825,7 +16825,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>942</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>942</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>942</v>
       </c>
@@ -16912,7 +16912,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>942</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>962</v>
       </c>
@@ -16963,14 +16963,14 @@
       <c r="G328" t="s">
         <v>269</v>
       </c>
-      <c r="H328" t="s">
-        <v>490</v>
+      <c r="H328" s="1">
+        <v>46122</v>
       </c>
       <c r="I328" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>962</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>962</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>962</v>
       </c>
@@ -17057,7 +17057,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>962</v>
       </c>
@@ -17086,7 +17086,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>962</v>
       </c>
@@ -17115,7 +17115,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>962</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>962</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>962</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>962</v>
       </c>
@@ -17231,7 +17231,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>962</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>962</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>962</v>
       </c>
@@ -17311,14 +17311,14 @@
       <c r="G340" t="s">
         <v>568</v>
       </c>
-      <c r="H340" t="s">
-        <v>490</v>
+      <c r="H340" s="1">
+        <v>46148</v>
       </c>
       <c r="I340" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>962</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>996</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>996</v>
       </c>
@@ -17405,7 +17405,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>304</v>
       </c>
@@ -17434,7 +17434,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>304</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>304</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>304</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>304</v>
       </c>
@@ -17550,7 +17550,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>304</v>
       </c>
@@ -17579,7 +17579,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>304</v>
       </c>
@@ -17608,7 +17608,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>304</v>
       </c>
@@ -17637,7 +17637,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>304</v>
       </c>
@@ -17666,7 +17666,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1018</v>
       </c>
@@ -17695,7 +17695,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1018</v>
       </c>
@@ -17724,7 +17724,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1018</v>
       </c>
@@ -17753,7 +17753,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1018</v>
       </c>
@@ -17782,7 +17782,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1018</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1018</v>
       </c>
@@ -17840,7 +17840,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1018</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1017</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1017</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1017</v>
       </c>
@@ -17956,7 +17956,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1017</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1017</v>
       </c>
@@ -18014,7 +18014,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1017</v>
       </c>
@@ -18043,7 +18043,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1017</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1017</v>
       </c>
@@ -18101,7 +18101,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1017</v>
       </c>
@@ -18130,7 +18130,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>820</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>820</v>
       </c>
@@ -18188,7 +18188,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>820</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>820</v>
       </c>
@@ -18246,7 +18246,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>820</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>820</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1068</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1068</v>
       </c>
@@ -18362,7 +18362,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1068</v>
       </c>
@@ -18391,7 +18391,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1068</v>
       </c>
@@ -18420,7 +18420,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1068</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1068</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1068</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1068</v>
       </c>
@@ -18536,7 +18536,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1068</v>
       </c>
@@ -18565,7 +18565,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1068</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1068</v>
       </c>
@@ -18623,7 +18623,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1068</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1068</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1068</v>
       </c>
@@ -18710,7 +18710,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1068</v>
       </c>
@@ -18739,7 +18739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1068</v>
       </c>
@@ -18768,7 +18768,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1068</v>
       </c>
@@ -18797,7 +18797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1102</v>
       </c>
@@ -18826,7 +18826,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1106</v>
       </c>
@@ -18855,7 +18855,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1106</v>
       </c>
@@ -18884,7 +18884,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1106</v>
       </c>
@@ -18913,7 +18913,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1106</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1106</v>
       </c>
@@ -18971,7 +18971,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1106</v>
       </c>
@@ -19000,7 +19000,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1106</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1120</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1120</v>
       </c>
@@ -19087,7 +19087,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1120</v>
       </c>
@@ -19116,7 +19116,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1120</v>
       </c>
@@ -19145,7 +19145,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1120</v>
       </c>
@@ -19174,7 +19174,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1120</v>
       </c>
@@ -19203,7 +19203,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1120</v>
       </c>
@@ -19232,7 +19232,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1138</v>
       </c>
@@ -19261,7 +19261,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1138</v>
       </c>
@@ -19290,7 +19290,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1138</v>
       </c>
@@ -19319,7 +19319,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1138</v>
       </c>
@@ -19348,7 +19348,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1138</v>
       </c>
@@ -19377,7 +19377,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1138</v>
       </c>
@@ -19406,7 +19406,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1138</v>
       </c>
@@ -19435,7 +19435,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1138</v>
       </c>
@@ -19464,7 +19464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1138</v>
       </c>
@@ -19493,7 +19493,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1160</v>
       </c>
@@ -19522,7 +19522,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1160</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1160</v>
       </c>
@@ -19580,7 +19580,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1160</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1160</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1160</v>
       </c>
@@ -19667,7 +19667,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1160</v>
       </c>
@@ -19696,7 +19696,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1160</v>
       </c>
@@ -19725,7 +19725,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1160</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1176</v>
       </c>
@@ -19783,7 +19783,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1176</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1176</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1176</v>
       </c>
@@ -19870,7 +19870,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1176</v>
       </c>
@@ -19899,7 +19899,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1176</v>
       </c>
@@ -19928,7 +19928,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1176</v>
       </c>
@@ -19957,7 +19957,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1176</v>
       </c>
@@ -19986,7 +19986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1176</v>
       </c>
@@ -20015,7 +20015,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1176</v>
       </c>
@@ -20044,7 +20044,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1176</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1176</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1176</v>
       </c>
@@ -20131,7 +20131,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1201</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1203</v>
       </c>
@@ -20189,7 +20189,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>678</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>678</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -20363,7 +20363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -20421,7 +20421,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -20450,7 +20450,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20479,7 +20479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20537,7 +20537,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20566,7 +20566,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20595,7 +20595,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20624,7 +20624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20653,7 +20653,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20711,7 +20711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20740,7 +20740,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20769,7 +20769,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20798,7 +20798,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20827,7 +20827,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20856,7 +20856,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20885,7 +20885,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20914,7 +20914,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20972,7 +20972,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -21001,7 +21001,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -21030,7 +21030,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -21059,7 +21059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21117,7 +21117,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21146,7 +21146,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21175,7 +21175,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21233,7 +21233,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21262,7 +21262,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21320,7 +21320,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21349,7 +21349,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21407,7 +21407,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21436,7 +21436,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21494,7 +21494,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21523,7 +21523,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21552,7 +21552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21581,7 +21581,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21610,7 +21610,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21639,7 +21639,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21668,7 +21668,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21697,7 +21697,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21726,7 +21726,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21755,7 +21755,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21842,7 +21842,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21871,7 +21871,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21900,7 +21900,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21958,7 +21958,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21987,7 +21987,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -22016,7 +22016,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -22045,7 +22045,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22103,7 +22103,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22132,7 +22132,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22161,7 +22161,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22190,7 +22190,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22219,7 +22219,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22248,7 +22248,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22277,7 +22277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22306,7 +22306,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22335,7 +22335,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22364,7 +22364,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22393,7 +22393,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22422,7 +22422,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22451,7 +22451,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22480,7 +22480,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22567,7 +22567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22596,7 +22596,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22625,7 +22625,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22654,7 +22654,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22683,7 +22683,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22799,7 +22799,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22828,7 +22828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22857,7 +22857,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22915,7 +22915,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -23060,7 +23060,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23089,7 +23089,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23147,7 +23147,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23205,7 +23205,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23234,7 +23234,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23321,7 +23321,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23350,7 +23350,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23379,7 +23379,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23437,7 +23437,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23466,7 +23466,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23524,7 +23524,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23582,7 +23582,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23698,7 +23698,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23756,7 +23756,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23785,7 +23785,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23843,7 +23843,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23872,7 +23872,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23901,7 +23901,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23930,7 +23930,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23959,7 +23959,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -24017,7 +24017,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -24104,7 +24104,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -24133,7 +24133,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -24162,7 +24162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24191,7 +24191,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24220,7 +24220,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24249,7 +24249,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24336,7 +24336,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24365,7 +24365,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24394,7 +24394,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24423,7 +24423,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24452,7 +24452,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24481,7 +24481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24539,7 +24539,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24568,7 +24568,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24597,7 +24597,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24626,7 +24626,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24655,7 +24655,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24684,7 +24684,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24771,7 +24771,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24800,7 +24800,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24829,7 +24829,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24858,7 +24858,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24887,7 +24887,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24916,7 +24916,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24945,7 +24945,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24974,7 +24974,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -25003,7 +25003,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -25032,7 +25032,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -25090,7 +25090,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -25119,7 +25119,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -25148,7 +25148,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -25177,7 +25177,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25206,7 +25206,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25235,7 +25235,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25264,7 +25264,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25293,7 +25293,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25322,7 +25322,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25380,7 +25380,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25409,7 +25409,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25438,7 +25438,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25467,7 +25467,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25525,7 +25525,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25554,7 +25554,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25583,7 +25583,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25612,7 +25612,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25641,7 +25641,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25670,7 +25670,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25699,7 +25699,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25728,7 +25728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25757,7 +25757,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25786,7 +25786,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25815,7 +25815,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25844,7 +25844,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25931,7 +25931,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25960,7 +25960,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25989,7 +25989,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -26018,7 +26018,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -26047,7 +26047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -26076,7 +26076,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -26105,7 +26105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -26134,7 +26134,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -26163,7 +26163,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26221,7 +26221,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26250,7 +26250,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26279,7 +26279,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26308,7 +26308,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26337,7 +26337,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26366,7 +26366,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26395,7 +26395,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26424,7 +26424,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26453,7 +26453,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26482,7 +26482,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26511,7 +26511,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26540,7 +26540,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26569,7 +26569,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26598,7 +26598,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26627,7 +26627,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26656,7 +26656,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26685,7 +26685,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26714,7 +26714,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26743,7 +26743,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26772,7 +26772,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26801,7 +26801,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26830,7 +26830,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26859,7 +26859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26888,7 +26888,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26917,7 +26917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26975,7 +26975,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -27004,7 +27004,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -27033,7 +27033,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -27062,7 +27062,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -27091,7 +27091,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -27120,7 +27120,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -27149,7 +27149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27178,7 +27178,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27207,7 +27207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27236,7 +27236,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27265,7 +27265,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27294,7 +27294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27323,7 +27323,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27352,7 +27352,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27381,7 +27381,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27410,7 +27410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27439,7 +27439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27468,7 +27468,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27497,7 +27497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27526,7 +27526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27555,7 +27555,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27584,7 +27584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27671,7 +27671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27700,7 +27700,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27729,7 +27729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27758,7 +27758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27787,7 +27787,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27816,7 +27816,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27845,7 +27845,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27874,7 +27874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27903,7 +27903,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27932,7 +27932,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27961,7 +27961,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27990,7 +27990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -28019,7 +28019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -28048,7 +28048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -28077,7 +28077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -28106,7 +28106,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -28135,7 +28135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -28164,7 +28164,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28222,7 +28222,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28251,7 +28251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28309,7 +28309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28338,7 +28338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28367,7 +28367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28396,7 +28396,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28425,7 +28425,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28454,7 +28454,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28483,7 +28483,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28512,7 +28512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28541,7 +28541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28570,7 +28570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28599,7 +28599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28628,7 +28628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28657,7 +28657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28686,7 +28686,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28715,7 +28715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28744,7 +28744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28773,7 +28773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28802,7 +28802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28831,7 +28831,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28889,7 +28889,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28918,7 +28918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28947,7 +28947,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28976,7 +28976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -29005,7 +29005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -29034,7 +29034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -29063,7 +29063,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -29092,7 +29092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -29121,7 +29121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -29150,7 +29150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29179,7 +29179,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29208,7 +29208,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29237,7 +29237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29266,7 +29266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29295,7 +29295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29324,7 +29324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29353,7 +29353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29382,7 +29382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29411,7 +29411,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29440,7 +29440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29469,7 +29469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29498,7 +29498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29527,7 +29527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29556,7 +29556,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29585,7 +29585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29614,7 +29614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29643,7 +29643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29672,7 +29672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29701,7 +29701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29730,7 +29730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29759,7 +29759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29788,7 +29788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29817,7 +29817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29846,7 +29846,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29904,7 +29904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29933,7 +29933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29991,7 +29991,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -30020,7 +30020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -30049,7 +30049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -30107,7 +30107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -30165,7 +30165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30194,7 +30194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30223,7 +30223,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30252,7 +30252,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30281,7 +30281,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30310,7 +30310,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30339,7 +30339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30368,7 +30368,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30397,7 +30397,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30426,7 +30426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30455,7 +30455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30513,7 +30513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30542,7 +30542,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30571,7 +30571,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30600,7 +30600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30629,7 +30629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30658,7 +30658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30687,7 +30687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30716,7 +30716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30745,7 +30745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30774,7 +30774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30803,7 +30803,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30832,7 +30832,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30861,7 +30861,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30890,7 +30890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30919,7 +30919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30948,7 +30948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30977,7 +30977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -31006,7 +31006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -31035,7 +31035,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -31064,7 +31064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -31093,7 +31093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -31122,7 +31122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -31151,7 +31151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31180,7 +31180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31209,7 +31209,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31267,7 +31267,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31296,7 +31296,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31325,7 +31325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31354,7 +31354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31412,7 +31412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31441,7 +31441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31470,7 +31470,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31528,7 +31528,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31557,7 +31557,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31586,7 +31586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31615,7 +31615,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31644,7 +31644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31673,7 +31673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31702,7 +31702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31731,7 +31731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31760,7 +31760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31789,7 +31789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31818,7 +31818,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31847,7 +31847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31876,7 +31876,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31905,7 +31905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31934,7 +31934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31963,7 +31963,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31992,7 +31992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -32021,7 +32021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -32050,7 +32050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -32079,7 +32079,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -32108,7 +32108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -32137,7 +32137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -32166,7 +32166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32195,7 +32195,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32224,7 +32224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32253,7 +32253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32282,7 +32282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32311,7 +32311,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32340,7 +32340,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>16</v>
       </c>
@@ -32369,7 +32369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>16</v>
       </c>
@@ -32398,7 +32398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>16</v>
       </c>
@@ -32427,7 +32427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>16</v>
       </c>
@@ -32456,7 +32456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>16</v>
       </c>
@@ -32485,7 +32485,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>16</v>
       </c>
@@ -32514,7 +32514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>16</v>
       </c>
@@ -32543,7 +32543,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>16</v>
       </c>
@@ -32572,7 +32572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>16</v>
       </c>
@@ -32601,7 +32601,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>16</v>
       </c>
@@ -32630,7 +32630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>16</v>
       </c>
@@ -32659,7 +32659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>16</v>
       </c>
@@ -32688,7 +32688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>16</v>
       </c>
@@ -32717,7 +32717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>16</v>
       </c>
@@ -32746,7 +32746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>16</v>
       </c>
@@ -32775,7 +32775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>16</v>
       </c>
@@ -32804,7 +32804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>16</v>
       </c>
@@ -32833,7 +32833,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>16</v>
       </c>
@@ -32862,7 +32862,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>16</v>
       </c>
@@ -32891,7 +32891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>16</v>
       </c>
@@ -32920,7 +32920,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>16</v>
       </c>
@@ -32949,7 +32949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>16</v>
       </c>
@@ -32978,7 +32978,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>16</v>
       </c>
@@ -33007,7 +33007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>16</v>
       </c>
@@ -33036,7 +33036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>16</v>
       </c>
@@ -33065,7 +33065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>16</v>
       </c>
@@ -33094,7 +33094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>16</v>
       </c>
@@ -33123,7 +33123,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>16</v>
       </c>
@@ -33152,7 +33152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>16</v>
       </c>
@@ -33181,7 +33181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>16</v>
       </c>
@@ -33210,7 +33210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>16</v>
       </c>
@@ -33239,7 +33239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>16</v>
       </c>
@@ -33268,7 +33268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>16</v>
       </c>
@@ -33297,7 +33297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>16</v>
       </c>
@@ -33326,7 +33326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>16</v>
       </c>
@@ -33355,7 +33355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>16</v>
       </c>
@@ -33384,7 +33384,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>16</v>
       </c>
@@ -33413,7 +33413,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>16</v>
       </c>
@@ -33442,7 +33442,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>16</v>
       </c>
@@ -33471,7 +33471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>16</v>
       </c>
@@ -33500,7 +33500,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>16</v>
       </c>
@@ -33529,7 +33529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>16</v>
       </c>
@@ -33558,7 +33558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>16</v>
       </c>
@@ -33587,7 +33587,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>9</v>
       </c>
@@ -33616,7 +33616,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>17</v>
       </c>
@@ -33645,7 +33645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>52</v>
       </c>
@@ -33674,7 +33674,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>52</v>
       </c>
@@ -33703,7 +33703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>61</v>
       </c>
@@ -33732,7 +33732,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>65</v>
       </c>
@@ -33761,7 +33761,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>65</v>
       </c>
@@ -33790,7 +33790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>72</v>
       </c>
@@ -33819,7 +33819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>102</v>
       </c>
@@ -33848,7 +33848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>143</v>
       </c>
@@ -33877,7 +33877,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>198</v>
       </c>
@@ -33906,7 +33906,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>225</v>
       </c>
@@ -33935,7 +33935,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>225</v>
       </c>
@@ -33964,7 +33964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>265</v>
       </c>
@@ -33993,7 +33993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>326</v>
       </c>
@@ -34022,7 +34022,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>338</v>
       </c>
@@ -34051,7 +34051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>388</v>
       </c>
@@ -34080,7 +34080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>419</v>
       </c>
@@ -34109,7 +34109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>440</v>
       </c>
@@ -34138,7 +34138,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>579</v>
       </c>
@@ -34167,7 +34167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>579</v>
       </c>
@@ -34196,7 +34196,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>87</v>
       </c>
@@ -34225,7 +34225,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>87</v>
       </c>
@@ -34254,7 +34254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>87</v>
       </c>
@@ -34283,7 +34283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>87</v>
       </c>
@@ -34312,7 +34312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>222</v>
       </c>
@@ -34341,7 +34341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>222</v>
       </c>
@@ -34370,7 +34370,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>222</v>
       </c>
@@ -34399,7 +34399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>660</v>
       </c>
@@ -34428,7 +34428,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>660</v>
       </c>
@@ -34457,7 +34457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>660</v>
       </c>
@@ -34486,7 +34486,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>679</v>
       </c>
@@ -34515,7 +34515,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>679</v>
       </c>
@@ -34544,7 +34544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>717</v>
       </c>
@@ -34573,7 +34573,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>736</v>
       </c>
@@ -34602,7 +34602,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>760</v>
       </c>
@@ -34631,7 +34631,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>776</v>
       </c>
@@ -34660,7 +34660,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>776</v>
       </c>
@@ -34689,7 +34689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>789</v>
       </c>
@@ -34718,7 +34718,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>802</v>
       </c>
@@ -34747,7 +34747,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>438</v>
       </c>
@@ -34776,7 +34776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>438</v>
       </c>
@@ -34805,7 +34805,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>438</v>
       </c>
@@ -34834,7 +34834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>438</v>
       </c>
@@ -34863,7 +34863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>897</v>
       </c>
@@ -34892,7 +34892,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>901</v>
       </c>
@@ -34921,7 +34921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>810</v>
       </c>
@@ -34950,7 +34950,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>810</v>
       </c>
@@ -34979,7 +34979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>810</v>
       </c>
@@ -35008,7 +35008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>942</v>
       </c>
@@ -35037,7 +35037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>942</v>
       </c>
@@ -35066,7 +35066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>962</v>
       </c>
@@ -35095,7 +35095,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>962</v>
       </c>
@@ -35124,7 +35124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>962</v>
       </c>
@@ -35153,7 +35153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>304</v>
       </c>
@@ -35182,7 +35182,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>1018</v>
       </c>
@@ -35211,7 +35211,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>1018</v>
       </c>
@@ -35240,7 +35240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>1017</v>
       </c>
@@ -35269,7 +35269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>1017</v>
       </c>
@@ -35298,7 +35298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>820</v>
       </c>
@@ -35327,7 +35327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>1068</v>
       </c>
@@ -35356,7 +35356,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>1068</v>
       </c>
@@ -35385,7 +35385,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>1068</v>
       </c>
@@ -35414,7 +35414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>1068</v>
       </c>
@@ -35443,7 +35443,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>1138</v>
       </c>
@@ -35472,7 +35472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>1176</v>
       </c>
@@ -35501,7 +35501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35530,7 +35530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35559,7 +35559,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35588,7 +35588,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35617,7 +35617,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35646,7 +35646,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35675,7 +35675,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35704,7 +35704,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35733,7 +35733,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35762,7 +35762,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35791,7 +35791,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35820,7 +35820,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35849,7 +35849,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35878,7 +35878,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35907,7 +35907,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35936,7 +35936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35965,7 +35965,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35994,7 +35994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -36023,7 +36023,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -36052,7 +36052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -36081,7 +36081,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -36110,7 +36110,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -36139,7 +36139,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -36168,7 +36168,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36197,7 +36197,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36226,7 +36226,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36255,7 +36255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36284,7 +36284,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36313,7 +36313,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36342,7 +36342,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36371,7 +36371,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36400,7 +36400,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36429,7 +36429,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36458,7 +36458,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36487,7 +36487,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36516,7 +36516,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36545,7 +36545,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36574,7 +36574,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36603,7 +36603,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36632,7 +36632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36661,7 +36661,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36690,7 +36690,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36719,7 +36719,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36748,7 +36748,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36777,7 +36777,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36806,7 +36806,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36835,7 +36835,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36864,7 +36864,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36893,7 +36893,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36922,7 +36922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36951,7 +36951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36980,7 +36980,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -37009,7 +37009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -37038,7 +37038,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -37067,7 +37067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -37096,7 +37096,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -37125,7 +37125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -37154,7 +37154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37183,7 +37183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37212,7 +37212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37241,7 +37241,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37270,7 +37270,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37299,7 +37299,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37328,7 +37328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37357,7 +37357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37386,7 +37386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37415,7 +37415,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37444,7 +37444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37473,7 +37473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37502,7 +37502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37531,7 +37531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37560,7 +37560,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37589,7 +37589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37618,7 +37618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37647,7 +37647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37676,7 +37676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37705,7 +37705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37734,7 +37734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37763,7 +37763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37792,7 +37792,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37821,7 +37821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37850,7 +37850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37879,7 +37879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37908,7 +37908,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37937,7 +37937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37966,7 +37966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37995,7 +37995,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -38024,7 +38024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -38053,7 +38053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -38082,7 +38082,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -38111,7 +38111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -38140,7 +38140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -38169,7 +38169,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38198,7 +38198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38227,7 +38227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38256,7 +38256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38286,10 +38286,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I717 A719:I1063 A718:G718 I718" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I327 A719:I1063 A718:G718 I718 A329:I339 A328:G328 A341:I717 A340:G340 I340" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9557" uniqueCount="2353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9553" uniqueCount="2353">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7459,9 +7459,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -7838,7 +7838,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>109</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -8128,7 +8128,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>109</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>124</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>137</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>145</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>154</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>154</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>175</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>175</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>186</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>186</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>195</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>195</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>204</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>204</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>204</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>216</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>219</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>219</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>228</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>235</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>240</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>240</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>240</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>250</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>250</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>250</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>272</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>275</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>275</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>275</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>275</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>275</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>275</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>297</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>297</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>297</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>297</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>310</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>310</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>310</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>310</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>310</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>310</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>293</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>293</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>293</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>293</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>293</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>347</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>353</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>353</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>353</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>359</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>359</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>359</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>359</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>359</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>359</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>359</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>377</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>382</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>382</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>382</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>391</v>
       </c>
@@ -10361,7 +10361,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>391</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>391</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>401</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>401</v>
       </c>
@@ -10477,7 +10477,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>401</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>408</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>408</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>408</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>408</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>408</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>408</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>427</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>427</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>427</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>427</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>427</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>439</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>439</v>
       </c>
@@ -10883,7 +10883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>445</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>445</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>445</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>445</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>460</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>460</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>460</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>460</v>
       </c>
@@ -11115,7 +11115,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>460</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>460</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>460</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>425</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>425</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>425</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>425</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>425</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>425</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>425</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>425</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>425</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>500</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>500</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>500</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>509</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>509</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>509</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>509</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>509</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>509</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>525</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>525</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>525</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>525</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>525</v>
       </c>
@@ -11869,7 +11869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>537</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>537</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>537</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>537</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>537</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>537</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>554</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>554</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>554</v>
       </c>
@@ -12130,7 +12130,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>563</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>563</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>563</v>
       </c>
@@ -12217,7 +12217,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>563</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>563</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>563</v>
       </c>
@@ -12297,14 +12297,14 @@
       <c r="G167" t="s">
         <v>577</v>
       </c>
-      <c r="H167" t="s">
-        <v>16</v>
+      <c r="H167" s="1">
+        <v>46150</v>
       </c>
       <c r="I167" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>563</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>563</v>
       </c>
@@ -12362,7 +12362,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>563</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>584</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>587</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>587</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>587</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>587</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>587</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>597</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>597</v>
       </c>
@@ -12623,7 +12623,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>123</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>123</v>
       </c>
@@ -12681,7 +12681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>123</v>
       </c>
@@ -12710,7 +12710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>123</v>
       </c>
@@ -12739,7 +12739,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>123</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>123</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>123</v>
       </c>
@@ -12826,7 +12826,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>123</v>
       </c>
@@ -12855,7 +12855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>123</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>123</v>
       </c>
@@ -12913,7 +12913,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>37</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>37</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>37</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>636</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>636</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>636</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>636</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>636</v>
       </c>
@@ -13145,7 +13145,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>636</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>636</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>636</v>
       </c>
@@ -13232,7 +13232,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>636</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>636</v>
       </c>
@@ -13290,7 +13290,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>661</v>
       </c>
@@ -13319,7 +13319,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>661</v>
       </c>
@@ -13348,7 +13348,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>661</v>
       </c>
@@ -13377,7 +13377,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>661</v>
       </c>
@@ -13406,7 +13406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>661</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>661</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>674</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>677</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>677</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>677</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>677</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>677</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>677</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>677</v>
       </c>
@@ -13696,7 +13696,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>677</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>695</v>
       </c>
@@ -13754,7 +13754,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>695</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>695</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>695</v>
       </c>
@@ -13841,7 +13841,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>695</v>
       </c>
@@ -13870,7 +13870,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>695</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>695</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>695</v>
       </c>
@@ -13957,7 +13957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>695</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>695</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>723</v>
       </c>
@@ -14044,7 +14044,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>723</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>723</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>723</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>723</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>733</v>
       </c>
@@ -14189,7 +14189,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>733</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>733</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>733</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>733</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>752</v>
       </c>
@@ -14334,7 +14334,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>752</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>752</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>752</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>752</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>515</v>
       </c>
@@ -14479,7 +14479,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>515</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>515</v>
       </c>
@@ -14537,7 +14537,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>515</v>
       </c>
@@ -14566,7 +14566,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>776</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>776</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>776</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>776</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>776</v>
       </c>
@@ -14711,7 +14711,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>776</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>789</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>792</v>
       </c>
@@ -14798,7 +14798,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>792</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>792</v>
       </c>
@@ -14856,7 +14856,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>792</v>
       </c>
@@ -14885,7 +14885,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>792</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>792</v>
       </c>
@@ -14943,7 +14943,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>792</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>805</v>
       </c>
@@ -15001,7 +15001,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>805</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>805</v>
       </c>
@@ -15059,7 +15059,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>805</v>
       </c>
@@ -15088,7 +15088,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>805</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>805</v>
       </c>
@@ -15146,7 +15146,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>818</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>818</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>818</v>
       </c>
@@ -15233,7 +15233,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>818</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>818</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>818</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>818</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>818</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>818</v>
       </c>
@@ -15407,7 +15407,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>818</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>818</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>818</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>818</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>849</v>
       </c>
@@ -15552,7 +15552,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>849</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>849</v>
       </c>
@@ -15610,7 +15610,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>849</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>849</v>
       </c>
@@ -15668,7 +15668,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>849</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>849</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>849</v>
       </c>
@@ -15755,7 +15755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>849</v>
       </c>
@@ -15784,7 +15784,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>849</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>849</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>849</v>
       </c>
@@ -15871,7 +15871,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>458</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>458</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>458</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>458</v>
       </c>
@@ -15987,7 +15987,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>458</v>
       </c>
@@ -16016,7 +16016,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>458</v>
       </c>
@@ -16045,7 +16045,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>458</v>
       </c>
@@ -16074,7 +16074,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>458</v>
       </c>
@@ -16103,7 +16103,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>458</v>
       </c>
@@ -16132,7 +16132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>458</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>458</v>
       </c>
@@ -16190,7 +16190,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>458</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>904</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>904</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>908</v>
       </c>
@@ -16306,7 +16306,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>908</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>908</v>
       </c>
@@ -16364,7 +16364,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>917</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>917</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>917</v>
       </c>
@@ -16451,7 +16451,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>917</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>917</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>917</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>917</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>917</v>
       </c>
@@ -16596,7 +16596,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>826</v>
       </c>
@@ -16625,7 +16625,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>826</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>826</v>
       </c>
@@ -16683,7 +16683,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>826</v>
       </c>
@@ -16712,7 +16712,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>826</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>826</v>
       </c>
@@ -16770,7 +16770,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>826</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>826</v>
       </c>
@@ -16828,7 +16828,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>826</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>958</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>958</v>
       </c>
@@ -16915,7 +16915,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>958</v>
       </c>
@@ -16944,7 +16944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>958</v>
       </c>
@@ -16973,7 +16973,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>958</v>
       </c>
@@ -17002,7 +17002,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>958</v>
       </c>
@@ -17031,7 +17031,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>958</v>
       </c>
@@ -17060,7 +17060,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>958</v>
       </c>
@@ -17089,7 +17089,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>958</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>958</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>978</v>
       </c>
@@ -17176,7 +17176,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>978</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>978</v>
       </c>
@@ -17234,7 +17234,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>978</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>978</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>978</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>978</v>
       </c>
@@ -17350,7 +17350,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>978</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>978</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>978</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>978</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>978</v>
       </c>
@@ -17495,7 +17495,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>978</v>
       </c>
@@ -17518,13 +17518,13 @@
         <v>587</v>
       </c>
       <c r="H347" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="I347" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>978</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1012</v>
       </c>
@@ -17582,7 +17582,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1012</v>
       </c>
@@ -17611,7 +17611,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>332</v>
       </c>
@@ -17640,7 +17640,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>332</v>
       </c>
@@ -17669,7 +17669,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>332</v>
       </c>
@@ -17698,7 +17698,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>332</v>
       </c>
@@ -17727,7 +17727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>332</v>
       </c>
@@ -17756,7 +17756,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>332</v>
       </c>
@@ -17785,7 +17785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>332</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>332</v>
       </c>
@@ -17843,7 +17843,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>332</v>
       </c>
@@ -17872,7 +17872,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1034</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1034</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1034</v>
       </c>
@@ -17959,7 +17959,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1034</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1034</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1034</v>
       </c>
@@ -18046,7 +18046,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1034</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1033</v>
       </c>
@@ -18104,7 +18104,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1033</v>
       </c>
@@ -18133,7 +18133,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1033</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1033</v>
       </c>
@@ -18191,7 +18191,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1033</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1033</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1033</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1033</v>
       </c>
@@ -18300,14 +18300,14 @@
       <c r="G374" t="s">
         <v>1070</v>
       </c>
-      <c r="H374" t="s">
-        <v>16</v>
+      <c r="H374" s="1">
+        <v>46150</v>
       </c>
       <c r="I374" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1033</v>
       </c>
@@ -18336,7 +18336,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>836</v>
       </c>
@@ -18365,7 +18365,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>836</v>
       </c>
@@ -18394,7 +18394,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>836</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>836</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>836</v>
       </c>
@@ -18481,7 +18481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>836</v>
       </c>
@@ -18510,7 +18510,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1083</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1083</v>
       </c>
@@ -18568,7 +18568,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1083</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1083</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1083</v>
       </c>
@@ -18655,7 +18655,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1083</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1083</v>
       </c>
@@ -18713,7 +18713,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1083</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1083</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1083</v>
       </c>
@@ -18800,7 +18800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1083</v>
       </c>
@@ -18829,7 +18829,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1083</v>
       </c>
@@ -18858,7 +18858,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1083</v>
       </c>
@@ -18887,7 +18887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1083</v>
       </c>
@@ -18916,7 +18916,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1083</v>
       </c>
@@ -18945,7 +18945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1083</v>
       </c>
@@ -18974,7 +18974,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1083</v>
       </c>
@@ -19003,7 +19003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1117</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1121</v>
       </c>
@@ -19061,7 +19061,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1121</v>
       </c>
@@ -19090,7 +19090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1121</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1121</v>
       </c>
@@ -19148,7 +19148,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1121</v>
       </c>
@@ -19177,7 +19177,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1121</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1121</v>
       </c>
@@ -19235,7 +19235,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1135</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1135</v>
       </c>
@@ -19293,7 +19293,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1135</v>
       </c>
@@ -19322,7 +19322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1135</v>
       </c>
@@ -19351,7 +19351,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1135</v>
       </c>
@@ -19380,7 +19380,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1135</v>
       </c>
@@ -19409,7 +19409,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1135</v>
       </c>
@@ -19438,7 +19438,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1153</v>
       </c>
@@ -19467,7 +19467,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1153</v>
       </c>
@@ -19496,7 +19496,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1153</v>
       </c>
@@ -19525,7 +19525,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1153</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1153</v>
       </c>
@@ -19583,7 +19583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1153</v>
       </c>
@@ -19612,7 +19612,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1153</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1153</v>
       </c>
@@ -19670,7 +19670,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1153</v>
       </c>
@@ -19699,7 +19699,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1175</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1175</v>
       </c>
@@ -19757,7 +19757,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1175</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1175</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1175</v>
       </c>
@@ -19844,7 +19844,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1175</v>
       </c>
@@ -19873,7 +19873,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1175</v>
       </c>
@@ -19902,7 +19902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1175</v>
       </c>
@@ -19931,7 +19931,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1175</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1191</v>
       </c>
@@ -19989,7 +19989,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1191</v>
       </c>
@@ -20018,7 +20018,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1191</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1191</v>
       </c>
@@ -20076,7 +20076,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1191</v>
       </c>
@@ -20105,7 +20105,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1191</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1191</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1191</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1191</v>
       </c>
@@ -20221,7 +20221,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1191</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1191</v>
       </c>
@@ -20279,7 +20279,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1191</v>
       </c>
@@ -20308,7 +20308,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1191</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1216</v>
       </c>
@@ -20366,7 +20366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1218</v>
       </c>
@@ -20395,7 +20395,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>694</v>
       </c>
@@ -20424,7 +20424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>694</v>
       </c>
@@ -20453,7 +20453,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -20511,7 +20511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -20540,7 +20540,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20569,7 +20569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20627,7 +20627,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20656,7 +20656,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20685,7 +20685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20801,7 +20801,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20830,7 +20830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -21004,7 +21004,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -21062,7 +21062,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21091,7 +21091,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21120,7 +21120,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21149,7 +21149,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21236,7 +21236,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21265,7 +21265,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21323,7 +21323,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21352,7 +21352,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21381,7 +21381,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21410,7 +21410,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21439,7 +21439,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21526,7 +21526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21555,7 +21555,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21584,7 +21584,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21671,7 +21671,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21700,7 +21700,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21729,7 +21729,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21787,7 +21787,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21845,7 +21845,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21874,7 +21874,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21903,7 +21903,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21932,7 +21932,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21961,7 +21961,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -22048,7 +22048,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22077,7 +22077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22106,7 +22106,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22135,7 +22135,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22164,7 +22164,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22193,7 +22193,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22222,7 +22222,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22251,7 +22251,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22280,7 +22280,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22338,7 +22338,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22367,7 +22367,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22396,7 +22396,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22454,7 +22454,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22483,7 +22483,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22541,7 +22541,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22570,7 +22570,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22628,7 +22628,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22657,7 +22657,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22686,7 +22686,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22715,7 +22715,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22773,7 +22773,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22802,7 +22802,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22860,7 +22860,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22889,7 +22889,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22947,7 +22947,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22976,7 +22976,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -23005,7 +23005,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23092,7 +23092,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23121,7 +23121,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23150,7 +23150,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23179,7 +23179,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23208,7 +23208,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23237,7 +23237,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23266,7 +23266,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23295,7 +23295,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23324,7 +23324,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23353,7 +23353,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23382,7 +23382,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23411,7 +23411,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23440,7 +23440,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23469,7 +23469,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>16</v>
       </c>
@@ -23498,7 +23498,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>16</v>
       </c>
@@ -23527,7 +23527,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="555" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>16</v>
       </c>
@@ -23556,7 +23556,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>16</v>
       </c>
@@ -23585,7 +23585,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="557" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>16</v>
       </c>
@@ -23614,7 +23614,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="558" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>16</v>
       </c>
@@ -23643,7 +23643,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="559" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>16</v>
       </c>
@@ -23672,7 +23672,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="560" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>16</v>
       </c>
@@ -23701,7 +23701,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="561" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>16</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="562" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>16</v>
       </c>
@@ -23759,7 +23759,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="563" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>16</v>
       </c>
@@ -23788,7 +23788,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="564" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>16</v>
       </c>
@@ -23817,7 +23817,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="565" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>16</v>
       </c>
@@ -23846,7 +23846,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="566" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>16</v>
       </c>
@@ -23875,7 +23875,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="567" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>16</v>
       </c>
@@ -23904,7 +23904,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="568" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>16</v>
       </c>
@@ -23933,7 +23933,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="569" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>16</v>
       </c>
@@ -23962,7 +23962,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="570" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>16</v>
       </c>
@@ -23991,7 +23991,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="571" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>16</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="572" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>16</v>
       </c>
@@ -24049,7 +24049,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="573" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>16</v>
       </c>
@@ -24071,14 +24071,14 @@
       <c r="G573" t="s">
         <v>1493</v>
       </c>
-      <c r="H573" t="s">
-        <v>16</v>
+      <c r="H573" s="1">
+        <v>46150</v>
       </c>
       <c r="I573" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="574" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>16</v>
       </c>
@@ -24107,7 +24107,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="575" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>16</v>
       </c>
@@ -24136,7 +24136,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="576" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>16</v>
       </c>
@@ -24165,7 +24165,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="577" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>16</v>
       </c>
@@ -24194,7 +24194,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>16</v>
       </c>
@@ -24223,7 +24223,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>16</v>
       </c>
@@ -24252,7 +24252,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>16</v>
       </c>
@@ -24281,7 +24281,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="581" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>16</v>
       </c>
@@ -24310,7 +24310,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="582" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>16</v>
       </c>
@@ -24339,7 +24339,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="583" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>16</v>
       </c>
@@ -24368,7 +24368,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="584" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>16</v>
       </c>
@@ -24397,7 +24397,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="585" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>16</v>
       </c>
@@ -24426,7 +24426,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="586" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>16</v>
       </c>
@@ -24455,7 +24455,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="587" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>16</v>
       </c>
@@ -24484,7 +24484,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="588" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>16</v>
       </c>
@@ -24513,7 +24513,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="589" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>16</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="590" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>16</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>16</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>16</v>
       </c>
@@ -24629,7 +24629,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>16</v>
       </c>
@@ -24658,7 +24658,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="594" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>16</v>
       </c>
@@ -24687,7 +24687,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="595" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>16</v>
       </c>
@@ -24716,7 +24716,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="596" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>16</v>
       </c>
@@ -24745,7 +24745,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="597" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>16</v>
       </c>
@@ -24774,7 +24774,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="598" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>16</v>
       </c>
@@ -24803,7 +24803,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="599" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>16</v>
       </c>
@@ -24832,7 +24832,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="600" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>16</v>
       </c>
@@ -24861,7 +24861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="601" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>16</v>
       </c>
@@ -24890,7 +24890,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="602" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>16</v>
       </c>
@@ -24919,7 +24919,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="603" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>16</v>
       </c>
@@ -24948,7 +24948,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="604" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>16</v>
       </c>
@@ -24977,7 +24977,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="605" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>16</v>
       </c>
@@ -25006,7 +25006,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="606" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>16</v>
       </c>
@@ -25035,7 +25035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="607" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>16</v>
       </c>
@@ -25064,7 +25064,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>16</v>
       </c>
@@ -25093,7 +25093,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>16</v>
       </c>
@@ -25122,7 +25122,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>16</v>
       </c>
@@ -25151,7 +25151,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>16</v>
       </c>
@@ -25180,7 +25180,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="612" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>16</v>
       </c>
@@ -25209,7 +25209,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="613" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>16</v>
       </c>
@@ -25238,7 +25238,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="614" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>16</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="615" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>16</v>
       </c>
@@ -25296,7 +25296,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>16</v>
       </c>
@@ -25325,7 +25325,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="617" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>16</v>
       </c>
@@ -25354,7 +25354,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="618" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>16</v>
       </c>
@@ -25383,7 +25383,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="619" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>16</v>
       </c>
@@ -25412,7 +25412,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="620" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>16</v>
       </c>
@@ -25441,7 +25441,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>16</v>
       </c>
@@ -25470,7 +25470,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>16</v>
       </c>
@@ -25499,7 +25499,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>16</v>
       </c>
@@ -25528,7 +25528,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>16</v>
       </c>
@@ -25557,7 +25557,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>16</v>
       </c>
@@ -25586,7 +25586,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>16</v>
       </c>
@@ -25615,7 +25615,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>16</v>
       </c>
@@ -25644,7 +25644,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="628" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>16</v>
       </c>
@@ -25673,7 +25673,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="629" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>16</v>
       </c>
@@ -25702,7 +25702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="630" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>16</v>
       </c>
@@ -25731,7 +25731,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="631" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>16</v>
       </c>
@@ -25760,7 +25760,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="632" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>16</v>
       </c>
@@ -25789,7 +25789,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="633" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>16</v>
       </c>
@@ -25818,7 +25818,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="634" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>16</v>
       </c>
@@ -25847,7 +25847,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="635" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>16</v>
       </c>
@@ -25876,7 +25876,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="636" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>16</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>16</v>
       </c>
@@ -25934,7 +25934,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>16</v>
       </c>
@@ -25963,7 +25963,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>16</v>
       </c>
@@ -25992,7 +25992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="640" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>16</v>
       </c>
@@ -26021,7 +26021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>16</v>
       </c>
@@ -26050,7 +26050,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>16</v>
       </c>
@@ -26079,7 +26079,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>16</v>
       </c>
@@ -26108,7 +26108,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>16</v>
       </c>
@@ -26137,7 +26137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>16</v>
       </c>
@@ -26166,7 +26166,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>16</v>
       </c>
@@ -26195,7 +26195,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>16</v>
       </c>
@@ -26224,7 +26224,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>16</v>
       </c>
@@ -26253,7 +26253,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>16</v>
       </c>
@@ -26282,7 +26282,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>16</v>
       </c>
@@ -26311,7 +26311,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>16</v>
       </c>
@@ -26340,7 +26340,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>16</v>
       </c>
@@ -26369,7 +26369,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>16</v>
       </c>
@@ -26398,7 +26398,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>16</v>
       </c>
@@ -26427,7 +26427,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>16</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>16</v>
       </c>
@@ -26485,7 +26485,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>16</v>
       </c>
@@ -26514,7 +26514,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>16</v>
       </c>
@@ -26543,7 +26543,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>16</v>
       </c>
@@ -26572,7 +26572,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>16</v>
       </c>
@@ -26601,7 +26601,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>16</v>
       </c>
@@ -26630,7 +26630,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>16</v>
       </c>
@@ -26659,7 +26659,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>16</v>
       </c>
@@ -26688,7 +26688,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>16</v>
       </c>
@@ -26717,7 +26717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>16</v>
       </c>
@@ -26746,7 +26746,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>16</v>
       </c>
@@ -26775,7 +26775,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>16</v>
       </c>
@@ -26804,7 +26804,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>16</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>16</v>
       </c>
@@ -26862,7 +26862,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>16</v>
       </c>
@@ -26891,7 +26891,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -26920,7 +26920,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>16</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="673" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>16</v>
       </c>
@@ -26978,7 +26978,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="674" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>16</v>
       </c>
@@ -27007,7 +27007,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>16</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="676" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>16</v>
       </c>
@@ -27065,7 +27065,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="677" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>16</v>
       </c>
@@ -27087,14 +27087,14 @@
       <c r="G677" t="s">
         <v>94</v>
       </c>
-      <c r="H677" t="s">
-        <v>16</v>
+      <c r="H677" s="1">
+        <v>46150</v>
       </c>
       <c r="I677" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>16</v>
       </c>
@@ -27123,7 +27123,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>16</v>
       </c>
@@ -27152,7 +27152,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="680" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>16</v>
       </c>
@@ -27181,7 +27181,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="681" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>16</v>
       </c>
@@ -27210,7 +27210,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="682" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>16</v>
       </c>
@@ -27239,7 +27239,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="683" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>16</v>
       </c>
@@ -27268,7 +27268,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="684" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>16</v>
       </c>
@@ -27297,7 +27297,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="685" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>16</v>
       </c>
@@ -27326,7 +27326,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="686" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>16</v>
       </c>
@@ -27355,7 +27355,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="687" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>16</v>
       </c>
@@ -27384,7 +27384,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="688" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>16</v>
       </c>
@@ -27413,7 +27413,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="689" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>16</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="690" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>16</v>
       </c>
@@ -27471,7 +27471,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>16</v>
       </c>
@@ -27500,7 +27500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="692" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>16</v>
       </c>
@@ -27529,7 +27529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="693" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>16</v>
       </c>
@@ -27558,7 +27558,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="694" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>16</v>
       </c>
@@ -27587,7 +27587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="695" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>16</v>
       </c>
@@ -27616,7 +27616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="696" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>16</v>
       </c>
@@ -27645,7 +27645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="697" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>16</v>
       </c>
@@ -27674,7 +27674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="698" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>16</v>
       </c>
@@ -27703,7 +27703,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>16</v>
       </c>
@@ -27732,7 +27732,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="700" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>16</v>
       </c>
@@ -27761,7 +27761,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="701" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>16</v>
       </c>
@@ -27790,7 +27790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="702" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>16</v>
       </c>
@@ -27819,7 +27819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="703" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>16</v>
       </c>
@@ -27848,7 +27848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="704" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>16</v>
       </c>
@@ -27877,7 +27877,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="705" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>16</v>
       </c>
@@ -27906,7 +27906,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="706" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>16</v>
       </c>
@@ -27935,7 +27935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>16</v>
       </c>
@@ -27964,7 +27964,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="708" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>16</v>
       </c>
@@ -27993,7 +27993,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="709" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>16</v>
       </c>
@@ -28022,7 +28022,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="710" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>16</v>
       </c>
@@ -28051,7 +28051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="711" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>16</v>
       </c>
@@ -28080,7 +28080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="712" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>16</v>
       </c>
@@ -28109,7 +28109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="713" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>16</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="714" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>16</v>
       </c>
@@ -28167,7 +28167,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>16</v>
       </c>
@@ -28196,7 +28196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="716" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>16</v>
       </c>
@@ -28225,7 +28225,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="717" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>16</v>
       </c>
@@ -28254,7 +28254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="718" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>16</v>
       </c>
@@ -28283,7 +28283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>16</v>
       </c>
@@ -28312,7 +28312,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="720" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>16</v>
       </c>
@@ -28341,7 +28341,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>16</v>
       </c>
@@ -28370,7 +28370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>16</v>
       </c>
@@ -28399,7 +28399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>16</v>
       </c>
@@ -28428,7 +28428,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>16</v>
       </c>
@@ -28457,7 +28457,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>16</v>
       </c>
@@ -28486,7 +28486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>16</v>
       </c>
@@ -28515,7 +28515,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>16</v>
       </c>
@@ -28544,7 +28544,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>16</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>16</v>
       </c>
@@ -28602,7 +28602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>16</v>
       </c>
@@ -28631,7 +28631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>16</v>
       </c>
@@ -28660,7 +28660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>16</v>
       </c>
@@ -28689,7 +28689,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>16</v>
       </c>
@@ -28718,7 +28718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>16</v>
       </c>
@@ -28747,7 +28747,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>16</v>
       </c>
@@ -28776,7 +28776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>16</v>
       </c>
@@ -28805,7 +28805,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>16</v>
       </c>
@@ -28834,7 +28834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>16</v>
       </c>
@@ -28863,7 +28863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>16</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>16</v>
       </c>
@@ -28921,7 +28921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>16</v>
       </c>
@@ -28950,7 +28950,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>16</v>
       </c>
@@ -28979,7 +28979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>16</v>
       </c>
@@ -29008,7 +29008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>16</v>
       </c>
@@ -29037,7 +29037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>16</v>
       </c>
@@ -29066,7 +29066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>16</v>
       </c>
@@ -29095,7 +29095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>16</v>
       </c>
@@ -29124,7 +29124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>16</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>16</v>
       </c>
@@ -29182,7 +29182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>16</v>
       </c>
@@ -29211,7 +29211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>16</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>16</v>
       </c>
@@ -29269,7 +29269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>16</v>
       </c>
@@ -29298,7 +29298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>16</v>
       </c>
@@ -29327,7 +29327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>16</v>
       </c>
@@ -29356,7 +29356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>16</v>
       </c>
@@ -29385,7 +29385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>16</v>
       </c>
@@ -29414,7 +29414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>16</v>
       </c>
@@ -29443,7 +29443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>16</v>
       </c>
@@ -29472,7 +29472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>16</v>
       </c>
@@ -29501,7 +29501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>16</v>
       </c>
@@ -29530,7 +29530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>16</v>
       </c>
@@ -29559,7 +29559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>16</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>16</v>
       </c>
@@ -29617,7 +29617,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>16</v>
       </c>
@@ -29646,7 +29646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>16</v>
       </c>
@@ -29675,7 +29675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>16</v>
       </c>
@@ -29704,7 +29704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>16</v>
       </c>
@@ -29733,7 +29733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>16</v>
       </c>
@@ -29762,7 +29762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>16</v>
       </c>
@@ -29791,7 +29791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>16</v>
       </c>
@@ -29820,7 +29820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>16</v>
       </c>
@@ -29849,7 +29849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>16</v>
       </c>
@@ -29878,7 +29878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>16</v>
       </c>
@@ -29907,7 +29907,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>16</v>
       </c>
@@ -29936,7 +29936,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>16</v>
       </c>
@@ -29965,7 +29965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>16</v>
       </c>
@@ -29994,7 +29994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>16</v>
       </c>
@@ -30023,7 +30023,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>16</v>
       </c>
@@ -30052,7 +30052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>16</v>
       </c>
@@ -30081,7 +30081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>16</v>
       </c>
@@ -30110,7 +30110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>16</v>
       </c>
@@ -30139,7 +30139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>16</v>
       </c>
@@ -30168,7 +30168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>16</v>
       </c>
@@ -30197,7 +30197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>16</v>
       </c>
@@ -30226,7 +30226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>16</v>
       </c>
@@ -30255,7 +30255,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>16</v>
       </c>
@@ -30284,7 +30284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>16</v>
       </c>
@@ -30313,7 +30313,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>16</v>
       </c>
@@ -30342,7 +30342,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>16</v>
       </c>
@@ -30371,7 +30371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>16</v>
       </c>
@@ -30400,7 +30400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>16</v>
       </c>
@@ -30429,7 +30429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>16</v>
       </c>
@@ -30458,7 +30458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>16</v>
       </c>
@@ -30487,7 +30487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>16</v>
       </c>
@@ -30516,7 +30516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>16</v>
       </c>
@@ -30545,7 +30545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>16</v>
       </c>
@@ -30574,7 +30574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>16</v>
       </c>
@@ -30603,7 +30603,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>16</v>
       </c>
@@ -30632,7 +30632,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>16</v>
       </c>
@@ -30661,7 +30661,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>16</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>16</v>
       </c>
@@ -30719,7 +30719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>16</v>
       </c>
@@ -30748,7 +30748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>16</v>
       </c>
@@ -30777,7 +30777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>16</v>
       </c>
@@ -30806,7 +30806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>16</v>
       </c>
@@ -30835,7 +30835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>16</v>
       </c>
@@ -30864,7 +30864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>16</v>
       </c>
@@ -30893,7 +30893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>16</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>16</v>
       </c>
@@ -30951,7 +30951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>16</v>
       </c>
@@ -30980,7 +30980,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>16</v>
       </c>
@@ -31009,7 +31009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>16</v>
       </c>
@@ -31038,7 +31038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>16</v>
       </c>
@@ -31067,7 +31067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>16</v>
       </c>
@@ -31096,7 +31096,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>16</v>
       </c>
@@ -31125,7 +31125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>16</v>
       </c>
@@ -31154,7 +31154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>16</v>
       </c>
@@ -31183,7 +31183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>16</v>
       </c>
@@ -31212,7 +31212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>16</v>
       </c>
@@ -31241,7 +31241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>16</v>
       </c>
@@ -31270,7 +31270,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>16</v>
       </c>
@@ -31299,7 +31299,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>16</v>
       </c>
@@ -31328,7 +31328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>16</v>
       </c>
@@ -31357,7 +31357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>16</v>
       </c>
@@ -31386,7 +31386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>16</v>
       </c>
@@ -31415,7 +31415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>16</v>
       </c>
@@ -31444,7 +31444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>16</v>
       </c>
@@ -31473,7 +31473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>16</v>
       </c>
@@ -31502,7 +31502,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>16</v>
       </c>
@@ -31531,7 +31531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>16</v>
       </c>
@@ -31560,7 +31560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>16</v>
       </c>
@@ -31589,7 +31589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>16</v>
       </c>
@@ -31618,7 +31618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>16</v>
       </c>
@@ -31647,7 +31647,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>16</v>
       </c>
@@ -31676,7 +31676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>16</v>
       </c>
@@ -31705,7 +31705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>16</v>
       </c>
@@ -31734,7 +31734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>16</v>
       </c>
@@ -31763,7 +31763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>16</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>16</v>
       </c>
@@ -31821,7 +31821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>16</v>
       </c>
@@ -31850,7 +31850,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>16</v>
       </c>
@@ -31879,7 +31879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>16</v>
       </c>
@@ -31908,7 +31908,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>16</v>
       </c>
@@ -31937,7 +31937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>16</v>
       </c>
@@ -31966,7 +31966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>16</v>
       </c>
@@ -31995,7 +31995,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>16</v>
       </c>
@@ -32024,7 +32024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>16</v>
       </c>
@@ -32053,7 +32053,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>16</v>
       </c>
@@ -32082,7 +32082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>16</v>
       </c>
@@ -32111,7 +32111,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>16</v>
       </c>
@@ -32140,7 +32140,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>16</v>
       </c>
@@ -32169,7 +32169,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>16</v>
       </c>
@@ -32198,7 +32198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>16</v>
       </c>
@@ -32227,7 +32227,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>16</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>16</v>
       </c>
@@ -32285,7 +32285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>16</v>
       </c>
@@ -32314,7 +32314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>16</v>
       </c>
@@ -32343,7 +32343,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>16</v>
       </c>
@@ -32372,7 +32372,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>16</v>
       </c>
@@ -32401,7 +32401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>16</v>
       </c>
@@ -32430,7 +32430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>16</v>
       </c>
@@ -32459,7 +32459,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>16</v>
       </c>
@@ -32488,7 +32488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>16</v>
       </c>
@@ -32517,7 +32517,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>16</v>
       </c>
@@ -32546,7 +32546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>16</v>
       </c>
@@ -32575,7 +32575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>16</v>
       </c>
@@ -32604,7 +32604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>16</v>
       </c>
@@ -32633,7 +32633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>16</v>
       </c>
@@ -32662,7 +32662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>16</v>
       </c>
@@ -32691,7 +32691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>16</v>
       </c>
@@ -32720,7 +32720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>16</v>
       </c>
@@ -32749,7 +32749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>16</v>
       </c>
@@ -32778,7 +32778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>16</v>
       </c>
@@ -32807,7 +32807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>16</v>
       </c>
@@ -32836,7 +32836,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>16</v>
       </c>
@@ -32865,7 +32865,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="877" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>16</v>
       </c>
@@ -32894,7 +32894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>16</v>
       </c>
@@ -32923,7 +32923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>16</v>
       </c>
@@ -32952,7 +32952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="880" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>16</v>
       </c>
@@ -32981,7 +32981,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="881" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>16</v>
       </c>
@@ -33010,7 +33010,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="882" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>16</v>
       </c>
@@ -33039,7 +33039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="883" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>16</v>
       </c>
@@ -33068,7 +33068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="884" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>16</v>
       </c>
@@ -33097,7 +33097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="885" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>16</v>
       </c>
@@ -33126,7 +33126,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="886" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>16</v>
       </c>
@@ -33155,7 +33155,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="887" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>16</v>
       </c>
@@ -33184,7 +33184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="888" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>16</v>
       </c>
@@ -33213,7 +33213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="889" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>16</v>
       </c>
@@ -33242,7 +33242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="890" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>16</v>
       </c>
@@ -33271,7 +33271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="891" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>16</v>
       </c>
@@ -33300,7 +33300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="892" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>16</v>
       </c>
@@ -33329,7 +33329,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="893" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>16</v>
       </c>
@@ -33358,7 +33358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="894" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>16</v>
       </c>
@@ -33387,7 +33387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="895" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>16</v>
       </c>
@@ -33416,7 +33416,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="896" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>16</v>
       </c>
@@ -33445,7 +33445,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="897" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>16</v>
       </c>
@@ -33474,7 +33474,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="898" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>16</v>
       </c>
@@ -33503,7 +33503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="899" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>16</v>
       </c>
@@ -33532,7 +33532,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="900" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>16</v>
       </c>
@@ -33561,7 +33561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="901" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>16</v>
       </c>
@@ -33590,7 +33590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="902" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>16</v>
       </c>
@@ -33619,7 +33619,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="903" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>16</v>
       </c>
@@ -33648,7 +33648,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="904" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>96</v>
       </c>
@@ -33677,7 +33677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="905" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>100</v>
       </c>
@@ -33706,7 +33706,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>104</v>
       </c>
@@ -33735,7 +33735,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>104</v>
       </c>
@@ -33764,7 +33764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="908" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>109</v>
       </c>
@@ -33793,7 +33793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="909" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>137</v>
       </c>
@@ -33822,7 +33822,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="910" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>175</v>
       </c>
@@ -33851,7 +33851,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="911" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>204</v>
       </c>
@@ -33880,7 +33880,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="912" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>228</v>
       </c>
@@ -33909,7 +33909,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="913" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>240</v>
       </c>
@@ -33938,7 +33938,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="914" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>250</v>
       </c>
@@ -33967,7 +33967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="915" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>293</v>
       </c>
@@ -33996,7 +33996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>347</v>
       </c>
@@ -34025,7 +34025,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="917" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>359</v>
       </c>
@@ -34054,7 +34054,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="918" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>408</v>
       </c>
@@ -34083,7 +34083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="919" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>439</v>
       </c>
@@ -34112,7 +34112,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="920" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>460</v>
       </c>
@@ -34141,7 +34141,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="921" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>597</v>
       </c>
@@ -34170,7 +34170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="922" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>597</v>
       </c>
@@ -34199,7 +34199,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>123</v>
       </c>
@@ -34228,7 +34228,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>123</v>
       </c>
@@ -34257,7 +34257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>123</v>
       </c>
@@ -34286,7 +34286,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="926" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>123</v>
       </c>
@@ -34315,7 +34315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="927" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>37</v>
       </c>
@@ -34344,7 +34344,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="928" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>37</v>
       </c>
@@ -34373,7 +34373,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="929" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>37</v>
       </c>
@@ -34402,7 +34402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="930" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>677</v>
       </c>
@@ -34431,7 +34431,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="931" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>677</v>
       </c>
@@ -34460,7 +34460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="932" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>677</v>
       </c>
@@ -34489,7 +34489,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="933" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>695</v>
       </c>
@@ -34518,7 +34518,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="934" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>695</v>
       </c>
@@ -34547,7 +34547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="935" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>733</v>
       </c>
@@ -34576,7 +34576,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="936" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>752</v>
       </c>
@@ -34605,7 +34605,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="937" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>776</v>
       </c>
@@ -34634,7 +34634,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="938" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>792</v>
       </c>
@@ -34663,7 +34663,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="939" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>792</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="940" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>805</v>
       </c>
@@ -34721,7 +34721,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="941" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>818</v>
       </c>
@@ -34750,7 +34750,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="942" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>458</v>
       </c>
@@ -34779,7 +34779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="943" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>458</v>
       </c>
@@ -34808,7 +34808,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="944" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>458</v>
       </c>
@@ -34837,7 +34837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="945" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>458</v>
       </c>
@@ -34866,7 +34866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="946" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>913</v>
       </c>
@@ -34895,7 +34895,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="947" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>917</v>
       </c>
@@ -34924,7 +34924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="948" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>826</v>
       </c>
@@ -34953,7 +34953,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="949" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>826</v>
       </c>
@@ -34982,7 +34982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>826</v>
       </c>
@@ -35011,7 +35011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="951" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>958</v>
       </c>
@@ -35040,7 +35040,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="952" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>958</v>
       </c>
@@ -35069,7 +35069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="953" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>978</v>
       </c>
@@ -35098,7 +35098,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="954" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>978</v>
       </c>
@@ -35127,7 +35127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="955" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>978</v>
       </c>
@@ -35156,7 +35156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="956" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>332</v>
       </c>
@@ -35185,7 +35185,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="957" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>1034</v>
       </c>
@@ -35214,7 +35214,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="958" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>1034</v>
       </c>
@@ -35243,7 +35243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="959" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>1033</v>
       </c>
@@ -35272,7 +35272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="960" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>1033</v>
       </c>
@@ -35301,7 +35301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="961" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>836</v>
       </c>
@@ -35330,7 +35330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="962" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>1083</v>
       </c>
@@ -35359,7 +35359,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="963" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>1083</v>
       </c>
@@ -35388,7 +35388,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="964" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>1083</v>
       </c>
@@ -35417,7 +35417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="965" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>1083</v>
       </c>
@@ -35446,7 +35446,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="966" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>1153</v>
       </c>
@@ -35475,7 +35475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="967" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>1191</v>
       </c>
@@ -35504,7 +35504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="968" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>16</v>
       </c>
@@ -35533,7 +35533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="969" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>16</v>
       </c>
@@ -35562,7 +35562,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="970" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>16</v>
       </c>
@@ -35591,7 +35591,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="971" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>16</v>
       </c>
@@ -35620,7 +35620,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="972" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>16</v>
       </c>
@@ -35649,7 +35649,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="973" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>16</v>
       </c>
@@ -35678,7 +35678,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="974" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>16</v>
       </c>
@@ -35707,7 +35707,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="975" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>16</v>
       </c>
@@ -35736,7 +35736,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="976" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>16</v>
       </c>
@@ -35765,7 +35765,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="977" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>16</v>
       </c>
@@ -35794,7 +35794,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="978" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>16</v>
       </c>
@@ -35823,7 +35823,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="979" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>16</v>
       </c>
@@ -35852,7 +35852,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="980" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>16</v>
       </c>
@@ -35881,7 +35881,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="981" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>16</v>
       </c>
@@ -35910,7 +35910,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="982" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>16</v>
       </c>
@@ -35939,7 +35939,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="983" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>16</v>
       </c>
@@ -35968,7 +35968,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="984" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>16</v>
       </c>
@@ -35997,7 +35997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="985" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>16</v>
       </c>
@@ -36026,7 +36026,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="986" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>16</v>
       </c>
@@ -36055,7 +36055,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="987" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>16</v>
       </c>
@@ -36084,7 +36084,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="988" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>16</v>
       </c>
@@ -36113,7 +36113,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="989" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>16</v>
       </c>
@@ -36142,7 +36142,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="990" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>16</v>
       </c>
@@ -36171,7 +36171,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="991" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>16</v>
       </c>
@@ -36200,7 +36200,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="992" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>16</v>
       </c>
@@ -36229,7 +36229,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="993" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>16</v>
       </c>
@@ -36258,7 +36258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="994" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>16</v>
       </c>
@@ -36287,7 +36287,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="995" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>16</v>
       </c>
@@ -36316,7 +36316,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="996" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>16</v>
       </c>
@@ -36345,7 +36345,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="997" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>16</v>
       </c>
@@ -36374,7 +36374,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="998" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>16</v>
       </c>
@@ -36403,7 +36403,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="999" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>16</v>
       </c>
@@ -36432,7 +36432,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>16</v>
       </c>
@@ -36461,7 +36461,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>16</v>
       </c>
@@ -36490,7 +36490,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>16</v>
       </c>
@@ -36519,7 +36519,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>16</v>
       </c>
@@ -36548,7 +36548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>16</v>
       </c>
@@ -36577,7 +36577,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>16</v>
       </c>
@@ -36606,7 +36606,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>16</v>
       </c>
@@ -36635,7 +36635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>16</v>
       </c>
@@ -36664,7 +36664,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>16</v>
       </c>
@@ -36693,7 +36693,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>16</v>
       </c>
@@ -36722,7 +36722,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>16</v>
       </c>
@@ -36751,7 +36751,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>16</v>
       </c>
@@ -36780,7 +36780,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>16</v>
       </c>
@@ -36809,7 +36809,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>16</v>
       </c>
@@ -36838,7 +36838,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>16</v>
       </c>
@@ -36867,7 +36867,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>16</v>
       </c>
@@ -36896,7 +36896,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>16</v>
       </c>
@@ -36925,7 +36925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>16</v>
       </c>
@@ -36954,7 +36954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>16</v>
       </c>
@@ -36983,7 +36983,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>16</v>
       </c>
@@ -37012,7 +37012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>16</v>
       </c>
@@ -37041,7 +37041,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>16</v>
       </c>
@@ -37070,7 +37070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>16</v>
       </c>
@@ -37099,7 +37099,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>16</v>
       </c>
@@ -37128,7 +37128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>16</v>
       </c>
@@ -37157,7 +37157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>16</v>
       </c>
@@ -37186,7 +37186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>16</v>
       </c>
@@ -37215,7 +37215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>16</v>
       </c>
@@ -37244,7 +37244,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>16</v>
       </c>
@@ -37273,7 +37273,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>16</v>
       </c>
@@ -37302,7 +37302,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>16</v>
       </c>
@@ -37331,7 +37331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>16</v>
       </c>
@@ -37360,7 +37360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>16</v>
       </c>
@@ -37389,7 +37389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>16</v>
       </c>
@@ -37418,7 +37418,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>16</v>
       </c>
@@ -37447,7 +37447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>16</v>
       </c>
@@ -37476,7 +37476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>16</v>
       </c>
@@ -37505,7 +37505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>16</v>
       </c>
@@ -37534,7 +37534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>16</v>
       </c>
@@ -37563,7 +37563,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>16</v>
       </c>
@@ -37592,7 +37592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>16</v>
       </c>
@@ -37621,7 +37621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>16</v>
       </c>
@@ -37650,7 +37650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>16</v>
       </c>
@@ -37679,7 +37679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>16</v>
       </c>
@@ -37708,7 +37708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>16</v>
       </c>
@@ -37737,7 +37737,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>16</v>
       </c>
@@ -37766,7 +37766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>16</v>
       </c>
@@ -37795,7 +37795,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>16</v>
       </c>
@@ -37824,7 +37824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>16</v>
       </c>
@@ -37853,7 +37853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>16</v>
       </c>
@@ -37882,7 +37882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>16</v>
       </c>
@@ -37911,7 +37911,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>16</v>
       </c>
@@ -37940,7 +37940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>16</v>
       </c>
@@ -37969,7 +37969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>16</v>
       </c>
@@ -37998,7 +37998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>16</v>
       </c>
@@ -38027,7 +38027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>16</v>
       </c>
@@ -38056,7 +38056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>16</v>
       </c>
@@ -38085,7 +38085,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>16</v>
       </c>
@@ -38114,7 +38114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>16</v>
       </c>
@@ -38143,7 +38143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>16</v>
       </c>
@@ -38172,7 +38172,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>16</v>
       </c>
@@ -38201,7 +38201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>16</v>
       </c>
@@ -38230,7 +38230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>16</v>
       </c>
@@ -38259,7 +38259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>16</v>
       </c>
@@ -38292,7 +38292,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:I34 A2:H2 A721:I1063 A720:G720 I720 A348:I719 A347:G347 I347 A38:I38 A35:F35 I35 A40:I337 A39:F39 I39 A339:I346 A338:F338 I338 A36:G37 I36:I37" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I34 A2:H2 A721:I1063 A720:G720 I720 A348:I373 A347:G347 I347 A38:I38 A35:F35 I35 A40:I166 A39:F39 I39 A339:I346 A338:F338 I338 A36:G37 I36:I37 A574:I676 A573:G573 I573 A168:I337 A167:G167 I167 A375:I572 A374:G374 I374 A678:I719 A677:G677 I677" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9553" uniqueCount="2353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9552" uniqueCount="2353">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -8382,8 +8382,8 @@
       <c r="G32" t="s">
         <v>145</v>
       </c>
-      <c r="H32" t="s">
-        <v>16</v>
+      <c r="H32" s="1">
+        <v>46150</v>
       </c>
       <c r="I32" t="s">
         <v>153</v>
@@ -38292,7 +38292,7 @@
   <autoFilter ref="A1:I1063"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:I34 A2:H2 A721:I1063 A720:G720 I720 A348:I373 A347:G347 I347 A38:I38 A35:F35 I35 A40:I166 A39:F39 I39 A339:I346 A338:F338 I338 A36:G37 I36:I37 A574:I676 A573:G573 I573 A168:I337 A167:G167 I167 A375:I572 A374:G374 I374 A678:I719 A677:G677 I677" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I31 A2:H2 A721:I1063 A720:G720 I720 A348:I373 A347:G347 I347 A38:I38 A35:F35 I35 A40:I166 A39:F39 I39 A339:I346 A338:F338 I338 A36:G37 I36:I37 A574:I676 A573:G573 I573 A168:I337 A167:G167 I167 A375:I572 A374:G374 I374 A678:I719 A677:G677 I677 A33:I34 A32:G32 I32" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/planning.xlsx
+++ b/planning.xlsx
@@ -8383,7 +8383,7 @@
         <v>145</v>
       </c>
       <c r="H32" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I32" t="s">
         <v>153</v>
@@ -8470,7 +8470,7 @@
         <v>46149</v>
       </c>
       <c r="H35" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="I35" t="s">
         <v>167</v>
@@ -8586,7 +8586,7 @@
         <v>46149</v>
       </c>
       <c r="H39" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="I39" t="s">
         <v>167</v>
@@ -12298,7 +12298,7 @@
         <v>577</v>
       </c>
       <c r="H167" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I167" t="s">
         <v>578</v>
@@ -17257,7 +17257,7 @@
         <v>46149</v>
       </c>
       <c r="H338" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="I338" t="s">
         <v>167</v>
@@ -18301,7 +18301,7 @@
         <v>1070</v>
       </c>
       <c r="H374" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I374" t="s">
         <v>578</v>
@@ -24072,7 +24072,7 @@
         <v>1493</v>
       </c>
       <c r="H573" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I573" t="s">
         <v>1494</v>
@@ -27088,7 +27088,7 @@
         <v>94</v>
       </c>
       <c r="H677" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I677" t="s">
         <v>578</v>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9564" uniqueCount="2356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9563" uniqueCount="2356">
   <si>
     <t>DATE DE CRÉATION</t>
   </si>
@@ -7468,9 +7468,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I1063"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>117</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>132</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>145</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>153</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>153</v>
       </c>
@@ -8478,14 +8478,14 @@
       <c r="G35" t="s">
         <v>153</v>
       </c>
-      <c r="H35" t="s">
-        <v>164</v>
+      <c r="H35" s="1">
+        <v>46155</v>
       </c>
       <c r="I35" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>166</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>166</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>183</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>187</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>187</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>197</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>206</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>206</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>215</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>215</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>226</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>229</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>229</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>238</v>
       </c>
@@ -9036,7 +9036,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>245</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>250</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>250</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>260</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>260</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>260</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>260</v>
       </c>
@@ -9268,7 +9268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>260</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>260</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>283</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>286</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>286</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>286</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>286</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>286</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>286</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>307</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>307</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>307</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>307</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>319</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>319</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>319</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>319</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>319</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>319</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>319</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>303</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>303</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>303</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>303</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>303</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>356</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>362</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>362</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>368</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>368</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>368</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>368</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>368</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>368</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>368</v>
       </c>
@@ -10312,7 +10312,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>386</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>391</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>391</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>391</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>400</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>400</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>400</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>410</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>410</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>410</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>418</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>418</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>418</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>418</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>418</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>418</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>439</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>439</v>
       </c>
@@ -10834,7 +10834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>439</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>439</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>439</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>76</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>76</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>457</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>457</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>457</v>
       </c>
@@ -11066,7 +11066,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>457</v>
       </c>
@@ -11095,7 +11095,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>472</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>472</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>472</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>472</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>472</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>472</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>472</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>437</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>437</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>437</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>437</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>437</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>437</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>437</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>437</v>
       </c>
@@ -11530,7 +11530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>437</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>512</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>512</v>
       </c>
@@ -11617,7 +11617,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>512</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>521</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>521</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>521</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>521</v>
       </c>
@@ -11762,7 +11762,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>521</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>521</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>536</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>536</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>536</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>536</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>536</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>548</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>548</v>
       </c>
@@ -12023,7 +12023,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>548</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>548</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>548</v>
       </c>
@@ -12110,7 +12110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>548</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>565</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>565</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>565</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>574</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>574</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>574</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>574</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>574</v>
       </c>
@@ -12371,7 +12371,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>574</v>
       </c>
@@ -12400,7 +12400,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>574</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>574</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>574</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>595</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>598</v>
       </c>
@@ -12545,7 +12545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>598</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>598</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>598</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>598</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>607</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>607</v>
       </c>
@@ -12719,7 +12719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>131</v>
       </c>
@@ -12748,7 +12748,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>131</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>131</v>
       </c>
@@ -12806,7 +12806,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>131</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>131</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>131</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>131</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>131</v>
       </c>
@@ -12951,7 +12951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>131</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>131</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>53</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>53</v>
       </c>
@@ -13067,7 +13067,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>53</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>646</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>646</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>646</v>
       </c>
@@ -13183,7 +13183,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>646</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>646</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>646</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>646</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>646</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>646</v>
       </c>
@@ -13357,7 +13357,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>646</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>671</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>671</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>671</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>671</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>671</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>671</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>683</v>
       </c>
@@ -13589,7 +13589,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>686</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>686</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>686</v>
       </c>
@@ -13676,7 +13676,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>686</v>
       </c>
@@ -13705,7 +13705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>686</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>686</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>686</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>686</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>703</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>703</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>703</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>703</v>
       </c>
@@ -13937,7 +13937,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>703</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>703</v>
       </c>
@@ -13995,7 +13995,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>703</v>
       </c>
@@ -14024,7 +14024,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>703</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>703</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>703</v>
       </c>
@@ -14111,7 +14111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>730</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>730</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>730</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>730</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>730</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>739</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>739</v>
       </c>
@@ -14314,7 +14314,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>739</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>739</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>739</v>
       </c>
@@ -14401,7 +14401,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>758</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>758</v>
       </c>
@@ -14459,7 +14459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>758</v>
       </c>
@@ -14488,7 +14488,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>758</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>758</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>767</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>767</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>767</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>767</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>782</v>
       </c>
@@ -14691,7 +14691,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>782</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>782</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>782</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>782</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>782</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>795</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>798</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>798</v>
       </c>
@@ -14923,7 +14923,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>798</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>798</v>
       </c>
@@ -14981,7 +14981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>798</v>
       </c>
@@ -15010,7 +15010,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>798</v>
       </c>
@@ -15039,7 +15039,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>798</v>
       </c>
@@ -15068,7 +15068,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>811</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>811</v>
       </c>
@@ -15126,7 +15126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>811</v>
       </c>
@@ -15155,7 +15155,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>811</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>811</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>811</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>824</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>824</v>
       </c>
@@ -15300,7 +15300,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>824</v>
       </c>
@@ -15329,7 +15329,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>824</v>
       </c>
@@ -15358,7 +15358,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>824</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>824</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>824</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>824</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>824</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>824</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>824</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>824</v>
       </c>
@@ -15590,7 +15590,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>824</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>855</v>
       </c>
@@ -15648,7 +15648,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>855</v>
       </c>
@@ -15677,7 +15677,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>855</v>
       </c>
@@ -15706,7 +15706,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>855</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>855</v>
       </c>
@@ -15764,7 +15764,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>855</v>
       </c>
@@ -15793,7 +15793,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>855</v>
       </c>
@@ -15822,7 +15822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>855</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>855</v>
       </c>
@@ -15880,7 +15880,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>855</v>
       </c>
@@ -15909,7 +15909,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>855</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>855</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>470</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>470</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>470</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>470</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>470</v>
       </c>
@@ -16112,7 +16112,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>470</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>470</v>
       </c>
@@ -16170,7 +16170,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>470</v>
       </c>
@@ -16199,7 +16199,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>470</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>470</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>470</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>470</v>
       </c>
@@ -16315,7 +16315,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>911</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>911</v>
       </c>
@@ -16373,7 +16373,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>915</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>915</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>915</v>
       </c>
@@ -16460,7 +16460,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>924</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>924</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>924</v>
       </c>
@@ -16547,7 +16547,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>924</v>
       </c>
@@ -16576,7 +16576,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>924</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>924</v>
       </c>
@@ -16634,7 +16634,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>924</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>924</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>832</v>
       </c>
@@ -16721,7 +16721,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>832</v>
       </c>
@@ -16750,7 +16750,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>832</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>832</v>
       </c>
@@ -16808,7 +16808,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>832</v>
       </c>
@@ -16837,7 +16837,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>832</v>
       </c>
@@ -16866,7 +16866,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>832</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>832</v>
       </c>
@@ -16924,7 +16924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>832</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>967</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>967</v>
       </c>
@@ -17011,7 +17011,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>967</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>967</v>
       </c>
@@ -17069,7 +17069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>967</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>967</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>967</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>967</v>
       </c>
@@ -17185,7 +17185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>967</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>967</v>
       </c>
@@ -17243,7 +17243,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>987</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>987</v>
       </c>
@@ -17301,7 +17301,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>987</v>
       </c>
@@ -17330,7 +17330,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>987</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>987</v>
       </c>
@@ -17388,7 +17388,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>987</v>
       </c>
@@ -17417,7 +17417,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>987</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>987</v>
       </c>
@@ -17475,7 +17475,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>987</v>
       </c>
@@ -17504,7 +17504,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>987</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>987</v>
       </c>
@@ -17562,7 +17562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>987</v>
       </c>
@@ -17591,7 +17591,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>987</v>
       </c>
@@ -17620,7 +17620,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>987</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1022</v>
       </c>
@@ -17678,7 +17678,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1022</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>341</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>341</v>
       </c>
@@ -17765,7 +17765,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>341</v>
       </c>
@@ -17794,7 +17794,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>341</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>341</v>
       </c>
@@ -17852,7 +17852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>341</v>
       </c>
@@ -17881,7 +17881,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>341</v>
       </c>
@@ -17910,7 +17910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>341</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>341</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1044</v>
       </c>
@@ -17997,7 +17997,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1044</v>
       </c>
@@ -18026,7 +18026,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1044</v>
       </c>
@@ -18055,7 +18055,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1044</v>
       </c>
@@ -18084,7 +18084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1044</v>
       </c>
@@ -18113,7 +18113,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1044</v>
       </c>
@@ -18142,7 +18142,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1044</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1043</v>
       </c>
@@ -18200,7 +18200,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1043</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1043</v>
       </c>
@@ -18258,7 +18258,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1043</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1043</v>
       </c>
@@ -18316,7 +18316,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1043</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1043</v>
       </c>
@@ -18374,7 +18374,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1043</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1043</v>
       </c>
@@ -18432,7 +18432,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>842</v>
       </c>
@@ -18461,7 +18461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>842</v>
       </c>
@@ -18490,7 +18490,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>842</v>
       </c>
@@ -18519,7 +18519,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>842</v>
       </c>
@@ -18548,7 +18548,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>842</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>842</v>
       </c>
@@ -18606,7 +18606,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1092</v>
       </c>
@@ -18635,7 +18635,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1092</v>
       </c>
@@ -18664,7 +18664,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1092</v>
       </c>
@@ -18693,7 +18693,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1092</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1092</v>
       </c>
@@ -18751,7 +18751,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1092</v>
       </c>
@@ -18780,7 +18780,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1092</v>
       </c>
@@ -18809,7 +18809,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1092</v>
       </c>
@@ -18838,7 +18838,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1092</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1092</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1092</v>
       </c>
@@ -18925,7 +18925,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1092</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1092</v>
       </c>
@@ -18983,7 +18983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1092</v>
       </c>
@@ -19012,7 +19012,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1092</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1092</v>
       </c>
@@ -19070,7 +19070,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1092</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1126</v>
       </c>
@@ -19128,7 +19128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1130</v>
       </c>
@@ -19157,7 +19157,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1130</v>
       </c>
@@ -19186,7 +19186,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1130</v>
       </c>
@@ -19215,7 +19215,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1130</v>
       </c>
@@ -19244,7 +19244,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1130</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1130</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1130</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1145</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1145</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1145</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1145</v>
       </c>
@@ -19447,7 +19447,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1145</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1145</v>
       </c>
@@ -19505,7 +19505,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1145</v>
       </c>
@@ -19534,7 +19534,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1163</v>
       </c>
@@ -19563,7 +19563,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1163</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1163</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1163</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1163</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1163</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1163</v>
       </c>
@@ -19737,7 +19737,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1163</v>
       </c>
@@ -19766,7 +19766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1163</v>
       </c>
@@ -19795,7 +19795,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1184</v>
       </c>
@@ -19824,7 +19824,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1184</v>
       </c>
@@ -19853,7 +19853,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1184</v>
       </c>
@@ -19882,7 +19882,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1184</v>
       </c>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1184</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="431" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1184</v>
       </c>
@@ -19969,7 +19969,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1184</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1184</v>
       </c>
@@ -20027,7 +20027,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1184</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1200</v>
       </c>
@@ -20085,7 +20085,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1200</v>
       </c>
@@ -20114,7 +20114,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1200</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1200</v>
       </c>
@@ -20172,7 +20172,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1200</v>
       </c>
@@ -20201,7 +20201,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1200</v>
       </c>
@@ -20230,7 +20230,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1200</v>
       </c>
@@ -20259,7 +20259,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1200</v>
       </c>
@@ -20288,7 +20288,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1200</v>
       </c>
@@ -20317,7 +20317,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1200</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1200</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1200</v>
       </c>
@@ -20404,7 +20404,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1200</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1226</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="449" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1228</v>
       </c>
@@ -20491,7 +20491,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1231</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="451" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1231</v>
       </c>
@@ -20549,7 +20549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="452" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="453" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="454" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -20636,7 +20636,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="455" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -20665,7 +20665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="457" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -20723,7 +20723,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -20752,7 +20752,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="460" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -20810,7 +20810,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="461" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -20839,7 +20839,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="462" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -20868,7 +20868,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="463" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -20897,7 +20897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -20926,7 +20926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -20955,7 +20955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="466" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="467" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -21013,7 +21013,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="468" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="469" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -21071,7 +21071,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="470" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -21100,7 +21100,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="471" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -21129,7 +21129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="472" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -21158,7 +21158,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="473" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -21187,7 +21187,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="474" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="475" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="476" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -21274,7 +21274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -21303,7 +21303,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -21361,7 +21361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -21390,7 +21390,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -21419,7 +21419,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="482" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -21448,7 +21448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>16</v>
       </c>
@@ -21477,7 +21477,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="484" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>16</v>
       </c>
@@ -21506,7 +21506,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="485" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>16</v>
       </c>
@@ -21535,7 +21535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>16</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="487" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>16</v>
       </c>
@@ -21593,7 +21593,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>16</v>
       </c>
@@ -21622,7 +21622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="489" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>16</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="490" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>16</v>
       </c>
@@ -21680,7 +21680,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="491" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>16</v>
       </c>
@@ -21709,7 +21709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>16</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="493" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>16</v>
       </c>
@@ -21767,7 +21767,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="494" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>16</v>
       </c>
@@ -21796,7 +21796,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="495" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>16</v>
       </c>
@@ -21825,7 +21825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>16</v>
       </c>
@@ -21854,7 +21854,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="497" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>16</v>
       </c>
@@ -21883,7 +21883,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="498" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>16</v>
       </c>
@@ -21912,7 +21912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="499" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>16</v>
       </c>
@@ -21941,7 +21941,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="500" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>16</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="501" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>16</v>
       </c>
@@ -21999,7 +21999,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="502" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>16</v>
       </c>
@@ -22028,7 +22028,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="503" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>16</v>
       </c>
@@ -22057,7 +22057,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="504" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -22086,7 +22086,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="505" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -22115,7 +22115,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="506" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -22144,7 +22144,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="507" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -22173,7 +22173,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="508" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -22202,7 +22202,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="509" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -22231,7 +22231,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="510" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>16</v>
       </c>
@@ -22289,7 +22289,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="512" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>16</v>
       </c>
@@ -22318,7 +22318,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="513" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>16</v>
       </c>
@@ -22347,7 +22347,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="514" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>16</v>
       </c>
@@ -22376,7 +22376,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="515" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>16</v>
       </c>
@@ -22405,7 +22405,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>16</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="517" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>16</v>
       </c>
@@ -22463,7 +22463,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>16</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="519" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>16</v>
       </c>
@@ -22521,7 +22521,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="520" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>16</v>
       </c>
@@ -22550,7 +22550,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="521" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>16</v>
       </c>
@@ -22579,7 +22579,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>16</v>
       </c>
@@ -22608,7 +22608,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="523" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>16</v>
       </c>
@@ -22637,7 +22637,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="524" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>16</v>
       </c>
@@ -22666,7 +22666,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>16</v>
       </c>
@@ -22695,7 +22695,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="526" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>16</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>16</v>
       </c>
@@ -22753,7 +22753,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="528" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>16</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="529" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>16</v>
       </c>
@@ -22811,7 +22811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="530" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>16</v>
       </c>
@@ -22840,7 +22840,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="531" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>16</v>
       </c>
@@ -22869,7 +22869,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="532" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>16</v>
       </c>
@@ -22898,7 +22898,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="533" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>16</v>
       </c>
@@ -22927,7 +22927,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="534" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>16</v>
       </c>
@@ -22956,7 +22956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="535" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>16</v>
       </c>
@@ -22985,7 +22985,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="536" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>16</v>
       </c>
@@ -23014,7 +23014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="537" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>16</v>
       </c>
@@ -23043,7 +23043,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="538" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>16</v>
       </c>
@@ -23072,7 +23072,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>16</v>
       </c>
@@ -23101,7 +23101,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="540" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>16</v>
       </c>
@@ -23130,7 +23130,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="541" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>16</v>
       </c>
@@ -23159,7 +23159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="542" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>16</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>16</v>
       </c>
@@ -23217,7 +23217,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="544" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>16</v>
       </c>
@@ -23246,7 +23246,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>16</v>
       </c>
@@ -23275,7 +23275,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>16</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="547" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>16</v>
       </c>
@@ -23333,7 +23333,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>16</v>
       </c>
@@ -23362,7 +23362,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>16</v>
       </c>
@@ -23391,7 +23391,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="550" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>16</v>
       </c>
@@ -23420,7 +23420,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="551" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>16</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="552" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>16</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="553" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553